--- a/Duwalcoe_Quick_FNA_Template.xlsx
+++ b/Duwalcoe_Quick_FNA_Template.xlsx
@@ -59,10 +59,10 @@
     <definedName name="QF_A_Inclusion">Inputs!$H$100</definedName>
     <definedName name="QF_A_PRExcl">Inputs!$H$101</definedName>
     <definedName name="QF_A_TaxTable">Inputs!$C$104:$E$110</definedName>
-    <definedName name="QF_K_checks">Inputs!$B$118</definedName>
-    <definedName name="QF_T_checks">Inputs!$B$119:$B$132</definedName>
+    <definedName name="QF_K_checks">Inputs!$B$119</definedName>
+    <definedName name="QF_T_checks">Inputs!$B$120:$B$133</definedName>
     <definedName name="QF_W_cost">Workings!$C$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inputs'!$A1:$J132</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inputs'!$A1:$J133</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inputs'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Summary'!$A1:$D35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$1:$2</definedName>
@@ -135,7 +135,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0</t>
+    <t>1.1</t>
   </si>
   <si>
     <t>Shares and unit trusts</t>
@@ -980,7 +980,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="19">
     <dxf>
       <font>
         <b/>
@@ -1000,6 +1000,108 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFEAF4EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFB45309"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF1E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC78A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1538,7 +1640,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:W132"/>
+  <dimension ref="B1:W133"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1562,6 +1664,14 @@
     <col min="21" max="21" width="9" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="9" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="9" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="9" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="9" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="9" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="9" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="9" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="9" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="9" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
@@ -3432,21 +3542,23 @@
       <c r="I117" s="19"/>
       <c r="J117" s="19"/>
     </row>
-    <row r="118" hidden="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B118" t="s">
+    <row r="118" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B118" s="19">
+        <f>IF(((C8&lt;&gt;AB8)+(C9&lt;&gt;AB9)+(C10&lt;&gt;AB10)+(C11&lt;&gt;AB11)+(C12&lt;&gt;AB12)+(C13&lt;&gt;AB13)+(C14&lt;&gt;AB14)+(C16&lt;&gt;AB16)+(C17&lt;&gt;AB17)+SUMPRODUCT(--(B22:I39&lt;&gt;AA22:AH39))+SUMPRODUCT(--(B45:I54&lt;&gt;AA45:AH54))+SUMPRODUCT(--(B59:I70&lt;&gt;AA59:AH70))+SUMPRODUCT(--(B76:I83&lt;&gt;AA76:AH83)))=0,"✓ Everything in sections 1 to 5 matches the CRM.","● "&amp;((C8&lt;&gt;AB8)+(C9&lt;&gt;AB9)+(C10&lt;&gt;AB10)+(C11&lt;&gt;AB11)+(C12&lt;&gt;AB12)+(C13&lt;&gt;AB13)+(C14&lt;&gt;AB14)+(C16&lt;&gt;AB16)+(C17&lt;&gt;AB17)+SUMPRODUCT(--(B22:I39&lt;&gt;AA22:AH39))+SUMPRODUCT(--(B45:I54&lt;&gt;AA45:AH54))+SUMPRODUCT(--(B59:I70&lt;&gt;AA59:AH70))+SUMPRODUCT(--(B76:I83&lt;&gt;AA76:AH83)))&amp;IF(((C8&lt;&gt;AB8)+(C9&lt;&gt;AB9)+(C10&lt;&gt;AB10)+(C11&lt;&gt;AB11)+(C12&lt;&gt;AB12)+(C13&lt;&gt;AB13)+(C14&lt;&gt;AB14)+(C16&lt;&gt;AB16)+(C17&lt;&gt;AB17)+SUMPRODUCT(--(B22:I39&lt;&gt;AA22:AH39))+SUMPRODUCT(--(B45:I54&lt;&gt;AA45:AH54))+SUMPRODUCT(--(B59:I70&lt;&gt;AA59:AH70))+SUMPRODUCT(--(B76:I83&lt;&gt;AA76:AH83)))=1," cell differs"," cells differ")&amp;" from the CRM (orange): update the CRM if they are facts, not a what-if.")</f>
+      </c>
+      <c r="C118" s="19"/>
+      <c r="D118" s="19"/>
+      <c r="E118" s="19"/>
+      <c r="F118" s="19"/>
+      <c r="G118" s="19"/>
+      <c r="H118" s="19"/>
+      <c r="I118" s="19"/>
+      <c r="J118" s="19"/>
+    </row>
+    <row r="119" hidden="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="119" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B119" s="20"/>
-      <c r="C119" s="20"/>
-      <c r="D119" s="20"/>
-      <c r="E119" s="20"/>
-      <c r="F119" s="20"/>
-      <c r="G119" s="20"/>
-      <c r="H119" s="20"/>
-      <c r="I119" s="20"/>
-      <c r="J119" s="20"/>
     </row>
     <row r="120" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="20"/>
@@ -3591,9 +3703,20 @@
       <c r="I132" s="20"/>
       <c r="J132" s="20"/>
     </row>
+    <row r="133" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B133" s="20"/>
+      <c r="C133" s="20"/>
+      <c r="D133" s="20"/>
+      <c r="E133" s="20"/>
+      <c r="F133" s="20"/>
+      <c r="G133" s="20"/>
+      <c r="H133" s="20"/>
+      <c r="I133" s="20"/>
+      <c r="J133" s="20"/>
+    </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
-  <mergeCells count="41">
+  <mergeCells count="42">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="C8:E8"/>
@@ -3621,7 +3744,7 @@
     <mergeCell ref="B115:J115"/>
     <mergeCell ref="B116:J116"/>
     <mergeCell ref="B117:J117"/>
-    <mergeCell ref="B119:J119"/>
+    <mergeCell ref="B118:J118"/>
     <mergeCell ref="B120:J120"/>
     <mergeCell ref="B121:J121"/>
     <mergeCell ref="B122:J122"/>
@@ -3635,13 +3758,82 @@
     <mergeCell ref="B130:J130"/>
     <mergeCell ref="B131:J131"/>
     <mergeCell ref="B132:J132"/>
+    <mergeCell ref="B133:J133"/>
   </mergeCells>
-  <conditionalFormatting sqref="B114:J132">
+  <conditionalFormatting sqref="B114:J133">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEFT($B114,1)="✗"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>LEFT($B114,1)="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>LEFT($B114,1)="●"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>C8&lt;&gt;AB8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>C9&lt;&gt;AB9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>C10&lt;&gt;AB10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>C11&lt;&gt;AB11</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>C12&lt;&gt;AB12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>C13&lt;&gt;AB13</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>C14&lt;&gt;AB14</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>C16&lt;&gt;AB16</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>C17&lt;&gt;AB17</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:I39">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>B22&lt;&gt;AA22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45:I54">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>B45&lt;&gt;AA45</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59:I70">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>B59&lt;&gt;AA59</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76:I83">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>B76&lt;&gt;AA76</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="30">
@@ -3784,7 +3976,7 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="21">
-        <f>IF(OR(COUNTIF('Inputs'!$B$119:$B$132,"✗ Full FNA*")&gt;0,LEFT('Inputs'!$B$117,1)="✗"),"NOT FOR THE CLIENT: this case needs the full FNA (see Checks on Inputs)","")</f>
+        <f>IF(OR(COUNTIF('Inputs'!$B$120:$B$133,"✗ Full FNA*")&gt;0,LEFT('Inputs'!$B$117,1)="✗"),"NOT FOR THE CLIENT: this case needs the full FNA (see Checks on Inputs)","")</f>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -4051,15 +4243,15 @@
     <mergeCell ref="B35:D35"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:D12">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>'Workings'!$C$56=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:D26">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>LEFT(C26,5)="Short"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>LEFT(C26,7)="Covered"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Duwalcoe_Quick_FNA_Template.xlsx
+++ b/Duwalcoe_Quick_FNA_Template.xlsx
@@ -59,16 +59,16 @@
     <definedName name="QF_A_Inclusion">Inputs!$H$100</definedName>
     <definedName name="QF_A_PRExcl">Inputs!$H$101</definedName>
     <definedName name="QF_A_TaxTable">Inputs!$C$104:$E$110</definedName>
-    <definedName name="QF_K_checks">Inputs!$B$119</definedName>
-    <definedName name="QF_T_checks">Inputs!$B$120:$B$133</definedName>
-    <definedName name="QF_W_cost">Workings!$C$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inputs'!$A1:$J133</definedName>
+    <definedName name="QF_K_checks">Inputs!$B$120</definedName>
+    <definedName name="QF_T_checks">Inputs!$B$121:$B$134</definedName>
+    <definedName name="QF_W_cost">Workings!$C$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inputs'!$A1:$J134</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inputs'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Summary'!$A1:$D35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Summary'!$A1:$D36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Figures for quoting'!$A1:$D35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Figures for quoting'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Workings'!$A1:$D60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Workings'!$A1:$D68</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Workings'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="198">
   <si>
     <t>kind</t>
   </si>
@@ -135,7 +135,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1</t>
+    <t>1.2</t>
   </si>
   <si>
     <t>Shares and unit trusts</t>
@@ -636,7 +636,13 @@
     <t>Average rate (duty / net value)</t>
   </si>
   <si>
+    <t>Estate duty the named people pay themselves (the executor recovers it from them):</t>
+  </si>
+  <si>
     <t>Less duty the executor recovers from named people (policies and bequests)</t>
+  </si>
+  <si>
+    <t>If the executor cannot recover it from them, the estate pays it.</t>
   </si>
   <si>
     <t>3. Does the estate have enough cash?</t>
@@ -1640,7 +1646,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:W133"/>
+  <dimension ref="B1:X134"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1664,6 +1670,7 @@
     <col min="21" max="21" width="9" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="9" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="9" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="9" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="9" hidden="1" customWidth="1"/>
     <col min="28" max="28" width="9" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="9" hidden="1" customWidth="1"/>
@@ -1879,7 +1886,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B22" s="8"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
@@ -1927,8 +1934,11 @@
       <c r="W22">
         <f>IF(AND(B22="",N(D22)=0),0,IF(OR(C22="",G22=""),1,0))</f>
       </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X22">
+        <f>IF(S22&gt;0,COUNTIF(S$22:S22,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
       <c r="C23" s="10"/>
       <c r="D23" s="11"/>
@@ -1976,8 +1986,11 @@
       <c r="W23">
         <f>IF(AND(B23="",N(D23)=0),0,IF(OR(C23="",G23=""),1,0))</f>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X23">
+        <f>IF(S23&gt;0,COUNTIF(S$22:S23,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="8"/>
       <c r="C24" s="10"/>
       <c r="D24" s="11"/>
@@ -2025,8 +2038,11 @@
       <c r="W24">
         <f>IF(AND(B24="",N(D24)=0),0,IF(OR(C24="",G24=""),1,0))</f>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X24">
+        <f>IF(S24&gt;0,COUNTIF(S$22:S24,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="8"/>
       <c r="C25" s="10"/>
       <c r="D25" s="11"/>
@@ -2074,8 +2090,11 @@
       <c r="W25">
         <f>IF(AND(B25="",N(D25)=0),0,IF(OR(C25="",G25=""),1,0))</f>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X25">
+        <f>IF(S25&gt;0,COUNTIF(S$22:S25,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="8"/>
       <c r="C26" s="10"/>
       <c r="D26" s="11"/>
@@ -2123,8 +2142,11 @@
       <c r="W26">
         <f>IF(AND(B26="",N(D26)=0),0,IF(OR(C26="",G26=""),1,0))</f>
       </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X26">
+        <f>IF(S26&gt;0,COUNTIF(S$22:S26,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="8"/>
       <c r="C27" s="10"/>
       <c r="D27" s="11"/>
@@ -2172,8 +2194,11 @@
       <c r="W27">
         <f>IF(AND(B27="",N(D27)=0),0,IF(OR(C27="",G27=""),1,0))</f>
       </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X27">
+        <f>IF(S27&gt;0,COUNTIF(S$22:S27,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="8"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
@@ -2221,8 +2246,11 @@
       <c r="W28">
         <f>IF(AND(B28="",N(D28)=0),0,IF(OR(C28="",G28=""),1,0))</f>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X28">
+        <f>IF(S28&gt;0,COUNTIF(S$22:S28,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" s="8"/>
       <c r="C29" s="10"/>
       <c r="D29" s="11"/>
@@ -2270,8 +2298,11 @@
       <c r="W29">
         <f>IF(AND(B29="",N(D29)=0),0,IF(OR(C29="",G29=""),1,0))</f>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X29">
+        <f>IF(S29&gt;0,COUNTIF(S$22:S29,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
       <c r="C30" s="10"/>
       <c r="D30" s="11"/>
@@ -2319,8 +2350,11 @@
       <c r="W30">
         <f>IF(AND(B30="",N(D30)=0),0,IF(OR(C30="",G30=""),1,0))</f>
       </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X30">
+        <f>IF(S30&gt;0,COUNTIF(S$22:S30,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="8"/>
       <c r="C31" s="10"/>
       <c r="D31" s="11"/>
@@ -2368,8 +2402,11 @@
       <c r="W31">
         <f>IF(AND(B31="",N(D31)=0),0,IF(OR(C31="",G31=""),1,0))</f>
       </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X31">
+        <f>IF(S31&gt;0,COUNTIF(S$22:S31,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="8"/>
       <c r="C32" s="10"/>
       <c r="D32" s="11"/>
@@ -2417,8 +2454,11 @@
       <c r="W32">
         <f>IF(AND(B32="",N(D32)=0),0,IF(OR(C32="",G32=""),1,0))</f>
       </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X32">
+        <f>IF(S32&gt;0,COUNTIF(S$22:S32,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B33" s="8"/>
       <c r="C33" s="10"/>
       <c r="D33" s="11"/>
@@ -2466,8 +2506,11 @@
       <c r="W33">
         <f>IF(AND(B33="",N(D33)=0),0,IF(OR(C33="",G33=""),1,0))</f>
       </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X33">
+        <f>IF(S33&gt;0,COUNTIF(S$22:S33,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" s="8"/>
       <c r="C34" s="10"/>
       <c r="D34" s="11"/>
@@ -2515,8 +2558,11 @@
       <c r="W34">
         <f>IF(AND(B34="",N(D34)=0),0,IF(OR(C34="",G34=""),1,0))</f>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X34">
+        <f>IF(S34&gt;0,COUNTIF(S$22:S34,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B35" s="8"/>
       <c r="C35" s="10"/>
       <c r="D35" s="11"/>
@@ -2564,8 +2610,11 @@
       <c r="W35">
         <f>IF(AND(B35="",N(D35)=0),0,IF(OR(C35="",G35=""),1,0))</f>
       </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X35">
+        <f>IF(S35&gt;0,COUNTIF(S$22:S35,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B36" s="8"/>
       <c r="C36" s="10"/>
       <c r="D36" s="11"/>
@@ -2613,8 +2662,11 @@
       <c r="W36">
         <f>IF(AND(B36="",N(D36)=0),0,IF(OR(C36="",G36=""),1,0))</f>
       </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X36">
+        <f>IF(S36&gt;0,COUNTIF(S$22:S36,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B37" s="8"/>
       <c r="C37" s="10"/>
       <c r="D37" s="11"/>
@@ -2662,8 +2714,11 @@
       <c r="W37">
         <f>IF(AND(B37="",N(D37)=0),0,IF(OR(C37="",G37=""),1,0))</f>
       </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X37">
+        <f>IF(S37&gt;0,COUNTIF(S$22:S37,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B38" s="8"/>
       <c r="C38" s="10"/>
       <c r="D38" s="11"/>
@@ -2711,8 +2766,11 @@
       <c r="W38">
         <f>IF(AND(B38="",N(D38)=0),0,IF(OR(C38="",G38=""),1,0))</f>
       </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X38">
+        <f>IF(S38&gt;0,COUNTIF(S$22:S38,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B39" s="8"/>
       <c r="C39" s="10"/>
       <c r="D39" s="11"/>
@@ -2760,6 +2818,9 @@
       <c r="W39">
         <f>IF(AND(B39="",N(D39)=0),0,IF(OR(C39="",G39=""),1,0))</f>
       </c>
+      <c r="X39">
+        <f>IF(S39&gt;0,COUNTIF(S$22:S39,"&gt;0"),0)</f>
+      </c>
     </row>
     <row r="40" ht="26" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="16" t="s">
@@ -2906,7 +2967,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B59" s="8"/>
       <c r="C59" s="10"/>
       <c r="D59" s="11"/>
@@ -2921,8 +2982,11 @@
       <c r="N59">
         <f>ROUND('Workings'!$D$37*L59,2)</f>
       </c>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O59">
+        <f>IF(L59&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L59,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B60" s="8"/>
       <c r="C60" s="10"/>
       <c r="D60" s="11"/>
@@ -2937,8 +3001,11 @@
       <c r="N60">
         <f>ROUND('Workings'!$D$37*L60,2)</f>
       </c>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O60">
+        <f>IF(L60&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L60,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B61" s="8"/>
       <c r="C61" s="10"/>
       <c r="D61" s="11"/>
@@ -2953,8 +3020,11 @@
       <c r="N61">
         <f>ROUND('Workings'!$D$37*L61,2)</f>
       </c>
-    </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O61">
+        <f>IF(L61&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L61,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B62" s="8"/>
       <c r="C62" s="10"/>
       <c r="D62" s="11"/>
@@ -2969,8 +3039,11 @@
       <c r="N62">
         <f>ROUND('Workings'!$D$37*L62,2)</f>
       </c>
-    </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O62">
+        <f>IF(L62&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L62,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B63" s="8"/>
       <c r="C63" s="10"/>
       <c r="D63" s="11"/>
@@ -2985,8 +3058,11 @@
       <c r="N63">
         <f>ROUND('Workings'!$D$37*L63,2)</f>
       </c>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O63">
+        <f>IF(L63&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L63,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B64" s="8"/>
       <c r="C64" s="10"/>
       <c r="D64" s="11"/>
@@ -3001,8 +3077,11 @@
       <c r="N64">
         <f>ROUND('Workings'!$D$37*L64,2)</f>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O64">
+        <f>IF(L64&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L64,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B65" s="8"/>
       <c r="C65" s="10"/>
       <c r="D65" s="11"/>
@@ -3017,8 +3096,11 @@
       <c r="N65">
         <f>ROUND('Workings'!$D$37*L65,2)</f>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O65">
+        <f>IF(L65&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L65,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B66" s="8"/>
       <c r="C66" s="10"/>
       <c r="D66" s="11"/>
@@ -3033,8 +3115,11 @@
       <c r="N66">
         <f>ROUND('Workings'!$D$37*L66,2)</f>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O66">
+        <f>IF(L66&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L66,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B67" s="8"/>
       <c r="C67" s="10"/>
       <c r="D67" s="11"/>
@@ -3049,8 +3134,11 @@
       <c r="N67">
         <f>ROUND('Workings'!$D$37*L67,2)</f>
       </c>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O67">
+        <f>IF(L67&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L67,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B68" s="8"/>
       <c r="C68" s="10"/>
       <c r="D68" s="11"/>
@@ -3065,8 +3153,11 @@
       <c r="N68">
         <f>ROUND('Workings'!$D$37*L68,2)</f>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O68">
+        <f>IF(L68&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L68,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B69" s="8"/>
       <c r="C69" s="10"/>
       <c r="D69" s="11"/>
@@ -3081,8 +3172,11 @@
       <c r="N69">
         <f>ROUND('Workings'!$D$37*L69,2)</f>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O69">
+        <f>IF(L69&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L69,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B70" s="8"/>
       <c r="C70" s="10"/>
       <c r="D70" s="11"/>
@@ -3096,6 +3190,9 @@
       </c>
       <c r="N70">
         <f>ROUND('Workings'!$D$37*L70,2)</f>
+      </c>
+      <c r="O70">
+        <f>IF(L70&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L70,"&gt;0"),0)</f>
       </c>
     </row>
     <row r="71" ht="26" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
@@ -3544,7 +3641,7 @@
     </row>
     <row r="118" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="19">
-        <f>IF(((C8&lt;&gt;AB8)+(C9&lt;&gt;AB9)+(C10&lt;&gt;AB10)+(C11&lt;&gt;AB11)+(C12&lt;&gt;AB12)+(C13&lt;&gt;AB13)+(C14&lt;&gt;AB14)+(C16&lt;&gt;AB16)+(C17&lt;&gt;AB17)+SUMPRODUCT(--(B22:I39&lt;&gt;AA22:AH39))+SUMPRODUCT(--(B45:I54&lt;&gt;AA45:AH54))+SUMPRODUCT(--(B59:I70&lt;&gt;AA59:AH70))+SUMPRODUCT(--(B76:I83&lt;&gt;AA76:AH83)))=0,"✓ Everything in sections 1 to 5 matches the CRM.","● "&amp;((C8&lt;&gt;AB8)+(C9&lt;&gt;AB9)+(C10&lt;&gt;AB10)+(C11&lt;&gt;AB11)+(C12&lt;&gt;AB12)+(C13&lt;&gt;AB13)+(C14&lt;&gt;AB14)+(C16&lt;&gt;AB16)+(C17&lt;&gt;AB17)+SUMPRODUCT(--(B22:I39&lt;&gt;AA22:AH39))+SUMPRODUCT(--(B45:I54&lt;&gt;AA45:AH54))+SUMPRODUCT(--(B59:I70&lt;&gt;AA59:AH70))+SUMPRODUCT(--(B76:I83&lt;&gt;AA76:AH83)))&amp;IF(((C8&lt;&gt;AB8)+(C9&lt;&gt;AB9)+(C10&lt;&gt;AB10)+(C11&lt;&gt;AB11)+(C12&lt;&gt;AB12)+(C13&lt;&gt;AB13)+(C14&lt;&gt;AB14)+(C16&lt;&gt;AB16)+(C17&lt;&gt;AB17)+SUMPRODUCT(--(B22:I39&lt;&gt;AA22:AH39))+SUMPRODUCT(--(B45:I54&lt;&gt;AA45:AH54))+SUMPRODUCT(--(B59:I70&lt;&gt;AA59:AH70))+SUMPRODUCT(--(B76:I83&lt;&gt;AA76:AH83)))=1," cell differs"," cells differ")&amp;" from the CRM (orange): update the CRM if they are facts, not a what-if.")</f>
+        <f>IF((COUNTIF(S22:S39,"&gt;0")+COUNTIF(L59:L70,"&gt;0"))&gt;6,"● "&amp;(COUNTIF(S22:S39,"&gt;0")+COUNTIF(L59:L70,"&gt;0"))&amp;" named people pay estate duty: Workings lists the first 6; the total includes them all.","✓ Every named person who pays estate duty is listed on Workings.")</f>
       </c>
       <c r="C118" s="19"/>
       <c r="D118" s="19"/>
@@ -3555,21 +3652,23 @@
       <c r="I118" s="19"/>
       <c r="J118" s="19"/>
     </row>
-    <row r="119" hidden="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B119" t="s">
+    <row r="119" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B119" s="19">
+        <f>IF(((C8&lt;&gt;AB8)+(C9&lt;&gt;AB9)+(C10&lt;&gt;AB10)+(C11&lt;&gt;AB11)+(C12&lt;&gt;AB12)+(C13&lt;&gt;AB13)+(C14&lt;&gt;AB14)+(C16&lt;&gt;AB16)+(C17&lt;&gt;AB17)+SUMPRODUCT(--(B22:I39&lt;&gt;AA22:AH39))+SUMPRODUCT(--(B45:I54&lt;&gt;AA45:AH54))+SUMPRODUCT(--(B59:I70&lt;&gt;AA59:AH70))+SUMPRODUCT(--(B76:I83&lt;&gt;AA76:AH83)))=0,"✓ Everything in sections 1 to 5 matches the CRM.","● "&amp;((C8&lt;&gt;AB8)+(C9&lt;&gt;AB9)+(C10&lt;&gt;AB10)+(C11&lt;&gt;AB11)+(C12&lt;&gt;AB12)+(C13&lt;&gt;AB13)+(C14&lt;&gt;AB14)+(C16&lt;&gt;AB16)+(C17&lt;&gt;AB17)+SUMPRODUCT(--(B22:I39&lt;&gt;AA22:AH39))+SUMPRODUCT(--(B45:I54&lt;&gt;AA45:AH54))+SUMPRODUCT(--(B59:I70&lt;&gt;AA59:AH70))+SUMPRODUCT(--(B76:I83&lt;&gt;AA76:AH83)))&amp;IF(((C8&lt;&gt;AB8)+(C9&lt;&gt;AB9)+(C10&lt;&gt;AB10)+(C11&lt;&gt;AB11)+(C12&lt;&gt;AB12)+(C13&lt;&gt;AB13)+(C14&lt;&gt;AB14)+(C16&lt;&gt;AB16)+(C17&lt;&gt;AB17)+SUMPRODUCT(--(B22:I39&lt;&gt;AA22:AH39))+SUMPRODUCT(--(B45:I54&lt;&gt;AA45:AH54))+SUMPRODUCT(--(B59:I70&lt;&gt;AA59:AH70))+SUMPRODUCT(--(B76:I83&lt;&gt;AA76:AH83)))=1," cell differs"," cells differ")&amp;" from the CRM (orange): update the CRM if they are facts, not a what-if.")</f>
+      </c>
+      <c r="C119" s="19"/>
+      <c r="D119" s="19"/>
+      <c r="E119" s="19"/>
+      <c r="F119" s="19"/>
+      <c r="G119" s="19"/>
+      <c r="H119" s="19"/>
+      <c r="I119" s="19"/>
+      <c r="J119" s="19"/>
+    </row>
+    <row r="120" hidden="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="120" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B120" s="20"/>
-      <c r="C120" s="20"/>
-      <c r="D120" s="20"/>
-      <c r="E120" s="20"/>
-      <c r="F120" s="20"/>
-      <c r="G120" s="20"/>
-      <c r="H120" s="20"/>
-      <c r="I120" s="20"/>
-      <c r="J120" s="20"/>
     </row>
     <row r="121" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="20"/>
@@ -3714,9 +3813,20 @@
       <c r="I133" s="20"/>
       <c r="J133" s="20"/>
     </row>
+    <row r="134" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B134" s="20"/>
+      <c r="C134" s="20"/>
+      <c r="D134" s="20"/>
+      <c r="E134" s="20"/>
+      <c r="F134" s="20"/>
+      <c r="G134" s="20"/>
+      <c r="H134" s="20"/>
+      <c r="I134" s="20"/>
+      <c r="J134" s="20"/>
+    </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
-  <mergeCells count="42">
+  <mergeCells count="43">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="C8:E8"/>
@@ -3745,7 +3855,7 @@
     <mergeCell ref="B116:J116"/>
     <mergeCell ref="B117:J117"/>
     <mergeCell ref="B118:J118"/>
-    <mergeCell ref="B120:J120"/>
+    <mergeCell ref="B119:J119"/>
     <mergeCell ref="B121:J121"/>
     <mergeCell ref="B122:J122"/>
     <mergeCell ref="B123:J123"/>
@@ -3759,8 +3869,9 @@
     <mergeCell ref="B131:J131"/>
     <mergeCell ref="B132:J132"/>
     <mergeCell ref="B133:J133"/>
+    <mergeCell ref="B134:J134"/>
   </mergeCells>
-  <conditionalFormatting sqref="B114:J133">
+  <conditionalFormatting sqref="B114:J134">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEFT($B114,1)="✗"</formula>
     </cfRule>
@@ -3951,7 +4062,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D35"/>
+  <dimension ref="B1:D36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -3976,7 +4087,7 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="21">
-        <f>IF(OR(COUNTIF('Inputs'!$B$120:$B$133,"✗ Full FNA*")&gt;0,LEFT('Inputs'!$B$117,1)="✗"),"NOT FOR THE CLIENT: this case needs the full FNA (see Checks on Inputs)","")</f>
+        <f>IF(OR(COUNTIF('Inputs'!$B$121:$B$134,"✗ Full FNA*")&gt;0,LEFT('Inputs'!$B$117,1)="✗"),"NOT FOR THE CLIENT: this case needs the full FNA (see Checks on Inputs)","")</f>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -3993,35 +4104,35 @@
     </row>
     <row r="7" ht="58" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="22">
-        <f>IF('Inputs'!$C$15&lt;&gt;"",TRIM('Inputs'!$C$15)&amp;" ","")&amp;"If you died today, winding up your estate would cost about R "&amp;FIXED(('Workings'!$C$48)/1000000,2)&amp;" million"&amp;IF('Workings'!$C$51&gt;0,", and your debts of R "&amp;FIXED(('Workings'!$C$51)/1000000,2)&amp;" million have to be paid too","")&amp;". Your executor would have R "&amp;FIXED(('Workings'!$C$55)/1000000,2)&amp;" million in cash, so "&amp;IF('Workings'!$C$56&gt;0,"would be short by about R "&amp;FIXED(('Workings'!$C$56)/1000000,2)&amp;" million.","would have enough, with about R "&amp;FIXED(ROUND('Workings'!$C$57,-3),0)&amp;" left over.")</f>
+        <f>IF('Inputs'!$C$15&lt;&gt;"",TRIM('Inputs'!$C$15)&amp;" ","")&amp;"If you died today, winding up your estate would cost about R "&amp;FIXED(('Workings'!$C$56)/1000000,2)&amp;" million"&amp;IF('Workings'!$C$59&gt;0,", and your debts of R "&amp;FIXED(('Workings'!$C$59)/1000000,2)&amp;" million have to be paid too","")&amp;". Your executor would have R "&amp;FIXED(('Workings'!$C$63)/1000000,2)&amp;" million in cash, so "&amp;IF('Workings'!$C$64&gt;0,"would be short by about R "&amp;FIXED(('Workings'!$C$64)/1000000,2)&amp;" million.","would have enough, with about R "&amp;FIXED(ROUND('Workings'!$C$65,-3),0)&amp;" left over.")</f>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
     </row>
     <row r="8" ht="44" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="22">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),"With a Capital Legacy will and the Legacy Protection Plan, the plan pays about R "&amp;FIXED(ROUND(-'Workings'!$D$49,-3),0)&amp;" of the executor's and conveyancing fees, "&amp;IF('Workings'!$D$56=0,IF('Workings'!$C$56&gt;0,"the shortfall disappears","your executor still has enough"),"the shortfall falls to about R "&amp;FIXED(ROUND('Workings'!$D$56,-3),0))&amp;", and your heirs receive about R "&amp;FIXED(('Workings'!$D$58-'Workings'!$C$58)/1000000,2)&amp;" million more.","")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),"With a Capital Legacy will and the Legacy Protection Plan, the plan pays about R "&amp;FIXED(ROUND(-'Workings'!$D$57,-3),0)&amp;" of the executor's and conveyancing fees, "&amp;IF('Workings'!$D$64=0,IF('Workings'!$C$64&gt;0,"the shortfall disappears","your executor still has enough"),"the shortfall falls to about R "&amp;FIXED(ROUND('Workings'!$D$64,-3),0))&amp;", and your heirs receive about R "&amp;FIXED(('Workings'!$D$66-'Workings'!$C$66)/1000000,2)&amp;" million more.","")</f>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="23">
-        <f>IF('Workings'!$C$56&gt;0,"YOUR EXECUTOR'S CASH SHORTFALL TODAY","CASH LEFT OVER FOR YOUR EXECUTOR TODAY")</f>
+        <f>IF('Workings'!$C$64&gt;0,"YOUR EXECUTOR'S CASH SHORTFALL TODAY","CASH LEFT OVER FOR YOUR EXECUTOR TODAY")</f>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
     </row>
     <row r="11" ht="28" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="24">
-        <f>"R "&amp;FIXED(ROUND(IF('Workings'!$C$56&gt;0,'Workings'!$C$56,'Workings'!$C$57),-3),0)</f>
+        <f>"R "&amp;FIXED(ROUND(IF('Workings'!$C$64&gt;0,'Workings'!$C$64,'Workings'!$C$65),-3),0)</f>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="24"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="25">
-        <f>IF('Workings'!$C$56&gt;0,"the cash that has to be found before your estate can be wound up","what is left once the costs are paid")</f>
+        <f>IF('Workings'!$C$64&gt;0,"the cash that has to be found before your estate can be wound up","what is left once the costs are paid")</f>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -4042,10 +4153,10 @@
         <v>118</v>
       </c>
       <c r="C15" s="15">
-        <f>'Workings'!$C$47</f>
+        <f>'Workings'!$C$55</f>
       </c>
       <c r="D15" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$47,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$55,"")</f>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
@@ -4053,10 +4164,10 @@
         <v>119</v>
       </c>
       <c r="C16" s="15">
-        <f>'Workings'!$C$46</f>
+        <f>'Workings'!$C$54</f>
       </c>
       <c r="D16" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$46,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$54,"")</f>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -4064,10 +4175,10 @@
         <f>"Executor's fees"&amp;CHAR(10)&amp;IF(ROUND('Inputs'!$C$95,0)='Inputs'!$C$95,FIXED('Inputs'!$C$95,0),IF(ROUND('Inputs'!$C$95,1)='Inputs'!$C$95,FIXED('Inputs'!$C$95,1),FIXED('Inputs'!$C$95,2)))&amp;"%"&amp;" plus VAT"&amp;IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0)," / Capital Legacy "&amp;IF(ROUND('Inputs'!$C$87,0)='Inputs'!$C$87,FIXED('Inputs'!$C$87,0),IF(ROUND('Inputs'!$C$87,1)='Inputs'!$C$87,FIXED('Inputs'!$C$87,1),FIXED('Inputs'!$C$87,2)))&amp;"%"&amp;" plus VAT","")</f>
       </c>
       <c r="C17" s="15">
-        <f>'Workings'!$C$43</f>
+        <f>'Workings'!$C$51</f>
       </c>
       <c r="D17" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$43,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$51,"")</f>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -4075,10 +4186,10 @@
         <f>"Property transfer and conveyancing"&amp;CHAR(10)&amp;IF(ROUND('Inputs'!$C$100,0)='Inputs'!$C$100,FIXED('Inputs'!$C$100,0),IF(ROUND('Inputs'!$C$100,1)='Inputs'!$C$100,FIXED('Inputs'!$C$100,1),FIXED('Inputs'!$C$100,2)))&amp;"%"&amp;" of value"&amp;IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0)," / Capital Legacy's estimate","")</f>
       </c>
       <c r="C18" s="15">
-        <f>'Workings'!$C$44</f>
+        <f>'Workings'!$C$52</f>
       </c>
       <c r="D18" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$44,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$52,"")</f>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
@@ -4086,10 +4197,10 @@
         <v>120</v>
       </c>
       <c r="C19" s="15">
-        <f>'Workings'!$C$45</f>
+        <f>'Workings'!$C$53</f>
       </c>
       <c r="D19" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$45,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$53,"")</f>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
@@ -4097,10 +4208,10 @@
         <v>121</v>
       </c>
       <c r="C20" s="15">
-        <f>'Workings'!$C$42</f>
+        <f>'Workings'!$C$50</f>
       </c>
       <c r="D20" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$42,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$50,"")</f>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
@@ -4108,10 +4219,10 @@
         <v>122</v>
       </c>
       <c r="C21" s="28">
-        <f>'Workings'!$C$48</f>
+        <f>'Workings'!$C$56</f>
       </c>
       <c r="D21" s="28">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$48,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$56,"")</f>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
@@ -4119,10 +4230,10 @@
         <v>123</v>
       </c>
       <c r="C22" s="15">
-        <f>-'Workings'!$C$49</f>
+        <f>-'Workings'!$C$57</f>
       </c>
       <c r="D22" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),-'Workings'!$D$49,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),-'Workings'!$D$57,"")</f>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
@@ -4130,10 +4241,10 @@
         <v>124</v>
       </c>
       <c r="C23" s="28">
-        <f>'Workings'!$C$50</f>
+        <f>'Workings'!$C$58</f>
       </c>
       <c r="D23" s="28">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$50,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$58,"")</f>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
@@ -4141,10 +4252,10 @@
         <v>125</v>
       </c>
       <c r="C24" s="15">
-        <f>'Workings'!$C$51</f>
+        <f>'Workings'!$C$59</f>
       </c>
       <c r="D24" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$51,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$59,"")</f>
       </c>
     </row>
     <row r="25" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -4152,10 +4263,10 @@
         <f>"Cash your executor has"&amp;CHAR(10)&amp;"bank accounts, deposits and investments cashed in"</f>
       </c>
       <c r="C25" s="15">
-        <f>'Workings'!$C$55</f>
+        <f>'Workings'!$C$63</f>
       </c>
       <c r="D25" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$55,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$63,"")</f>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
@@ -4163,10 +4274,10 @@
         <v>126</v>
       </c>
       <c r="C26" s="29">
-        <f>IF('Workings'!$C$56&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$C$56,-3),0),"Covered: R "&amp;FIXED(ROUND('Workings'!$C$57,-3),0)&amp;" left over")</f>
+        <f>IF('Workings'!$C$64&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$C$64,-3),0),"Covered: R "&amp;FIXED(ROUND('Workings'!$C$65,-3),0)&amp;" left over")</f>
       </c>
       <c r="D26" s="29">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),IF('Workings'!$D$56&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$D$56,-3),0),"Covered: R "&amp;FIXED(ROUND('Workings'!$D$57,-3),0)&amp;" left over"),"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),IF('Workings'!$D$64&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$D$64,-3),0),"Covered: R "&amp;FIXED(ROUND('Workings'!$D$65,-3),0)&amp;" left over"),"")</f>
       </c>
     </row>
     <row r="27" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -4174,10 +4285,10 @@
         <f>IF(OR(SUM('Inputs'!$R$22:$R$39)&gt;0,'Inputs'!$C$14="Spouse"),"Left for your spouse and heirs","Left for your heirs")&amp;CHAR(10)&amp;"if they pay any shortfall in"</f>
       </c>
       <c r="C27" s="15">
-        <f>'Workings'!$C$58</f>
+        <f>'Workings'!$C$66</f>
       </c>
       <c r="D27" s="30">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$58,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$66,"")</f>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
@@ -4191,44 +4302,51 @@
         <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),IF(ISNUMBER('Inputs'!$C$91),"From R "&amp;FIXED('Inputs'!$C$91,2)&amp;" a month","Premium: enter it on Inputs"),"")</f>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
+    <row r="29" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="16">
+        <f>IF('Workings'!$C$45&lt;0,"The people you leave policies or bequests to directly pay R "&amp;FIXED(-'Workings'!$C$45,0)&amp;" of the estate duty themselves; your executor recovers it from them and it is not in the cost above. If it cannot be recovered, your estate pays it.","")</f>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="32">
-        <f>"1.  Sign a new will that says what you want"&amp;IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),", with Capital Legacy as your executor","")&amp;". Until you do, your current will, or the law if you have none, decides who inherits."</f>
-      </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
     </row>
     <row r="32" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="32">
-        <f>"2.  "&amp;IF('Workings'!$C$56&gt;0,"Decide how your executor will find the cash: "&amp;IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),"the Legacy Protection Plan, ","")&amp;"a property sold, or your heirs paying it in.","Keep enough cash for your executor: today there is enough, with about R "&amp;FIXED(ROUND('Workings'!$C$57,-3),0)&amp;" to spare.")</f>
+        <f>"1.  Sign a new will that says what you want"&amp;IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),", with Capital Legacy as your executor","")&amp;". Until you do, your current will, or the law if you have none, decides who inherits."</f>
       </c>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
     </row>
     <row r="33" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="32">
-        <f>"3.  Remember that your savings are your executor's cash. Every R 1 spent from them "&amp;IF('Workings'!$C$56&gt;0,"adds about "&amp;ROUND(100*(1-'Inputs'!$C$95/100*(1+'Inputs'!$C$96/100))*IF('Workings'!$C$35&gt;0,1-'Inputs'!$H$96/100,1),0)&amp;" cents to the shortfall.","takes about "&amp;ROUND(100*(1-'Inputs'!$C$95/100*(1+'Inputs'!$C$96/100))*IF('Workings'!$C$35&gt;0,1-'Inputs'!$H$96/100,1),0)&amp;" cents off what your executor has spare.")</f>
+        <f>"2.  "&amp;IF('Workings'!$C$64&gt;0,"Decide how your executor will find the cash: "&amp;IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),"the Legacy Protection Plan, ","")&amp;"a property sold, or your heirs paying it in.","Keep enough cash for your executor: today there is enough, with about R "&amp;FIXED(ROUND('Workings'!$C$65,-3),0)&amp;" to spare.")</f>
       </c>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
     </row>
-    <row r="35" ht="52" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="33">
+    <row r="34" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="32">
+        <f>"3.  Remember that your savings are your executor's cash. Every R 1 spent from them "&amp;IF('Workings'!$C$64&gt;0,"adds about "&amp;ROUND(100*(1-'Inputs'!$C$95/100*(1+'Inputs'!$C$96/100))*IF('Workings'!$C$35&gt;0,1-'Inputs'!$H$96/100,1),0)&amp;" cents to the shortfall.","takes about "&amp;ROUND(100*(1-'Inputs'!$C$95/100*(1+'Inputs'!$C$96/100))*IF('Workings'!$C$35&gt;0,1-'Inputs'!$H$96/100,1),0)&amp;" cents off what your executor has spare.")</f>
+      </c>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+    </row>
+    <row r="36" ht="52" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="33">
         <f>"Basis: indicative and worst case, based on your instructed wishes, not a signed will, and on the values you gave us"&amp;IF(ISNUMBER('Inputs'!$C$12)," on "&amp;FIXED(DAY('Inputs'!$C$12),0)&amp;" "&amp;CHOOSE(MONTH('Inputs'!$C$12),"January","February","March","April","May","June","July","August","September","October","November","December")&amp;" "&amp;FIXED(YEAR('Inputs'!$C$12),0,TRUE),"")&amp;". Our standard assumptions are on the Workings page."&amp;IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0)," Capital Legacy quote "&amp;'Inputs'!$C$86&amp;"; premiums rise each year and are not guaranteed.","")&amp;" Figures are for your death today. Not legal or tax advice; the executor's actual costs may differ."</f>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
@@ -4237,14 +4355,15 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B36:D36"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:D12">
     <cfRule type="expression" dxfId="16" priority="1">
-      <formula>'Workings'!$C$56=0</formula>
+      <formula>'Workings'!$C$64=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:D26">
@@ -4470,10 +4589,10 @@
         <v>147</v>
       </c>
       <c r="C23" s="15">
-        <f>'Workings'!$C$51</f>
+        <f>'Workings'!$C$59</f>
       </c>
       <c r="D23" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$C$51,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$C$59,"")</f>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
@@ -4488,10 +4607,10 @@
         <v>149</v>
       </c>
       <c r="C25" s="15">
-        <f>'Workings'!$C$43</f>
+        <f>'Workings'!$C$51</f>
       </c>
       <c r="D25" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$43,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$51,"")</f>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
@@ -4499,10 +4618,10 @@
         <v>150</v>
       </c>
       <c r="C26" s="15">
-        <f>'Workings'!$C$42</f>
+        <f>'Workings'!$C$50</f>
       </c>
       <c r="D26" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$42,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$50,"")</f>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
@@ -4510,10 +4629,10 @@
         <v>151</v>
       </c>
       <c r="C27" s="15">
-        <f>'Workings'!$C$44</f>
+        <f>'Workings'!$C$52</f>
       </c>
       <c r="D27" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$44,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$52,"")</f>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
@@ -4521,10 +4640,10 @@
         <v>152</v>
       </c>
       <c r="C28" s="15">
-        <f>'Workings'!$C$45</f>
+        <f>'Workings'!$C$53</f>
       </c>
       <c r="D28" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$45,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$53,"")</f>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
@@ -4532,10 +4651,10 @@
         <v>119</v>
       </c>
       <c r="C29" s="15">
-        <f>'Workings'!$C$46</f>
+        <f>'Workings'!$C$54</f>
       </c>
       <c r="D29" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$46,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$54,"")</f>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
@@ -4543,10 +4662,10 @@
         <v>153</v>
       </c>
       <c r="C30" s="15">
-        <f>'Workings'!$C$47</f>
+        <f>'Workings'!$C$55</f>
       </c>
       <c r="D30" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$47,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$55,"")</f>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
@@ -4554,10 +4673,10 @@
         <v>154</v>
       </c>
       <c r="C31" s="28">
-        <f>'Workings'!$C$48</f>
+        <f>'Workings'!$C$56</f>
       </c>
       <c r="D31" s="28">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$48,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$56,"")</f>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
@@ -4565,10 +4684,10 @@
         <v>123</v>
       </c>
       <c r="C32" s="15">
-        <f>-'Workings'!$C$49</f>
+        <f>-'Workings'!$C$57</f>
       </c>
       <c r="D32" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),-'Workings'!$D$49,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),-'Workings'!$D$57,"")</f>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
@@ -4576,10 +4695,10 @@
         <v>155</v>
       </c>
       <c r="C33" s="15">
-        <f>'Workings'!$C$51</f>
+        <f>'Workings'!$C$59</f>
       </c>
       <c r="D33" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$51,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),'Workings'!$D$59,"")</f>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -4614,7 +4733,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D60"/>
+  <dimension ref="B1:D68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -4977,239 +5096,315 @@
         <f>IF(D33&gt;0,D36/D33,0)</f>
       </c>
     </row>
-    <row r="38" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" ht="27" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="35">
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="7">
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
+      </c>
+      <c r="C39" s="35">
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(1,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(1,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+      <c r="D39" s="35">
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(1,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(1,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="7">
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
+      </c>
+      <c r="C40" s="35">
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(2,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(2,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+      <c r="D40" s="35">
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(2,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(2,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="7">
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
+      </c>
+      <c r="C41" s="35">
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(3,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(3,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+      <c r="D41" s="35">
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(3,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(3,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="7">
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
+      </c>
+      <c r="C42" s="35">
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(4,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(4,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+      <c r="D42" s="35">
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(4,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(4,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="7">
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
+      </c>
+      <c r="C43" s="35">
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(5,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(5,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+      <c r="D43" s="35">
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(5,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(5,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="7">
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(6,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(6,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(6,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(6,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(6,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(6,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
+      </c>
+      <c r="C44" s="35">
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(6,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(6,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+      <c r="D44" s="35">
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(6,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(6,'Inputs'!$O$59:$O$70,0)),""))</f>
+      </c>
+    </row>
+    <row r="45" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C45" s="35">
         <f>-(SUM('Inputs'!$M$59:$M$70)+SUM('Inputs'!$U$22:$U$39))</f>
       </c>
-      <c r="D38" s="35">
+      <c r="D45" s="35">
         <f>-(SUM('Inputs'!$N$59:$N$70)+SUM('Inputs'!$V$22:$V$39))</f>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="27" t="s">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="C39" s="36">
-        <f>C36+C38</f>
-      </c>
-      <c r="D39" s="36">
-        <f>D36+D38</f>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C41" s="13" t="s">
+      <c r="C46" s="36">
+        <f>C36+C45</f>
+      </c>
+      <c r="D46" s="36">
+        <f>D36+D45</f>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D49" s="13" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="7" t="s">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C42" s="35">
+      <c r="C50" s="35">
         <f>-(C25+C26+C27)</f>
       </c>
-      <c r="D42" s="35">
+      <c r="D50" s="35">
         <f>-(D25+D26+D27)</f>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" s="35">
-        <f>-C28</f>
-      </c>
-      <c r="D43" s="35">
-        <f>-D28</f>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C44" s="35">
-        <f>-C29</f>
-      </c>
-      <c r="D44" s="35">
-        <f>-D29</f>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C45" s="35">
-        <f>-C30</f>
-      </c>
-      <c r="D45" s="35">
-        <f>-D30</f>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C46" s="35">
-        <f>C16</f>
-      </c>
-      <c r="D46" s="35">
-        <f>D16</f>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C47" s="35">
-        <f>C39</f>
-      </c>
-      <c r="D47" s="35">
-        <f>D39</f>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C48" s="36">
-        <f>ROUND(SUM(C42:C47),2)</f>
-      </c>
-      <c r="D48" s="36">
-        <f>ROUND(SUM(D42:D47),2)</f>
-      </c>
-    </row>
-    <row r="49" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B49" s="7">
-        <f>"Less paid by the Legacy plan: "&amp;IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),FIXED(N('Inputs'!$C$89),0)&amp;"% of the executor's fee and conveyancing, up to R "&amp;FIXED(N('Inputs'!$C$90),2),"no quote entered")</f>
-      </c>
-      <c r="C49" s="35">
-        <f>0</f>
-      </c>
-      <c r="D49" s="35">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),-ROUND(MIN(N('Inputs'!$C$89)/100*(D43+D44),N('Inputs'!$C$90)),2),0)</f>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B50" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="C50" s="36">
-        <f>ROUND(C48+C49,2)</f>
-      </c>
-      <c r="D50" s="36">
-        <f>ROUND(D48+D49,2)</f>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="7" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="C51" s="35">
-        <f>-C24</f>
+        <f>-C28</f>
       </c>
       <c r="D51" s="35">
-        <f>-D24</f>
+        <f>-D28</f>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="C52" s="36">
-        <f>ROUND(C50+C51,2)</f>
-      </c>
-      <c r="D52" s="36">
-        <f>ROUND(D50+D51,2)</f>
+      <c r="C52" s="35">
+        <f>-C29</f>
+      </c>
+      <c r="D52" s="35">
+        <f>-D29</f>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="7" t="s">
-        <v>191</v>
+        <v>120</v>
       </c>
       <c r="C53" s="35">
-        <f>ROUND(SUM('Inputs'!$O$22:$O$39),2)</f>
+        <f>-C30</f>
       </c>
       <c r="D53" s="35">
-        <f>ROUND(SUM('Inputs'!$O$22:$O$39),2)</f>
+        <f>-D30</f>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C54" s="35">
-        <f>C20</f>
+        <f>C16</f>
       </c>
       <c r="D54" s="35">
-        <f>D20</f>
+        <f>D16</f>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="C55" s="36">
-        <f>C53+C54</f>
-      </c>
-      <c r="D55" s="36">
-        <f>D53+D54</f>
+      <c r="B55" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C55" s="35">
+        <f>C46</f>
+      </c>
+      <c r="D55" s="35">
+        <f>D46</f>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C56" s="36">
+        <f>ROUND(SUM(C50:C55),2)</f>
+      </c>
+      <c r="D56" s="36">
+        <f>ROUND(SUM(D50:D55),2)</f>
+      </c>
+    </row>
+    <row r="57" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="7">
+        <f>"Less paid by the Legacy plan: "&amp;IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),FIXED(N('Inputs'!$C$89),0)&amp;"% of the executor's fee and conveyancing, up to R "&amp;FIXED(N('Inputs'!$C$90),2),"no quote entered")</f>
+      </c>
+      <c r="C57" s="35">
+        <f>0</f>
+      </c>
+      <c r="D57" s="35">
+        <f>IF(AND(ISNUMBER('Inputs'!$C$87),'Inputs'!$C$87&gt;0),-ROUND(MIN(N('Inputs'!$C$89)/100*(D51+D52),N('Inputs'!$C$90)),2),0)</f>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B58" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C58" s="36">
+        <f>ROUND(C56+C57,2)</f>
+      </c>
+      <c r="D58" s="36">
+        <f>ROUND(D56+D57,2)</f>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B59" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" s="35">
+        <f>-C24</f>
+      </c>
+      <c r="D59" s="35">
+        <f>-D24</f>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B60" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" s="36">
+        <f>ROUND(C58+C59,2)</f>
+      </c>
+      <c r="D60" s="36">
+        <f>ROUND(D58+D59,2)</f>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B61" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C56" s="36">
-        <f>ROUND(MAX(0,C52-C55),2)</f>
-      </c>
-      <c r="D56" s="36">
-        <f>ROUND(MAX(0,D52-D55),2)</f>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B57" s="7" t="s">
+      <c r="C61" s="35">
+        <f>ROUND(SUM('Inputs'!$O$22:$O$39),2)</f>
+      </c>
+      <c r="D61" s="35">
+        <f>ROUND(SUM('Inputs'!$O$22:$O$39),2)</f>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B62" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C62" s="35">
+        <f>C20</f>
+      </c>
+      <c r="D62" s="35">
+        <f>D20</f>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B63" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="C57" s="35">
-        <f>ROUND(MAX(0,C55-C52),2)</f>
-      </c>
-      <c r="D57" s="35">
-        <f>ROUND(MAX(0,D55-D52),2)</f>
-      </c>
-    </row>
-    <row r="58" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B58" s="27" t="s">
+      <c r="C63" s="36">
+        <f>C61+C62</f>
+      </c>
+      <c r="D63" s="36">
+        <f>D61+D62</f>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B64" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="C58" s="36">
-        <f>ROUND(C21-C52,2)</f>
-      </c>
-      <c r="D58" s="36">
-        <f>ROUND(D21-D52,2)</f>
-      </c>
-    </row>
-    <row r="60" ht="52" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B60" s="33">
+      <c r="C64" s="36">
+        <f>ROUND(MAX(0,C60-C63),2)</f>
+      </c>
+      <c r="D64" s="36">
+        <f>ROUND(MAX(0,D60-D63),2)</f>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C65" s="35">
+        <f>ROUND(MAX(0,C63-C60),2)</f>
+      </c>
+      <c r="D65" s="35">
+        <f>ROUND(MAX(0,D63-D60),2)</f>
+      </c>
+    </row>
+    <row r="66" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" s="36">
+        <f>ROUND(C21-C60,2)</f>
+      </c>
+      <c r="D66" s="36">
+        <f>ROUND(D21-D60,2)</f>
+      </c>
+    </row>
+    <row r="68" ht="52" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B68" s="33">
         <f>"Our standard assumptions: executor "&amp;IF(ROUND('Inputs'!$C$95,0)='Inputs'!$C$95,FIXED('Inputs'!$C$95,0),IF(ROUND('Inputs'!$C$95,1)='Inputs'!$C$95,FIXED('Inputs'!$C$95,1),FIXED('Inputs'!$C$95,2)))&amp;"%"&amp;" plus VAT unless Capital Legacy acts; Master's fees R "&amp;FIXED('Inputs'!$C$97,0)&amp;"; funeral R "&amp;FIXED('Inputs'!$C$98,0)&amp;"; sundries R "&amp;FIXED('Inputs'!$C$99,0)&amp;"; property transfer costs "&amp;IF(ROUND('Inputs'!$C$100,0)='Inputs'!$C$100,FIXED('Inputs'!$C$100,0),IF(ROUND('Inputs'!$C$100,1)='Inputs'!$C$100,FIXED('Inputs'!$C$100,1),FIXED('Inputs'!$C$100,2)))&amp;"%"&amp;" of value; agent's commission "&amp;IF(ROUND('Inputs'!$C$101,0)='Inputs'!$C$101,FIXED('Inputs'!$C$101,0),IF(ROUND('Inputs'!$C$101,1)='Inputs'!$C$101,FIXED('Inputs'!$C$101,1),FIXED('Inputs'!$C$101,2)))&amp;"%"&amp;" plus VAT on a property sold; estate duty "&amp;IF(ROUND('Inputs'!$H$96,0)='Inputs'!$H$96,FIXED('Inputs'!$H$96,0),IF(ROUND('Inputs'!$H$96,1)='Inputs'!$H$96,FIXED('Inputs'!$H$96,1),FIXED('Inputs'!$H$96,2)))&amp;"%"&amp;" above R "&amp;FIXED('Inputs'!$H$95,0)&amp;"; 2027 tax tables. Capital gains tax on death (s.9HA): everything treated as sold at its value; assets left to a spouse roll over (no tax now). The Capital Legacy fees stay deductible for estate duty, although the plan pays them."</f>
       </c>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
+      <c r="C68" s="33"/>
+      <c r="D68" s="33"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
   <mergeCells count="3">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B68:D68"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.25" footer="0.3"/>

--- a/Duwalcoe_Quick_FNA_Template.xlsx
+++ b/Duwalcoe_Quick_FNA_Template.xlsx
@@ -1498,7 +1498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
@@ -1589,7 +1589,7 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1607,6 +1607,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5933,7 +5936,7 @@
         <f>IF(AND(ISNUMBER('Inputs'!$C$101),'Inputs'!$C$101&gt;0),'Workings'!$D$65,"")</f>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="20" t="s">
         <v>173</v>
       </c>
@@ -6040,7 +6043,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.25" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Cost of dying&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
   </headerFooter>
@@ -6096,11 +6099,11 @@
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
@@ -6180,11 +6183,11 @@
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
@@ -6220,11 +6223,11 @@
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
@@ -6260,11 +6263,11 @@
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
@@ -6385,7 +6388,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.25" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Figures for quoting&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
   </headerFooter>
@@ -6445,10 +6448,10 @@
       <c r="B8" s="7">
         <f>"Taxable income for the year"&amp;IF('Inputs'!$C$17&lt;&gt;"",": "&amp;'Inputs'!$C$17,"")</f>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="42">
         <f>N('Inputs'!$C$16)</f>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="42">
         <f>N('Inputs'!$C$16)</f>
       </c>
     </row>
@@ -6456,10 +6459,10 @@
       <c r="B9" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="42">
         <f>SUM('Inputs'!$M$22:$M$39)</f>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="42">
         <f>SUM('Inputs'!$M$22:$M$39)</f>
       </c>
     </row>
@@ -6467,10 +6470,10 @@
       <c r="B10" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="42">
         <f>-SUM('Inputs'!$N$22:$N$39)</f>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="42">
         <f>-SUM('Inputs'!$N$22:$N$39)</f>
       </c>
     </row>
@@ -6478,10 +6481,10 @@
       <c r="B11" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="42">
         <f>-MIN('Inputs'!$C$120,MAX(0,C9+C10))</f>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="42">
         <f>-MIN('Inputs'!$C$120,MAX(0,D9+D10))</f>
       </c>
     </row>
@@ -6489,10 +6492,10 @@
       <c r="B12" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="43">
         <f>MAX(0,C9+C10+C11)</f>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="43">
         <f>MAX(0,D9+D10+D11)</f>
       </c>
     </row>
@@ -6500,10 +6503,10 @@
       <c r="B13" s="7">
         <f>"Added to taxable income: "&amp;FIXED('Inputs'!$H$109,0)&amp;"% of the net gain (the inclusion rate, not a tax rate)"</f>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="42">
         <f>C12*'Inputs'!$H$109/100</f>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="42">
         <f>D12*'Inputs'!$H$109/100</f>
       </c>
     </row>
@@ -6511,10 +6514,10 @@
       <c r="B14" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="42">
         <f>(INDEX('Inputs'!$D$123:$D$129,MATCH(C8+C13,'Inputs'!$C$123:$C$129,1))+INDEX('Inputs'!$E$123:$E$129,MATCH(C8+C13,'Inputs'!$C$123:$C$129,1))/100*((C8+C13)-INDEX('Inputs'!$C$123:$C$129,MATCH(C8+C13,'Inputs'!$C$123:$C$129,1))))</f>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="42">
         <f>(INDEX('Inputs'!$D$123:$D$129,MATCH(D8+D13,'Inputs'!$C$123:$C$129,1))+INDEX('Inputs'!$E$123:$E$129,MATCH(D8+D13,'Inputs'!$C$123:$C$129,1))/100*((D8+D13)-INDEX('Inputs'!$C$123:$C$129,MATCH(D8+D13,'Inputs'!$C$123:$C$129,1))))</f>
       </c>
     </row>
@@ -6522,10 +6525,10 @@
       <c r="B15" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="42">
         <f>-(INDEX('Inputs'!$D$123:$D$129,MATCH(C8,'Inputs'!$C$123:$C$129,1))+INDEX('Inputs'!$E$123:$E$129,MATCH(C8,'Inputs'!$C$123:$C$129,1))/100*((C8)-INDEX('Inputs'!$C$123:$C$129,MATCH(C8,'Inputs'!$C$123:$C$129,1))))</f>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="42">
         <f>-(INDEX('Inputs'!$D$123:$D$129,MATCH(D8,'Inputs'!$C$123:$C$129,1))+INDEX('Inputs'!$E$123:$E$129,MATCH(D8,'Inputs'!$C$123:$C$129,1))/100*((D8)-INDEX('Inputs'!$C$123:$C$129,MATCH(D8,'Inputs'!$C$123:$C$129,1))))</f>
       </c>
     </row>
@@ -6533,10 +6536,10 @@
       <c r="B16" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="43">
         <f>IF(C12&gt;0,ROUND(C14+C15,2),0)</f>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="43">
         <f>IF(D12&gt;0,ROUND(D14+D15,2),0)</f>
       </c>
     </row>
@@ -6555,10 +6558,10 @@
       <c r="B19" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="42">
         <f>ROUND(SUM('Inputs'!$D$22:$D$39),2)</f>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="42">
         <f>ROUND(SUM('Inputs'!$D$22:$D$39),2)</f>
       </c>
     </row>
@@ -6566,10 +6569,10 @@
       <c r="B20" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C20" s="41">
+      <c r="C20" s="42">
         <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Estate")</f>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="42">
         <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Estate")</f>
       </c>
     </row>
@@ -6577,10 +6580,10 @@
       <c r="B21" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="43">
         <f>C19+C20</f>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="43">
         <f>D19+D20</f>
       </c>
     </row>
@@ -6588,10 +6591,10 @@
       <c r="B22" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="C22" s="41">
+      <c r="C22" s="42">
         <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"&lt;&gt;Estate",'Inputs'!$E$59:$E$70,"&lt;&gt;No")</f>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="42">
         <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"&lt;&gt;Estate",'Inputs'!$E$59:$E$70,"&lt;&gt;No")</f>
       </c>
     </row>
@@ -6599,10 +6602,10 @@
       <c r="B23" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="43">
         <f>C21+C22</f>
       </c>
-      <c r="D23" s="42">
+      <c r="D23" s="43">
         <f>D21+D22</f>
       </c>
     </row>
@@ -6610,10 +6613,10 @@
       <c r="B24" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="41">
+      <c r="C24" s="42">
         <f>-SUM('Inputs'!$D$45:$D$54)</f>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="42">
         <f>-SUM('Inputs'!$D$45:$D$54)</f>
       </c>
     </row>
@@ -6621,10 +6624,10 @@
       <c r="B25" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C25" s="41">
+      <c r="C25" s="42">
         <f>-'Inputs'!$C$112</f>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="42">
         <f>-'Inputs'!$C$112</f>
       </c>
     </row>
@@ -6632,10 +6635,10 @@
       <c r="B26" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="42">
         <f>-'Inputs'!$C$111</f>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="42">
         <f>-'Inputs'!$C$111</f>
       </c>
     </row>
@@ -6643,10 +6646,10 @@
       <c r="B27" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="42">
         <f>-'Inputs'!$C$113</f>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="42">
         <f>-'Inputs'!$C$113</f>
       </c>
     </row>
@@ -6654,10 +6657,10 @@
       <c r="B28" s="7">
         <f>"Less executor's fees: "&amp;IF(ROUND('Inputs'!$C$109,0)='Inputs'!$C$109,FIXED('Inputs'!$C$109,0),IF(ROUND('Inputs'!$C$109,1)='Inputs'!$C$109,FIXED('Inputs'!$C$109,1),FIXED('Inputs'!$C$109,2)))&amp;"%"&amp;" plus VAT"&amp;IF(AND(ISNUMBER('Inputs'!$C$101),'Inputs'!$C$101&gt;0)," / Capital Legacy "&amp;IF(ROUND('Inputs'!$C$101,0)='Inputs'!$C$101,FIXED('Inputs'!$C$101,0),IF(ROUND('Inputs'!$C$101,1)='Inputs'!$C$101,FIXED('Inputs'!$C$101,1),FIXED('Inputs'!$C$101,2)))&amp;"%"&amp;" plus VAT","")</f>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="42">
         <f>-ROUND('Inputs'!$C$109/100*(1+'Inputs'!$C$110/100)*C21,2)</f>
       </c>
-      <c r="D28" s="41">
+      <c r="D28" s="42">
         <f>-ROUND(IF(AND(ISNUMBER('Inputs'!$C$101),'Inputs'!$C$101&gt;0),'Inputs'!$C$101,'Inputs'!$C$109)/100*(1+'Inputs'!$C$110/100)*D21,2)</f>
       </c>
     </row>
@@ -6665,10 +6668,10 @@
       <c r="B29" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="42">
         <f>-SUM('Inputs'!$P$22:$P$39)</f>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="42">
         <f>-IF(AND(AND(ISNUMBER('Inputs'!$C$101),'Inputs'!$C$101&gt;0),ISNUMBER('Inputs'!$C$102)),'Inputs'!$C$102,SUM('Inputs'!$P$22:$P$39))</f>
       </c>
     </row>
@@ -6676,10 +6679,10 @@
       <c r="B30" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C30" s="41">
+      <c r="C30" s="42">
         <f>-SUM('Inputs'!$Q$22:$Q$39)</f>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="42">
         <f>-SUM('Inputs'!$Q$22:$Q$39)</f>
       </c>
     </row>
@@ -6687,10 +6690,10 @@
       <c r="B31" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="C31" s="41">
+      <c r="C31" s="42">
         <f>-C16</f>
       </c>
-      <c r="D31" s="41">
+      <c r="D31" s="42">
         <f>-D16</f>
       </c>
     </row>
@@ -6698,10 +6701,10 @@
       <c r="B32" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C32" s="41">
+      <c r="C32" s="42">
         <f>ROUND(C21+C24-(-C25-C26-C27-C28-C29-C30-C31)-SUM('Inputs'!$R$22:$R$39)-SUM('Inputs'!$S$22:$S$39),2)</f>
       </c>
-      <c r="D32" s="41">
+      <c r="D32" s="42">
         <f>ROUND(D21+D24-(-D25-D26-D27-D28-D29-D30-D31)-SUM('Inputs'!$R$22:$R$39)-SUM('Inputs'!$S$22:$S$39),2)</f>
       </c>
     </row>
@@ -6709,10 +6712,10 @@
       <c r="B33" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="C33" s="43">
+      <c r="C33" s="44">
         <f>IF(C32&lt;0,IF(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39)&gt;0,MAX(0,1+C32/(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39))),1),1)</f>
       </c>
-      <c r="D33" s="43">
+      <c r="D33" s="44">
         <f>IF(D32&lt;0,IF(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39)&gt;0,MAX(0,1+D32/(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39))),1),1)</f>
       </c>
     </row>
@@ -6720,10 +6723,10 @@
       <c r="B34" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C34" s="41">
+      <c r="C34" s="42">
         <f>-(SUM('Inputs'!$R$22:$R$39)*C33+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+IF('Inputs'!$C$14="Spouse",MAX(0,C32),0))</f>
       </c>
-      <c r="D34" s="41">
+      <c r="D34" s="42">
         <f>-(SUM('Inputs'!$R$22:$R$39)*D33+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+IF('Inputs'!$C$14="Spouse",MAX(0,D32),0))</f>
       </c>
     </row>
@@ -6731,10 +6734,10 @@
       <c r="B35" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="43">
         <f>ROUND(C23+C24+C25+C26+C27+C28+C29+C30+C31+C34,2)</f>
       </c>
-      <c r="D35" s="42">
+      <c r="D35" s="43">
         <f>ROUND(D23+D24+D25+D26+D27+D28+D29+D30+D31+D34,2)</f>
       </c>
     </row>
@@ -6742,10 +6745,10 @@
       <c r="B36" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C36" s="41">
+      <c r="C36" s="42">
         <f>-'Inputs'!$C$116</f>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="42">
         <f>-'Inputs'!$C$116</f>
       </c>
     </row>
@@ -6753,10 +6756,10 @@
       <c r="B37" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C37" s="41">
+      <c r="C37" s="42">
         <f>MAX(0,C35+C36)</f>
       </c>
-      <c r="D37" s="41">
+      <c r="D37" s="42">
         <f>MAX(0,D35+D36)</f>
       </c>
     </row>
@@ -6764,10 +6767,10 @@
       <c r="B38" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="C38" s="42">
+      <c r="C38" s="43">
         <f>ROUND(IF(C37&lt;='Inputs'!$C$118,C37*'Inputs'!$C$117/100,'Inputs'!$C$118*'Inputs'!$C$117/100+(C37-'Inputs'!$C$118)*'Inputs'!$C$119/100),2)</f>
       </c>
-      <c r="D38" s="42">
+      <c r="D38" s="43">
         <f>ROUND(IF(D37&lt;='Inputs'!$C$118,D37*'Inputs'!$C$117/100,'Inputs'!$C$118*'Inputs'!$C$117/100+(D37-'Inputs'!$C$118)*'Inputs'!$C$119/100),2)</f>
       </c>
     </row>
@@ -6775,10 +6778,10 @@
       <c r="B39" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C39" s="44">
+      <c r="C39" s="45">
         <f>IF(C35&gt;0,C38/C35,0)</f>
       </c>
-      <c r="D39" s="44">
+      <c r="D39" s="45">
         <f>IF(D35&gt;0,D38/D35,0)</f>
       </c>
     </row>
@@ -6791,10 +6794,10 @@
       <c r="B41" s="7">
         <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
       </c>
-      <c r="C41" s="41">
+      <c r="C41" s="42">
         <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(1,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(1,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
-      <c r="D41" s="41">
+      <c r="D41" s="42">
         <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(1,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(1,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
     </row>
@@ -6802,10 +6805,10 @@
       <c r="B42" s="7">
         <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
       </c>
-      <c r="C42" s="41">
+      <c r="C42" s="42">
         <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(2,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(2,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
-      <c r="D42" s="41">
+      <c r="D42" s="42">
         <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(2,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(2,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
     </row>
@@ -6813,10 +6816,10 @@
       <c r="B43" s="7">
         <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
       </c>
-      <c r="C43" s="41">
+      <c r="C43" s="42">
         <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(3,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(3,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
-      <c r="D43" s="41">
+      <c r="D43" s="42">
         <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(3,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(3,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
     </row>
@@ -6824,10 +6827,10 @@
       <c r="B44" s="7">
         <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
       </c>
-      <c r="C44" s="41">
+      <c r="C44" s="42">
         <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(4,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(4,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
-      <c r="D44" s="41">
+      <c r="D44" s="42">
         <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(4,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(4,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
     </row>
@@ -6835,10 +6838,10 @@
       <c r="B45" s="7">
         <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
       </c>
-      <c r="C45" s="41">
+      <c r="C45" s="42">
         <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(5,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(5,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
-      <c r="D45" s="41">
+      <c r="D45" s="42">
         <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(5,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(5,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
     </row>
@@ -6846,10 +6849,10 @@
       <c r="B46" s="7">
         <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(6,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(6,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(6,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(6,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(6,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(6,'Inputs'!$O$59:$O$70,0))&amp;")",""),""))</f>
       </c>
-      <c r="C46" s="41">
+      <c r="C46" s="42">
         <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(6,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(6,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
-      <c r="D46" s="41">
+      <c r="D46" s="42">
         <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(6,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(6,'Inputs'!$O$59:$O$70,0)),""))</f>
       </c>
     </row>
@@ -6857,10 +6860,10 @@
       <c r="B47" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="C47" s="41">
+      <c r="C47" s="42">
         <f>-(SUM('Inputs'!$M$59:$M$70)+SUM('Inputs'!$U$22:$U$39))</f>
       </c>
-      <c r="D47" s="41">
+      <c r="D47" s="42">
         <f>-(SUM('Inputs'!$N$59:$N$70)+SUM('Inputs'!$V$22:$V$39))</f>
       </c>
     </row>
@@ -6868,10 +6871,10 @@
       <c r="B48" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="C48" s="42">
+      <c r="C48" s="43">
         <f>C38+C47</f>
       </c>
-      <c r="D48" s="42">
+      <c r="D48" s="43">
         <f>D38+D47</f>
       </c>
     </row>
@@ -6895,10 +6898,10 @@
       <c r="B52" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C52" s="41">
+      <c r="C52" s="42">
         <f>-(C25+C26+C27)</f>
       </c>
-      <c r="D52" s="41">
+      <c r="D52" s="42">
         <f>-(D25+D26+D27)</f>
       </c>
     </row>
@@ -6906,10 +6909,10 @@
       <c r="B53" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="C53" s="41">
+      <c r="C53" s="42">
         <f>-C28</f>
       </c>
-      <c r="D53" s="41">
+      <c r="D53" s="42">
         <f>-D28</f>
       </c>
     </row>
@@ -6917,10 +6920,10 @@
       <c r="B54" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="C54" s="41">
+      <c r="C54" s="42">
         <f>-C29</f>
       </c>
-      <c r="D54" s="41">
+      <c r="D54" s="42">
         <f>-D29</f>
       </c>
     </row>
@@ -6928,10 +6931,10 @@
       <c r="B55" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C55" s="41">
+      <c r="C55" s="42">
         <f>-C30</f>
       </c>
-      <c r="D55" s="41">
+      <c r="D55" s="42">
         <f>-D30</f>
       </c>
     </row>
@@ -6939,10 +6942,10 @@
       <c r="B56" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="C56" s="41">
+      <c r="C56" s="42">
         <f>C16</f>
       </c>
-      <c r="D56" s="41">
+      <c r="D56" s="42">
         <f>D16</f>
       </c>
     </row>
@@ -6950,10 +6953,10 @@
       <c r="B57" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C57" s="41">
+      <c r="C57" s="42">
         <f>C48</f>
       </c>
-      <c r="D57" s="41">
+      <c r="D57" s="42">
         <f>D48</f>
       </c>
     </row>
@@ -6961,10 +6964,10 @@
       <c r="B58" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="C58" s="42">
+      <c r="C58" s="43">
         <f>ROUND(SUM(C52:C57),2)</f>
       </c>
-      <c r="D58" s="42">
+      <c r="D58" s="43">
         <f>ROUND(SUM(D52:D57),2)</f>
       </c>
     </row>
@@ -6972,10 +6975,10 @@
       <c r="B59" s="7">
         <f>"Less paid by the Legacy plan: "&amp;IF(AND(ISNUMBER('Inputs'!$C$101),'Inputs'!$C$101&gt;0),FIXED(N('Inputs'!$C$103),0)&amp;"% of the executor's fee and conveyancing, up to R "&amp;FIXED(N('Inputs'!$C$104),2),"no quote entered")</f>
       </c>
-      <c r="C59" s="41">
+      <c r="C59" s="42">
         <f>0</f>
       </c>
-      <c r="D59" s="41">
+      <c r="D59" s="42">
         <f>IF(AND(ISNUMBER('Inputs'!$C$101),'Inputs'!$C$101&gt;0),-ROUND(MIN(N('Inputs'!$C$103)/100*(D53+D54),N('Inputs'!$C$104)),2),0)</f>
       </c>
     </row>
@@ -6983,10 +6986,10 @@
       <c r="B60" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="C60" s="42">
+      <c r="C60" s="43">
         <f>ROUND(C58+C59,2)</f>
       </c>
-      <c r="D60" s="42">
+      <c r="D60" s="43">
         <f>ROUND(D58+D59,2)</f>
       </c>
     </row>
@@ -6994,10 +6997,10 @@
       <c r="B61" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C61" s="41">
+      <c r="C61" s="42">
         <f>-C24</f>
       </c>
-      <c r="D61" s="41">
+      <c r="D61" s="42">
         <f>-D24</f>
       </c>
     </row>
@@ -7005,10 +7008,10 @@
       <c r="B62" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="C62" s="42">
+      <c r="C62" s="43">
         <f>ROUND(C60+C61,2)</f>
       </c>
-      <c r="D62" s="42">
+      <c r="D62" s="43">
         <f>ROUND(D60+D61,2)</f>
       </c>
     </row>
@@ -7016,10 +7019,10 @@
       <c r="B63" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C63" s="41">
+      <c r="C63" s="42">
         <f>ROUND(SUM('Inputs'!$O$22:$O$39),2)</f>
       </c>
-      <c r="D63" s="41">
+      <c r="D63" s="42">
         <f>ROUND(SUM('Inputs'!$O$22:$O$39),2)</f>
       </c>
     </row>
@@ -7027,10 +7030,10 @@
       <c r="B64" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C64" s="41">
+      <c r="C64" s="42">
         <f>C20</f>
       </c>
-      <c r="D64" s="41">
+      <c r="D64" s="42">
         <f>D20</f>
       </c>
     </row>
@@ -7038,10 +7041,10 @@
       <c r="B65" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="C65" s="42">
+      <c r="C65" s="43">
         <f>C63+C64</f>
       </c>
-      <c r="D65" s="42">
+      <c r="D65" s="43">
         <f>D63+D64</f>
       </c>
     </row>
@@ -7049,10 +7052,10 @@
       <c r="B66" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="C66" s="42">
+      <c r="C66" s="43">
         <f>ROUND(MAX(0,C62-C65),2)</f>
       </c>
-      <c r="D66" s="42">
+      <c r="D66" s="43">
         <f>ROUND(MAX(0,D62-D65),2)</f>
       </c>
     </row>
@@ -7060,10 +7063,10 @@
       <c r="B67" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="C67" s="41">
+      <c r="C67" s="42">
         <f>ROUND(MAX(0,C65-C62),2)</f>
       </c>
-      <c r="D67" s="41">
+      <c r="D67" s="42">
         <f>ROUND(MAX(0,D65-D62),2)</f>
       </c>
     </row>
@@ -7071,10 +7074,10 @@
       <c r="B68" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="C68" s="42">
+      <c r="C68" s="43">
         <f>ROUND(C21-C62,2)</f>
       </c>
-      <c r="D68" s="42">
+      <c r="D68" s="43">
         <f>ROUND(D21-D62,2)</f>
       </c>
     </row>
@@ -16753,22 +16756,22 @@
       <c r="B8" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="42">
         <f>IF('Inputs'!$B$89="","",N('Inputs'!$E$89))</f>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="42">
         <f>IF('Inputs'!$B$90="","",N('Inputs'!$E$90))</f>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="42">
         <f>IF('Inputs'!$B$91="","",N('Inputs'!$E$91))</f>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="42">
         <f>IF('Inputs'!$B$92="","",N('Inputs'!$E$92))</f>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="42">
         <f>IF('Inputs'!$B$93="","",N('Inputs'!$E$93))</f>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="42">
         <f>IF('Inputs'!$B$94="","",N('Inputs'!$E$94))</f>
       </c>
     </row>
@@ -16776,22 +16779,22 @@
       <c r="B9" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="46">
         <f>IF('Inputs'!$B$89="","",IF('Needs years'!$C$6=0,"",'Needs years'!$C$6))</f>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="46">
         <f>IF('Inputs'!$B$90="","",IF('Needs years'!$C$62=0,"",'Needs years'!$C$62))</f>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="46">
         <f>IF('Inputs'!$B$91="","",IF('Needs years'!$C$118=0,"",'Needs years'!$C$118))</f>
       </c>
-      <c r="F9" s="45">
+      <c r="F9" s="46">
         <f>IF('Inputs'!$B$92="","",IF('Needs years'!$C$174=0,"",'Needs years'!$C$174))</f>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="46">
         <f>IF('Inputs'!$B$93="","",IF('Needs years'!$C$230=0,"",'Needs years'!$C$230))</f>
       </c>
-      <c r="H9" s="45">
+      <c r="H9" s="46">
         <f>IF('Inputs'!$B$94="","",IF('Needs years'!$C$286=0,"",'Needs years'!$C$286))</f>
       </c>
     </row>
@@ -16799,22 +16802,22 @@
       <c r="B10" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="47">
         <f>IF('Inputs'!$B$89="","",IF('Needs years'!$C$6=0,"",'Needs years'!$C$8))</f>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>IF('Inputs'!$B$90="","",IF('Needs years'!$C$62=0,"",'Needs years'!$C$64))</f>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="47">
         <f>IF('Inputs'!$B$91="","",IF('Needs years'!$C$118=0,"",'Needs years'!$C$120))</f>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="47">
         <f>IF('Inputs'!$B$92="","",IF('Needs years'!$C$174=0,"",'Needs years'!$C$176))</f>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="47">
         <f>IF('Inputs'!$B$93="","",IF('Needs years'!$C$230=0,"",'Needs years'!$C$232))</f>
       </c>
-      <c r="H10" s="46">
+      <c r="H10" s="47">
         <f>IF('Inputs'!$B$94="","",IF('Needs years'!$C$286=0,"",'Needs years'!$C$288))</f>
       </c>
     </row>
@@ -16822,22 +16825,22 @@
       <c r="B11" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="42">
         <f>IF('Inputs'!$B$89="","",'Needs years'!$C$10)</f>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="42">
         <f>IF('Inputs'!$B$90="","",'Needs years'!$C$66)</f>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="42">
         <f>IF('Inputs'!$B$91="","",'Needs years'!$C$122)</f>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="42">
         <f>IF('Inputs'!$B$92="","",'Needs years'!$C$178)</f>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="42">
         <f>IF('Inputs'!$B$93="","",'Needs years'!$C$234)</f>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="42">
         <f>IF('Inputs'!$B$94="","",'Needs years'!$C$290)</f>
       </c>
     </row>
@@ -16845,22 +16848,22 @@
       <c r="B12" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="43">
         <f>IF('Inputs'!$B$89="","",'Needs calc'!$C$39)</f>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="43">
         <f>IF('Inputs'!$B$90="","",'Needs calc'!$C$46)</f>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="43">
         <f>IF('Inputs'!$B$91="","",'Needs calc'!$C$53)</f>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="43">
         <f>IF('Inputs'!$B$92="","",'Needs calc'!$C$60)</f>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="43">
         <f>IF('Inputs'!$B$93="","",'Needs calc'!$C$67)</f>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="43">
         <f>IF('Inputs'!$B$94="","",'Needs calc'!$C$74)</f>
       </c>
     </row>
@@ -16891,22 +16894,22 @@
       <c r="B14" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="47">
         <f>IF('Inputs'!$B$89="","",'Needs calc'!$C$42)</f>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="47">
         <f>IF('Inputs'!$B$90="","",'Needs calc'!$C$49)</f>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="47">
         <f>IF('Inputs'!$B$91="","",'Needs calc'!$C$56)</f>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="47">
         <f>IF('Inputs'!$B$92="","",'Needs calc'!$C$63)</f>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="47">
         <f>IF('Inputs'!$B$93="","",'Needs calc'!$C$70)</f>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="47">
         <f>IF('Inputs'!$B$94="","",'Needs calc'!$C$77)</f>
       </c>
     </row>
@@ -16914,22 +16917,22 @@
       <c r="B15" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="43">
         <f>IF('Inputs'!$B$89="","",'Needs calc'!$C$43)</f>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="43">
         <f>IF('Inputs'!$B$90="","",'Needs calc'!$C$50)</f>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="43">
         <f>IF('Inputs'!$B$91="","",'Needs calc'!$C$57)</f>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="43">
         <f>IF('Inputs'!$B$92="","",'Needs calc'!$C$64)</f>
       </c>
-      <c r="G15" s="42">
+      <c r="G15" s="43">
         <f>IF('Inputs'!$B$93="","",'Needs calc'!$C$71)</f>
       </c>
-      <c r="H15" s="42">
+      <c r="H15" s="43">
         <f>IF('Inputs'!$B$94="","",'Needs calc'!$C$78)</f>
       </c>
     </row>
@@ -16937,22 +16940,22 @@
       <c r="B16" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="43">
         <f>IF('Inputs'!$B$89="","",'Needs calc'!$C$44)</f>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="43">
         <f>IF('Inputs'!$B$90="","",'Needs calc'!$C$51)</f>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="43">
         <f>IF('Inputs'!$B$91="","",'Needs calc'!$C$58)</f>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="43">
         <f>IF('Inputs'!$B$92="","",'Needs calc'!$C$65)</f>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="43">
         <f>IF('Inputs'!$B$93="","",'Needs calc'!$C$72)</f>
       </c>
-      <c r="H16" s="42">
+      <c r="H16" s="43">
         <f>IF('Inputs'!$B$94="","",'Needs calc'!$C$79)</f>
       </c>
     </row>
@@ -16960,22 +16963,22 @@
       <c r="B17" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="42">
         <f>IF('Inputs'!$B$89="","",'Needs calc'!$C$45)</f>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <f>IF('Inputs'!$B$90="","",'Needs calc'!$C$52)</f>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <f>IF('Inputs'!$B$91="","",'Needs calc'!$C$59)</f>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="42">
         <f>IF('Inputs'!$B$92="","",'Needs calc'!$C$66)</f>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="42">
         <f>IF('Inputs'!$B$93="","",'Needs calc'!$C$73)</f>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="42">
         <f>IF('Inputs'!$B$94="","",'Needs calc'!$C$80)</f>
       </c>
     </row>
@@ -17018,22 +17021,22 @@
       <c r="B21" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="43">
         <f>IF('Inputs'!$B$89="","",'Needs calc'!$T$4)</f>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="43">
         <f>IF('Inputs'!$B$90="","",'Needs calc'!$T$5)</f>
       </c>
-      <c r="E21" s="42">
+      <c r="E21" s="43">
         <f>IF('Inputs'!$B$91="","",'Needs calc'!$T$6)</f>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="43">
         <f>IF('Inputs'!$B$92="","",'Needs calc'!$T$7)</f>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="43">
         <f>IF('Inputs'!$B$93="","",'Needs calc'!$T$8)</f>
       </c>
-      <c r="H21" s="42">
+      <c r="H21" s="43">
         <f>IF('Inputs'!$B$94="","",'Needs calc'!$T$9)</f>
       </c>
     </row>
@@ -17041,22 +17044,22 @@
       <c r="B22" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="C22" s="41">
+      <c r="C22" s="42">
         <f>IF('Inputs'!$B$89="","",IF('Needs calc'!$T$4=0,"",IF('Inputs'!$T$89=1,"spouse, no duty",IF('Inputs'!$Q$89=1,"the trust","them"))))</f>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="42">
         <f>IF('Inputs'!$B$90="","",IF('Needs calc'!$T$5=0,"",IF('Inputs'!$T$90=1,"spouse, no duty",IF('Inputs'!$Q$90=1,"the trust","them"))))</f>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="42">
         <f>IF('Inputs'!$B$91="","",IF('Needs calc'!$T$6=0,"",IF('Inputs'!$T$91=1,"spouse, no duty",IF('Inputs'!$Q$91=1,"the trust","them"))))</f>
       </c>
-      <c r="F22" s="41">
+      <c r="F22" s="42">
         <f>IF('Inputs'!$B$92="","",IF('Needs calc'!$T$7=0,"",IF('Inputs'!$T$92=1,"spouse, no duty",IF('Inputs'!$Q$92=1,"the trust","them"))))</f>
       </c>
-      <c r="G22" s="41">
+      <c r="G22" s="42">
         <f>IF('Inputs'!$B$93="","",IF('Needs calc'!$T$8=0,"",IF('Inputs'!$T$93=1,"spouse, no duty",IF('Inputs'!$Q$93=1,"the trust","them"))))</f>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="42">
         <f>IF('Inputs'!$B$94="","",IF('Needs calc'!$T$9=0,"",IF('Inputs'!$T$94=1,"spouse, no duty",IF('Inputs'!$Q$94=1,"the trust","them"))))</f>
       </c>
     </row>
@@ -17064,22 +17067,22 @@
       <c r="B23" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="C23" s="41">
+      <c r="C23" s="42">
         <f>IF('Inputs'!$B$89="","",'Needs calc'!$T$39)</f>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="42">
         <f>IF('Inputs'!$B$90="","",'Needs calc'!$T$46)</f>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="42">
         <f>IF('Inputs'!$B$91="","",'Needs calc'!$T$53)</f>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="42">
         <f>IF('Inputs'!$B$92="","",'Needs calc'!$T$60)</f>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="42">
         <f>IF('Inputs'!$B$93="","",'Needs calc'!$T$67)</f>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="42">
         <f>IF('Inputs'!$B$94="","",'Needs calc'!$T$74)</f>
       </c>
     </row>
@@ -17110,22 +17113,22 @@
       <c r="B25" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="C25" s="41">
+      <c r="C25" s="42">
         <f>IF('Inputs'!$B$89="","",'Needs calc'!$T$43)</f>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="42">
         <f>IF('Inputs'!$B$90="","",'Needs calc'!$T$50)</f>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="42">
         <f>IF('Inputs'!$B$91="","",'Needs calc'!$T$57)</f>
       </c>
-      <c r="F25" s="41">
+      <c r="F25" s="42">
         <f>IF('Inputs'!$B$92="","",'Needs calc'!$T$64)</f>
       </c>
-      <c r="G25" s="41">
+      <c r="G25" s="42">
         <f>IF('Inputs'!$B$93="","",'Needs calc'!$T$71)</f>
       </c>
-      <c r="H25" s="41">
+      <c r="H25" s="42">
         <f>IF('Inputs'!$B$94="","",'Needs calc'!$T$78)</f>
       </c>
     </row>
@@ -17133,22 +17136,22 @@
       <c r="B26" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="42">
         <f>IF('Inputs'!$B$89="","",'Needs calc'!$T$44)</f>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="42">
         <f>IF('Inputs'!$B$90="","",'Needs calc'!$T$51)</f>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="42">
         <f>IF('Inputs'!$B$91="","",'Needs calc'!$T$58)</f>
       </c>
-      <c r="F26" s="41">
+      <c r="F26" s="42">
         <f>IF('Inputs'!$B$92="","",'Needs calc'!$T$65)</f>
       </c>
-      <c r="G26" s="41">
+      <c r="G26" s="42">
         <f>IF('Inputs'!$B$93="","",'Needs calc'!$T$72)</f>
       </c>
-      <c r="H26" s="41">
+      <c r="H26" s="42">
         <f>IF('Inputs'!$B$94="","",'Needs calc'!$T$79)</f>
       </c>
     </row>
@@ -17156,7 +17159,7 @@
       <c r="B28" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="42">
         <f>'Workings'!$C$66</f>
       </c>
     </row>
@@ -17164,7 +17167,7 @@
       <c r="B29" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="42">
         <f>'Needs calc'!$T$10</f>
       </c>
     </row>
@@ -17172,7 +17175,7 @@
       <c r="B30" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C30" s="41">
+      <c r="C30" s="42">
         <f>'Needs calc'!$T$26</f>
       </c>
     </row>
@@ -17180,7 +17183,7 @@
       <c r="B31" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C31" s="41">
+      <c r="C31" s="42">
         <f>IF(AND(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),'Workings'!$C$66&gt;0),'Workings'!$C$66,0)</f>
       </c>
     </row>
@@ -17188,7 +17191,7 @@
       <c r="B32" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C32" s="41">
+      <c r="C32" s="42">
         <f>'Needs calc'!$T$17</f>
       </c>
     </row>
@@ -17196,7 +17199,7 @@
       <c r="B33" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="45">
         <f>'Needs calc'!$T$18</f>
       </c>
     </row>
@@ -17204,7 +17207,7 @@
       <c r="B34" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C34" s="41">
+      <c r="C34" s="42">
         <f>'Needs calc'!$T$25</f>
       </c>
     </row>
@@ -17212,7 +17215,7 @@
       <c r="B35" s="29" t="s">
         <v>290</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="43">
         <f>('Needs calc'!$T$10+('Needs calc'!$T$4+'Needs calc'!$T$5+'Needs calc'!$T$6+'Needs calc'!$T$7+'Needs calc'!$T$8+'Needs calc'!$T$9))</f>
       </c>
     </row>
@@ -17255,22 +17258,22 @@
       <c r="B39" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="C39" s="41">
+      <c r="C39" s="42">
         <f>IF('Inputs'!$B$89="","",'Needs years'!$C$11)</f>
       </c>
-      <c r="D39" s="41">
+      <c r="D39" s="42">
         <f>IF('Inputs'!$B$90="","",'Needs years'!$C$67)</f>
       </c>
-      <c r="E39" s="41">
+      <c r="E39" s="42">
         <f>IF('Inputs'!$B$91="","",'Needs years'!$C$123)</f>
       </c>
-      <c r="F39" s="41">
+      <c r="F39" s="42">
         <f>IF('Inputs'!$B$92="","",'Needs years'!$C$179)</f>
       </c>
-      <c r="G39" s="41">
+      <c r="G39" s="42">
         <f>IF('Inputs'!$B$93="","",'Needs years'!$C$235)</f>
       </c>
-      <c r="H39" s="41">
+      <c r="H39" s="42">
         <f>IF('Inputs'!$B$94="","",'Needs years'!$C$291)</f>
       </c>
     </row>
@@ -17278,22 +17281,22 @@
       <c r="B40" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="C40" s="41">
+      <c r="C40" s="42">
         <f>IF('Inputs'!$B$89="","",'Needs years'!$C$12)</f>
       </c>
-      <c r="D40" s="41">
+      <c r="D40" s="42">
         <f>IF('Inputs'!$B$90="","",'Needs years'!$C$68)</f>
       </c>
-      <c r="E40" s="41">
+      <c r="E40" s="42">
         <f>IF('Inputs'!$B$91="","",'Needs years'!$C$124)</f>
       </c>
-      <c r="F40" s="41">
+      <c r="F40" s="42">
         <f>IF('Inputs'!$B$92="","",'Needs years'!$C$180)</f>
       </c>
-      <c r="G40" s="41">
+      <c r="G40" s="42">
         <f>IF('Inputs'!$B$93="","",'Needs years'!$C$236)</f>
       </c>
-      <c r="H40" s="41">
+      <c r="H40" s="42">
         <f>IF('Inputs'!$B$94="","",'Needs years'!$C$292)</f>
       </c>
     </row>
@@ -17301,22 +17304,22 @@
       <c r="B41" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="C41" s="41">
+      <c r="C41" s="42">
         <f>IF('Inputs'!$B$89="","",'Needs years'!$C$13)</f>
       </c>
-      <c r="D41" s="41">
+      <c r="D41" s="42">
         <f>IF('Inputs'!$B$90="","",'Needs years'!$C$69)</f>
       </c>
-      <c r="E41" s="41">
+      <c r="E41" s="42">
         <f>IF('Inputs'!$B$91="","",'Needs years'!$C$125)</f>
       </c>
-      <c r="F41" s="41">
+      <c r="F41" s="42">
         <f>IF('Inputs'!$B$92="","",'Needs years'!$C$181)</f>
       </c>
-      <c r="G41" s="41">
+      <c r="G41" s="42">
         <f>IF('Inputs'!$B$93="","",'Needs years'!$C$237)</f>
       </c>
-      <c r="H41" s="41">
+      <c r="H41" s="42">
         <f>IF('Inputs'!$B$94="","",'Needs years'!$C$293)</f>
       </c>
     </row>
@@ -17627,16 +17630,16 @@
       <c r="B27" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="38">
         <f>IF('Inputs'!$B$89="","",IF('Needs calc'!$C$44&gt;0,"Short R "&amp;FIXED(ROUND('Needs calc'!$C$44,-3),0),IF('Needs calc'!$C$44&lt;0,"R "&amp;FIXED(ROUND(-'Needs calc'!$C$44,-3),0)&amp;" over","Covered")))</f>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="38">
         <f>IF('Inputs'!$B$90="","",IF('Needs calc'!$C$51&gt;0,"Short R "&amp;FIXED(ROUND('Needs calc'!$C$51,-3),0),IF('Needs calc'!$C$51&lt;0,"R "&amp;FIXED(ROUND(-'Needs calc'!$C$51,-3),0)&amp;" over","Covered")))</f>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="38">
         <f>IF('Inputs'!$B$91="","",IF('Needs calc'!$C$58&gt;0,"Short R "&amp;FIXED(ROUND('Needs calc'!$C$58,-3),0),IF('Needs calc'!$C$58&lt;0,"R "&amp;FIXED(ROUND(-'Needs calc'!$C$58,-3),0)&amp;" over","Covered")))</f>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="38">
         <f>IF('Inputs'!$B$92="","",IF('Needs calc'!$C$65&gt;0,"Short R "&amp;FIXED(ROUND('Needs calc'!$C$65,-3),0),IF('Needs calc'!$C$65&lt;0,"R "&amp;FIXED(ROUND(-'Needs calc'!$C$65,-3),0)&amp;" over","Covered")))</f>
       </c>
     </row>
@@ -17658,13 +17661,13 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="38">
+      <c r="B29" s="39">
         <f>TRIM(IF(COUNTIF('Inputs'!$B$89:$B$94,"?*")&gt;4,"The others who depend on you are on the workings page. ","")&amp;IF('Needs calc'!$C$37&gt;0,"Life cover of R "&amp;FIXED(ROUND('Needs calc'!$C$37,-3),0)&amp;" is paid directly to "&amp;IF(SUMPRODUCT('Inputs'!$R$59:$R$70*('Inputs'!$F$59:$F$70="")*('Inputs'!$D$59:$D$70&gt;0))=1,"someone who is","people who are")&amp;" not recorded as depending on you"&amp;IF('Needs calc'!$C$38&gt;0,"; they pay R "&amp;FIXED(ROUND('Needs calc'!$C$38,-3),0)&amp;" of the estate duty on it today","")&amp;", and it is not counted for anyone above. ","")&amp;IF(SUMPRODUCT(('Inputs'!$T$89:$T$94=1)*1)&gt;0,"New cover for your spouse is nominated to them, so it carries no estate duty.",""))</f>
       </c>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="12" t="s">
@@ -17728,7 +17731,7 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="39">
+      <c r="B37" s="40">
         <f>IF(SUMPRODUCT(('Inputs'!$H$89:$H$94="Yes")*('Inputs'!$B$89:$B$94&lt;&gt;""))&gt;0,"First year","")</f>
       </c>
       <c r="C37" s="15">
@@ -17745,7 +17748,7 @@
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="39">
+      <c r="B38" s="40">
         <f>IF(SUMPRODUCT(('Inputs'!$H$89:$H$94="Yes")*('Inputs'!$B$89:$B$94&lt;&gt;""))&gt;0,"Over the whole period","")</f>
       </c>
       <c r="C38" s="15">
@@ -17762,7 +17765,7 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="39">
+      <c r="B39" s="40">
         <f>IF(SUMPRODUCT(('Inputs'!$H$89:$H$94="Yes")*('Inputs'!$B$89:$B$94&lt;&gt;""))&gt;0,"Extra capital it needs today (already in the need)","")</f>
       </c>
       <c r="C39" s="15">
@@ -17868,7 +17871,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.25" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Life cover need&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
   </headerFooter>

--- a/Duwalcoe_Quick_FNA_Template.xlsx
+++ b/Duwalcoe_Quick_FNA_Template.xlsx
@@ -186,7 +186,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2</t>
+    <t>2.3</t>
   </si>
   <si>
     <t>Shares and unit trusts</t>
@@ -429,13 +429,13 @@
     <t>Retirement fund or annuity</t>
   </si>
   <si>
-    <t>Credited to (the fund trustees decide, s.37C)</t>
+    <t>Credited to (the fund trustees decide, s.37C; a living annuity goes to its nominee)</t>
   </si>
   <si>
     <t>Paid out, after lump sum tax</t>
   </si>
   <si>
-    <t>Credited to: who the fund trustees are expected to pay. They must look after dependants first (s.37C), so where the nominee is not a dependant the CRM proposes the children. Blank: not counted for any dependant. Paid out in cash, taxed as a death benefit lump sum on the total of all the funds (the first R 550,000 free).</t>
+    <t>Credited to: who the fund trustees are expected to pay. They must look after dependants first (s.37C), so where the nominee is not a dependant the CRM proposes the children. A living annuity is not a fund: it goes straight to its nominee. Blank: not counted for any dependant. Paid out in cash, taxed as a death benefit lump sum on the total of all the funds and annuities (the first R 550,000 free).</t>
   </si>
   <si>
     <t>6. The people who depend on your client</t>

--- a/Duwalcoe_Quick_FNA_Template.xlsx
+++ b/Duwalcoe_Quick_FNA_Template.xlsx
@@ -84,16 +84,16 @@
     <definedName name="QF_A_LumpTable">Inputs!$G$134:$I$137</definedName>
     <definedName name="QF_K_checks">Inputs!$B$153</definedName>
     <definedName name="QF_T_checks">Inputs!$B$154:$B$167</definedName>
-    <definedName name="QF_W_cost">Workings!$C$59</definedName>
+    <definedName name="QF_W_cost">Workings!$C$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Inputs'!$A1:$J167</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inputs'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Summary'!$A1:$D36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Life cover need'!$A1:$F48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Life cover need'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Figures for quoting'!$A1:$D36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Figures for quoting'!$A1:$D37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Figures for quoting'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Workings'!$A1:$D71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Workings'!$A1:$D73</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Workings'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Needs workings'!$A1:$I45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Needs workings'!$1:$2</definedName>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="425">
   <si>
     <t>kind</t>
   </si>
@@ -186,7 +186,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3</t>
+    <t>2.4</t>
   </si>
   <si>
     <t>Shares and unit trusts</t>
@@ -765,10 +765,13 @@
     <t>OUTSIDE THE ESTATE: NO EXECUTOR'S FEES</t>
   </si>
   <si>
-    <t>Policies paid to a named person or spouse (counted for estate duty)</t>
-  </si>
-  <si>
-    <t>Death income benefits, at their value (counted for estate duty)</t>
+    <t>Policies paid to a named person (counted for estate duty)</t>
+  </si>
+  <si>
+    <t>Death income for a named person, at its value (counted for estate duty)</t>
+  </si>
+  <si>
+    <t>Policies and death income paid to the spouse (no estate duty, s.4(q))</t>
   </si>
   <si>
     <t>Approved group life (not counted)</t>
@@ -861,7 +864,13 @@
     <t>Gross estate (handled by the executor)</t>
   </si>
   <si>
-    <t>Policies paid to a named person or spouse, counted for estate duty</t>
+    <t>Policies paid to a named person, counted for estate duty</t>
+  </si>
+  <si>
+    <t>Policies and death income paid to the spouse (counted for estate duty, s.3(3)(a))</t>
+  </si>
+  <si>
+    <t>Less the same: it passes to the spouse (s.4(q))</t>
   </si>
   <si>
     <t>Gross dutiable estate</t>
@@ -894,7 +903,7 @@
     <t>Share of the bequests the estate can pay</t>
   </si>
   <si>
-    <t>Less everything passing to the spouse (s.4(q))</t>
+    <t>Less assets and residue passing to the spouse (s.4(q))</t>
   </si>
   <si>
     <t>Net value of the estate</t>
@@ -2757,10 +2766,10 @@
         <f>IF(AND(L22=1,N(D22)&gt;0,E22=""),1,0)</f>
       </c>
       <c r="U22">
-        <f>ROUND('Workings'!$C$40*S22,2)</f>
+        <f>ROUND('Workings'!$C$42*S22,2)</f>
       </c>
       <c r="V22">
-        <f>ROUND('Workings'!$D$40*S22,2)</f>
+        <f>ROUND('Workings'!$D$42*S22,2)</f>
       </c>
       <c r="W22">
         <f>IF(AND(B22="",N(D22)=0),0,IF(OR(C22="",G22=""),1,0))</f>
@@ -2815,10 +2824,10 @@
         <f>IF(AND(L23=1,N(D23)&gt;0,E23=""),1,0)</f>
       </c>
       <c r="U23">
-        <f>ROUND('Workings'!$C$40*S23,2)</f>
+        <f>ROUND('Workings'!$C$42*S23,2)</f>
       </c>
       <c r="V23">
-        <f>ROUND('Workings'!$D$40*S23,2)</f>
+        <f>ROUND('Workings'!$D$42*S23,2)</f>
       </c>
       <c r="W23">
         <f>IF(AND(B23="",N(D23)=0),0,IF(OR(C23="",G23=""),1,0))</f>
@@ -2873,10 +2882,10 @@
         <f>IF(AND(L24=1,N(D24)&gt;0,E24=""),1,0)</f>
       </c>
       <c r="U24">
-        <f>ROUND('Workings'!$C$40*S24,2)</f>
+        <f>ROUND('Workings'!$C$42*S24,2)</f>
       </c>
       <c r="V24">
-        <f>ROUND('Workings'!$D$40*S24,2)</f>
+        <f>ROUND('Workings'!$D$42*S24,2)</f>
       </c>
       <c r="W24">
         <f>IF(AND(B24="",N(D24)=0),0,IF(OR(C24="",G24=""),1,0))</f>
@@ -2931,10 +2940,10 @@
         <f>IF(AND(L25=1,N(D25)&gt;0,E25=""),1,0)</f>
       </c>
       <c r="U25">
-        <f>ROUND('Workings'!$C$40*S25,2)</f>
+        <f>ROUND('Workings'!$C$42*S25,2)</f>
       </c>
       <c r="V25">
-        <f>ROUND('Workings'!$D$40*S25,2)</f>
+        <f>ROUND('Workings'!$D$42*S25,2)</f>
       </c>
       <c r="W25">
         <f>IF(AND(B25="",N(D25)=0),0,IF(OR(C25="",G25=""),1,0))</f>
@@ -2989,10 +2998,10 @@
         <f>IF(AND(L26=1,N(D26)&gt;0,E26=""),1,0)</f>
       </c>
       <c r="U26">
-        <f>ROUND('Workings'!$C$40*S26,2)</f>
+        <f>ROUND('Workings'!$C$42*S26,2)</f>
       </c>
       <c r="V26">
-        <f>ROUND('Workings'!$D$40*S26,2)</f>
+        <f>ROUND('Workings'!$D$42*S26,2)</f>
       </c>
       <c r="W26">
         <f>IF(AND(B26="",N(D26)=0),0,IF(OR(C26="",G26=""),1,0))</f>
@@ -3047,10 +3056,10 @@
         <f>IF(AND(L27=1,N(D27)&gt;0,E27=""),1,0)</f>
       </c>
       <c r="U27">
-        <f>ROUND('Workings'!$C$40*S27,2)</f>
+        <f>ROUND('Workings'!$C$42*S27,2)</f>
       </c>
       <c r="V27">
-        <f>ROUND('Workings'!$D$40*S27,2)</f>
+        <f>ROUND('Workings'!$D$42*S27,2)</f>
       </c>
       <c r="W27">
         <f>IF(AND(B27="",N(D27)=0),0,IF(OR(C27="",G27=""),1,0))</f>
@@ -3105,10 +3114,10 @@
         <f>IF(AND(L28=1,N(D28)&gt;0,E28=""),1,0)</f>
       </c>
       <c r="U28">
-        <f>ROUND('Workings'!$C$40*S28,2)</f>
+        <f>ROUND('Workings'!$C$42*S28,2)</f>
       </c>
       <c r="V28">
-        <f>ROUND('Workings'!$D$40*S28,2)</f>
+        <f>ROUND('Workings'!$D$42*S28,2)</f>
       </c>
       <c r="W28">
         <f>IF(AND(B28="",N(D28)=0),0,IF(OR(C28="",G28=""),1,0))</f>
@@ -3163,10 +3172,10 @@
         <f>IF(AND(L29=1,N(D29)&gt;0,E29=""),1,0)</f>
       </c>
       <c r="U29">
-        <f>ROUND('Workings'!$C$40*S29,2)</f>
+        <f>ROUND('Workings'!$C$42*S29,2)</f>
       </c>
       <c r="V29">
-        <f>ROUND('Workings'!$D$40*S29,2)</f>
+        <f>ROUND('Workings'!$D$42*S29,2)</f>
       </c>
       <c r="W29">
         <f>IF(AND(B29="",N(D29)=0),0,IF(OR(C29="",G29=""),1,0))</f>
@@ -3221,10 +3230,10 @@
         <f>IF(AND(L30=1,N(D30)&gt;0,E30=""),1,0)</f>
       </c>
       <c r="U30">
-        <f>ROUND('Workings'!$C$40*S30,2)</f>
+        <f>ROUND('Workings'!$C$42*S30,2)</f>
       </c>
       <c r="V30">
-        <f>ROUND('Workings'!$D$40*S30,2)</f>
+        <f>ROUND('Workings'!$D$42*S30,2)</f>
       </c>
       <c r="W30">
         <f>IF(AND(B30="",N(D30)=0),0,IF(OR(C30="",G30=""),1,0))</f>
@@ -3279,10 +3288,10 @@
         <f>IF(AND(L31=1,N(D31)&gt;0,E31=""),1,0)</f>
       </c>
       <c r="U31">
-        <f>ROUND('Workings'!$C$40*S31,2)</f>
+        <f>ROUND('Workings'!$C$42*S31,2)</f>
       </c>
       <c r="V31">
-        <f>ROUND('Workings'!$D$40*S31,2)</f>
+        <f>ROUND('Workings'!$D$42*S31,2)</f>
       </c>
       <c r="W31">
         <f>IF(AND(B31="",N(D31)=0),0,IF(OR(C31="",G31=""),1,0))</f>
@@ -3337,10 +3346,10 @@
         <f>IF(AND(L32=1,N(D32)&gt;0,E32=""),1,0)</f>
       </c>
       <c r="U32">
-        <f>ROUND('Workings'!$C$40*S32,2)</f>
+        <f>ROUND('Workings'!$C$42*S32,2)</f>
       </c>
       <c r="V32">
-        <f>ROUND('Workings'!$D$40*S32,2)</f>
+        <f>ROUND('Workings'!$D$42*S32,2)</f>
       </c>
       <c r="W32">
         <f>IF(AND(B32="",N(D32)=0),0,IF(OR(C32="",G32=""),1,0))</f>
@@ -3395,10 +3404,10 @@
         <f>IF(AND(L33=1,N(D33)&gt;0,E33=""),1,0)</f>
       </c>
       <c r="U33">
-        <f>ROUND('Workings'!$C$40*S33,2)</f>
+        <f>ROUND('Workings'!$C$42*S33,2)</f>
       </c>
       <c r="V33">
-        <f>ROUND('Workings'!$D$40*S33,2)</f>
+        <f>ROUND('Workings'!$D$42*S33,2)</f>
       </c>
       <c r="W33">
         <f>IF(AND(B33="",N(D33)=0),0,IF(OR(C33="",G33=""),1,0))</f>
@@ -3453,10 +3462,10 @@
         <f>IF(AND(L34=1,N(D34)&gt;0,E34=""),1,0)</f>
       </c>
       <c r="U34">
-        <f>ROUND('Workings'!$C$40*S34,2)</f>
+        <f>ROUND('Workings'!$C$42*S34,2)</f>
       </c>
       <c r="V34">
-        <f>ROUND('Workings'!$D$40*S34,2)</f>
+        <f>ROUND('Workings'!$D$42*S34,2)</f>
       </c>
       <c r="W34">
         <f>IF(AND(B34="",N(D34)=0),0,IF(OR(C34="",G34=""),1,0))</f>
@@ -3511,10 +3520,10 @@
         <f>IF(AND(L35=1,N(D35)&gt;0,E35=""),1,0)</f>
       </c>
       <c r="U35">
-        <f>ROUND('Workings'!$C$40*S35,2)</f>
+        <f>ROUND('Workings'!$C$42*S35,2)</f>
       </c>
       <c r="V35">
-        <f>ROUND('Workings'!$D$40*S35,2)</f>
+        <f>ROUND('Workings'!$D$42*S35,2)</f>
       </c>
       <c r="W35">
         <f>IF(AND(B35="",N(D35)=0),0,IF(OR(C35="",G35=""),1,0))</f>
@@ -3569,10 +3578,10 @@
         <f>IF(AND(L36=1,N(D36)&gt;0,E36=""),1,0)</f>
       </c>
       <c r="U36">
-        <f>ROUND('Workings'!$C$40*S36,2)</f>
+        <f>ROUND('Workings'!$C$42*S36,2)</f>
       </c>
       <c r="V36">
-        <f>ROUND('Workings'!$D$40*S36,2)</f>
+        <f>ROUND('Workings'!$D$42*S36,2)</f>
       </c>
       <c r="W36">
         <f>IF(AND(B36="",N(D36)=0),0,IF(OR(C36="",G36=""),1,0))</f>
@@ -3627,10 +3636,10 @@
         <f>IF(AND(L37=1,N(D37)&gt;0,E37=""),1,0)</f>
       </c>
       <c r="U37">
-        <f>ROUND('Workings'!$C$40*S37,2)</f>
+        <f>ROUND('Workings'!$C$42*S37,2)</f>
       </c>
       <c r="V37">
-        <f>ROUND('Workings'!$D$40*S37,2)</f>
+        <f>ROUND('Workings'!$D$42*S37,2)</f>
       </c>
       <c r="W37">
         <f>IF(AND(B37="",N(D37)=0),0,IF(OR(C37="",G37=""),1,0))</f>
@@ -3685,10 +3694,10 @@
         <f>IF(AND(L38=1,N(D38)&gt;0,E38=""),1,0)</f>
       </c>
       <c r="U38">
-        <f>ROUND('Workings'!$C$40*S38,2)</f>
+        <f>ROUND('Workings'!$C$42*S38,2)</f>
       </c>
       <c r="V38">
-        <f>ROUND('Workings'!$D$40*S38,2)</f>
+        <f>ROUND('Workings'!$D$42*S38,2)</f>
       </c>
       <c r="W38">
         <f>IF(AND(B38="",N(D38)=0),0,IF(OR(C38="",G38=""),1,0))</f>
@@ -3743,10 +3752,10 @@
         <f>IF(AND(L39=1,N(D39)&gt;0,E39=""),1,0)</f>
       </c>
       <c r="U39">
-        <f>ROUND('Workings'!$C$40*S39,2)</f>
+        <f>ROUND('Workings'!$C$42*S39,2)</f>
       </c>
       <c r="V39">
-        <f>ROUND('Workings'!$D$40*S39,2)</f>
+        <f>ROUND('Workings'!$D$42*S39,2)</f>
       </c>
       <c r="W39">
         <f>IF(AND(B39="",N(D39)=0),0,IF(OR(C39="",G39=""),1,0))</f>
@@ -3927,10 +3936,10 @@
         <f>IF(AND(C59="Named person",E59&lt;&gt;"No"),N(D59),0)</f>
       </c>
       <c r="M59">
-        <f>ROUND('Workings'!$C$40*L59,2)</f>
+        <f>ROUND('Workings'!$C$42*L59,2)</f>
       </c>
       <c r="N59">
-        <f>ROUND('Workings'!$D$40*L59,2)</f>
+        <f>ROUND('Workings'!$D$42*L59,2)</f>
       </c>
       <c r="O59">
         <f>IF(L59&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L59,"&gt;0"),0)</f>
@@ -3958,10 +3967,10 @@
         <f>IF(AND(C60="Named person",E60&lt;&gt;"No"),N(D60),0)</f>
       </c>
       <c r="M60">
-        <f>ROUND('Workings'!$C$40*L60,2)</f>
+        <f>ROUND('Workings'!$C$42*L60,2)</f>
       </c>
       <c r="N60">
-        <f>ROUND('Workings'!$D$40*L60,2)</f>
+        <f>ROUND('Workings'!$D$42*L60,2)</f>
       </c>
       <c r="O60">
         <f>IF(L60&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L60,"&gt;0"),0)</f>
@@ -3989,10 +3998,10 @@
         <f>IF(AND(C61="Named person",E61&lt;&gt;"No"),N(D61),0)</f>
       </c>
       <c r="M61">
-        <f>ROUND('Workings'!$C$40*L61,2)</f>
+        <f>ROUND('Workings'!$C$42*L61,2)</f>
       </c>
       <c r="N61">
-        <f>ROUND('Workings'!$D$40*L61,2)</f>
+        <f>ROUND('Workings'!$D$42*L61,2)</f>
       </c>
       <c r="O61">
         <f>IF(L61&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L61,"&gt;0"),0)</f>
@@ -4020,10 +4029,10 @@
         <f>IF(AND(C62="Named person",E62&lt;&gt;"No"),N(D62),0)</f>
       </c>
       <c r="M62">
-        <f>ROUND('Workings'!$C$40*L62,2)</f>
+        <f>ROUND('Workings'!$C$42*L62,2)</f>
       </c>
       <c r="N62">
-        <f>ROUND('Workings'!$D$40*L62,2)</f>
+        <f>ROUND('Workings'!$D$42*L62,2)</f>
       </c>
       <c r="O62">
         <f>IF(L62&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L62,"&gt;0"),0)</f>
@@ -4051,10 +4060,10 @@
         <f>IF(AND(C63="Named person",E63&lt;&gt;"No"),N(D63),0)</f>
       </c>
       <c r="M63">
-        <f>ROUND('Workings'!$C$40*L63,2)</f>
+        <f>ROUND('Workings'!$C$42*L63,2)</f>
       </c>
       <c r="N63">
-        <f>ROUND('Workings'!$D$40*L63,2)</f>
+        <f>ROUND('Workings'!$D$42*L63,2)</f>
       </c>
       <c r="O63">
         <f>IF(L63&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L63,"&gt;0"),0)</f>
@@ -4082,10 +4091,10 @@
         <f>IF(AND(C64="Named person",E64&lt;&gt;"No"),N(D64),0)</f>
       </c>
       <c r="M64">
-        <f>ROUND('Workings'!$C$40*L64,2)</f>
+        <f>ROUND('Workings'!$C$42*L64,2)</f>
       </c>
       <c r="N64">
-        <f>ROUND('Workings'!$D$40*L64,2)</f>
+        <f>ROUND('Workings'!$D$42*L64,2)</f>
       </c>
       <c r="O64">
         <f>IF(L64&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L64,"&gt;0"),0)</f>
@@ -4113,10 +4122,10 @@
         <f>IF(AND(C65="Named person",E65&lt;&gt;"No"),N(D65),0)</f>
       </c>
       <c r="M65">
-        <f>ROUND('Workings'!$C$40*L65,2)</f>
+        <f>ROUND('Workings'!$C$42*L65,2)</f>
       </c>
       <c r="N65">
-        <f>ROUND('Workings'!$D$40*L65,2)</f>
+        <f>ROUND('Workings'!$D$42*L65,2)</f>
       </c>
       <c r="O65">
         <f>IF(L65&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L65,"&gt;0"),0)</f>
@@ -4144,10 +4153,10 @@
         <f>IF(AND(C66="Named person",E66&lt;&gt;"No"),N(D66),0)</f>
       </c>
       <c r="M66">
-        <f>ROUND('Workings'!$C$40*L66,2)</f>
+        <f>ROUND('Workings'!$C$42*L66,2)</f>
       </c>
       <c r="N66">
-        <f>ROUND('Workings'!$D$40*L66,2)</f>
+        <f>ROUND('Workings'!$D$42*L66,2)</f>
       </c>
       <c r="O66">
         <f>IF(L66&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L66,"&gt;0"),0)</f>
@@ -4175,10 +4184,10 @@
         <f>IF(AND(C67="Named person",E67&lt;&gt;"No"),N(D67),0)</f>
       </c>
       <c r="M67">
-        <f>ROUND('Workings'!$C$40*L67,2)</f>
+        <f>ROUND('Workings'!$C$42*L67,2)</f>
       </c>
       <c r="N67">
-        <f>ROUND('Workings'!$D$40*L67,2)</f>
+        <f>ROUND('Workings'!$D$42*L67,2)</f>
       </c>
       <c r="O67">
         <f>IF(L67&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L67,"&gt;0"),0)</f>
@@ -4206,10 +4215,10 @@
         <f>IF(AND(C68="Named person",E68&lt;&gt;"No"),N(D68),0)</f>
       </c>
       <c r="M68">
-        <f>ROUND('Workings'!$C$40*L68,2)</f>
+        <f>ROUND('Workings'!$C$42*L68,2)</f>
       </c>
       <c r="N68">
-        <f>ROUND('Workings'!$D$40*L68,2)</f>
+        <f>ROUND('Workings'!$D$42*L68,2)</f>
       </c>
       <c r="O68">
         <f>IF(L68&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L68,"&gt;0"),0)</f>
@@ -4237,10 +4246,10 @@
         <f>IF(AND(C69="Named person",E69&lt;&gt;"No"),N(D69),0)</f>
       </c>
       <c r="M69">
-        <f>ROUND('Workings'!$C$40*L69,2)</f>
+        <f>ROUND('Workings'!$C$42*L69,2)</f>
       </c>
       <c r="N69">
-        <f>ROUND('Workings'!$D$40*L69,2)</f>
+        <f>ROUND('Workings'!$D$42*L69,2)</f>
       </c>
       <c r="O69">
         <f>IF(L69&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L69,"&gt;0"),0)</f>
@@ -4268,10 +4277,10 @@
         <f>IF(AND(C70="Named person",E70&lt;&gt;"No"),N(D70),0)</f>
       </c>
       <c r="M70">
-        <f>ROUND('Workings'!$C$40*L70,2)</f>
+        <f>ROUND('Workings'!$C$42*L70,2)</f>
       </c>
       <c r="N70">
-        <f>ROUND('Workings'!$D$40*L70,2)</f>
+        <f>ROUND('Workings'!$D$42*L70,2)</f>
       </c>
       <c r="O70">
         <f>IF(L70&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L70,"&gt;0"),0)</f>
@@ -4392,10 +4401,10 @@
         <f>IF(N76=1,0,M76)</f>
       </c>
       <c r="P76">
-        <f>ROUND('Workings'!$C$40*O76,2)</f>
+        <f>ROUND('Workings'!$C$42*O76,2)</f>
       </c>
       <c r="Q76">
-        <f>ROUND('Workings'!$D$40*O76,2)</f>
+        <f>ROUND('Workings'!$D$42*O76,2)</f>
       </c>
       <c r="R76">
         <f>IF(O76&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L$70,"&gt;0")+COUNTIF(O$76:O76,"&gt;0"),0)</f>
@@ -4432,10 +4441,10 @@
         <f>IF(N77=1,0,M77)</f>
       </c>
       <c r="P77">
-        <f>ROUND('Workings'!$C$40*O77,2)</f>
+        <f>ROUND('Workings'!$C$42*O77,2)</f>
       </c>
       <c r="Q77">
-        <f>ROUND('Workings'!$D$40*O77,2)</f>
+        <f>ROUND('Workings'!$D$42*O77,2)</f>
       </c>
       <c r="R77">
         <f>IF(O77&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L$70,"&gt;0")+COUNTIF(O$76:O77,"&gt;0"),0)</f>
@@ -4472,10 +4481,10 @@
         <f>IF(N78=1,0,M78)</f>
       </c>
       <c r="P78">
-        <f>ROUND('Workings'!$C$40*O78,2)</f>
+        <f>ROUND('Workings'!$C$42*O78,2)</f>
       </c>
       <c r="Q78">
-        <f>ROUND('Workings'!$D$40*O78,2)</f>
+        <f>ROUND('Workings'!$D$42*O78,2)</f>
       </c>
       <c r="R78">
         <f>IF(O78&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L$70,"&gt;0")+COUNTIF(O$76:O78,"&gt;0"),0)</f>
@@ -4512,10 +4521,10 @@
         <f>IF(N79=1,0,M79)</f>
       </c>
       <c r="P79">
-        <f>ROUND('Workings'!$C$40*O79,2)</f>
+        <f>ROUND('Workings'!$C$42*O79,2)</f>
       </c>
       <c r="Q79">
-        <f>ROUND('Workings'!$D$40*O79,2)</f>
+        <f>ROUND('Workings'!$D$42*O79,2)</f>
       </c>
       <c r="R79">
         <f>IF(O79&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L$70,"&gt;0")+COUNTIF(O$76:O79,"&gt;0"),0)</f>
@@ -4552,10 +4561,10 @@
         <f>IF(N80=1,0,M80)</f>
       </c>
       <c r="P80">
-        <f>ROUND('Workings'!$C$40*O80,2)</f>
+        <f>ROUND('Workings'!$C$42*O80,2)</f>
       </c>
       <c r="Q80">
-        <f>ROUND('Workings'!$D$40*O80,2)</f>
+        <f>ROUND('Workings'!$D$42*O80,2)</f>
       </c>
       <c r="R80">
         <f>IF(O80&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L$70,"&gt;0")+COUNTIF(O$76:O80,"&gt;0"),0)</f>
@@ -4592,10 +4601,10 @@
         <f>IF(N81=1,0,M81)</f>
       </c>
       <c r="P81">
-        <f>ROUND('Workings'!$C$40*O81,2)</f>
+        <f>ROUND('Workings'!$C$42*O81,2)</f>
       </c>
       <c r="Q81">
-        <f>ROUND('Workings'!$D$40*O81,2)</f>
+        <f>ROUND('Workings'!$D$42*O81,2)</f>
       </c>
       <c r="R81">
         <f>IF(O81&gt;0,COUNTIF(S$22:S$39,"&gt;0")+COUNTIF(L$59:L$70,"&gt;0")+COUNTIF(O$76:O81,"&gt;0"),0)</f>
@@ -6231,35 +6240,35 @@
     </row>
     <row r="7" ht="58" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="25">
-        <f>IF('Inputs'!$C$15&lt;&gt;"",TRIM('Inputs'!$C$15)&amp;" ","")&amp;"If you died today, winding up your estate would cost about R "&amp;FIXED(('Workings'!$C$59)/1000000,2)&amp;" million"&amp;IF('Workings'!$C$62&gt;0,", and your debts of R "&amp;FIXED(('Workings'!$C$62)/1000000,2)&amp;" million have to be paid too","")&amp;". Your executor would have R "&amp;FIXED(('Workings'!$C$66)/1000000,2)&amp;" million in cash, so "&amp;IF('Workings'!$C$67&gt;0,"would be short by about R "&amp;FIXED(('Workings'!$C$67)/1000000,2)&amp;" million.","would have enough, with about R "&amp;FIXED(ROUND('Workings'!$C$68,-3),0)&amp;" left over.")</f>
+        <f>IF('Inputs'!$C$15&lt;&gt;"",TRIM('Inputs'!$C$15)&amp;" ","")&amp;"If you died today, winding up your estate would cost about R "&amp;FIXED(('Workings'!$C$61)/1000000,2)&amp;" million"&amp;IF('Workings'!$C$64&gt;0,", and your debts of R "&amp;FIXED(('Workings'!$C$64)/1000000,2)&amp;" million have to be paid too","")&amp;". Your executor would have R "&amp;FIXED(('Workings'!$C$68)/1000000,2)&amp;" million in cash, so "&amp;IF('Workings'!$C$69&gt;0,"would be short by about R "&amp;FIXED(('Workings'!$C$69)/1000000,2)&amp;" million.","would have enough, with about R "&amp;FIXED(ROUND('Workings'!$C$70,-3),0)&amp;" left over.")</f>
       </c>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
     <row r="8" ht="44" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="25">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),"With a Capital Legacy will and the Legacy Protection Plan, the plan pays about R "&amp;FIXED(ROUND(-'Workings'!$D$60,-3),0)&amp;" of the executor's and conveyancing fees, "&amp;IF('Workings'!$D$67=0,IF('Workings'!$C$67&gt;0,"the shortfall disappears","your executor still has enough"),"the shortfall falls to about R "&amp;FIXED(ROUND('Workings'!$D$67,-3),0))&amp;", and your heirs receive about R "&amp;FIXED(('Workings'!$D$69-'Workings'!$C$69)/1000000,2)&amp;" million more.","")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),"With a Capital Legacy will and the Legacy Protection Plan, the plan pays about R "&amp;FIXED(ROUND(-'Workings'!$D$62,-3),0)&amp;" of the executor's and conveyancing fees, "&amp;IF('Workings'!$D$69=0,IF('Workings'!$C$69&gt;0,"the shortfall disappears","your executor still has enough"),"the shortfall falls to about R "&amp;FIXED(ROUND('Workings'!$D$69,-3),0))&amp;", and your heirs receive about R "&amp;FIXED(('Workings'!$D$71-'Workings'!$C$71)/1000000,2)&amp;" million more.","")</f>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="26">
-        <f>IF('Workings'!$C$67&gt;0,"YOUR EXECUTOR'S CASH SHORTFALL TODAY","CASH LEFT OVER FOR YOUR EXECUTOR TODAY")</f>
+        <f>IF('Workings'!$C$69&gt;0,"YOUR EXECUTOR'S CASH SHORTFALL TODAY","CASH LEFT OVER FOR YOUR EXECUTOR TODAY")</f>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
     </row>
     <row r="11" ht="28" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="27">
-        <f>"R "&amp;FIXED(ROUND(IF('Workings'!$C$67&gt;0,'Workings'!$C$67,'Workings'!$C$68),-3),0)</f>
+        <f>"R "&amp;FIXED(ROUND(IF('Workings'!$C$69&gt;0,'Workings'!$C$69,'Workings'!$C$70),-3),0)</f>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="28">
-        <f>IF('Workings'!$C$67&gt;0,"the cash that has to be found before your estate can be wound up","what is left once the costs are paid")</f>
+        <f>IF('Workings'!$C$69&gt;0,"the cash that has to be found before your estate can be wound up","what is left once the costs are paid")</f>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
@@ -6280,10 +6289,10 @@
         <v>175</v>
       </c>
       <c r="C15" s="15">
-        <f>'Workings'!$C$58</f>
+        <f>'Workings'!$C$60</f>
       </c>
       <c r="D15" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$58,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$60,"")</f>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
@@ -6291,10 +6300,10 @@
         <v>176</v>
       </c>
       <c r="C16" s="15">
-        <f>'Workings'!$C$57</f>
+        <f>'Workings'!$C$59</f>
       </c>
       <c r="D16" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$57,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$59,"")</f>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -6302,10 +6311,10 @@
         <f>"Executor's fees"&amp;CHAR(10)&amp;IF(ROUND('Inputs'!$C$120,0)='Inputs'!$C$120,FIXED('Inputs'!$C$120,0),IF(ROUND('Inputs'!$C$120,1)='Inputs'!$C$120,FIXED('Inputs'!$C$120,1),FIXED('Inputs'!$C$120,2)))&amp;"%"&amp;" plus VAT"&amp;IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0)," / Capital Legacy "&amp;IF(ROUND('Inputs'!$C$112,0)='Inputs'!$C$112,FIXED('Inputs'!$C$112,0),IF(ROUND('Inputs'!$C$112,1)='Inputs'!$C$112,FIXED('Inputs'!$C$112,1),FIXED('Inputs'!$C$112,2)))&amp;"%"&amp;" plus VAT","")</f>
       </c>
       <c r="C17" s="15">
-        <f>'Workings'!$C$54</f>
+        <f>'Workings'!$C$56</f>
       </c>
       <c r="D17" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$54,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$56,"")</f>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -6313,10 +6322,10 @@
         <f>"Property transfer and conveyancing"&amp;CHAR(10)&amp;IF(ROUND('Inputs'!$C$125,0)='Inputs'!$C$125,FIXED('Inputs'!$C$125,0),IF(ROUND('Inputs'!$C$125,1)='Inputs'!$C$125,FIXED('Inputs'!$C$125,1),FIXED('Inputs'!$C$125,2)))&amp;"%"&amp;" of value"&amp;IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0)," / Capital Legacy's estimate","")</f>
       </c>
       <c r="C18" s="15">
-        <f>'Workings'!$C$55</f>
+        <f>'Workings'!$C$57</f>
       </c>
       <c r="D18" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$55,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$57,"")</f>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
@@ -6324,10 +6333,10 @@
         <v>177</v>
       </c>
       <c r="C19" s="15">
-        <f>'Workings'!$C$56</f>
+        <f>'Workings'!$C$58</f>
       </c>
       <c r="D19" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$56,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$58,"")</f>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
@@ -6335,10 +6344,10 @@
         <v>178</v>
       </c>
       <c r="C20" s="15">
-        <f>'Workings'!$C$53</f>
+        <f>'Workings'!$C$55</f>
       </c>
       <c r="D20" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$53,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$55,"")</f>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
@@ -6346,10 +6355,10 @@
         <v>179</v>
       </c>
       <c r="C21" s="31">
-        <f>'Workings'!$C$59</f>
+        <f>'Workings'!$C$61</f>
       </c>
       <c r="D21" s="31">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$59,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$61,"")</f>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
@@ -6357,10 +6366,10 @@
         <v>180</v>
       </c>
       <c r="C22" s="15">
-        <f>-'Workings'!$C$60</f>
+        <f>-'Workings'!$C$62</f>
       </c>
       <c r="D22" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),-'Workings'!$D$60,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),-'Workings'!$D$62,"")</f>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
@@ -6368,10 +6377,10 @@
         <v>181</v>
       </c>
       <c r="C23" s="31">
-        <f>'Workings'!$C$61</f>
+        <f>'Workings'!$C$63</f>
       </c>
       <c r="D23" s="31">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$61,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$63,"")</f>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
@@ -6379,10 +6388,10 @@
         <v>182</v>
       </c>
       <c r="C24" s="15">
-        <f>'Workings'!$C$62</f>
+        <f>'Workings'!$C$64</f>
       </c>
       <c r="D24" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$62,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$64,"")</f>
       </c>
     </row>
     <row r="25" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -6390,10 +6399,10 @@
         <f>"Cash your executor has"&amp;CHAR(10)&amp;"bank accounts, deposits and investments cashed in"</f>
       </c>
       <c r="C25" s="15">
-        <f>'Workings'!$C$66</f>
+        <f>'Workings'!$C$68</f>
       </c>
       <c r="D25" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$66,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$68,"")</f>
       </c>
     </row>
     <row r="26" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -6401,21 +6410,21 @@
         <v>183</v>
       </c>
       <c r="C26" s="32">
-        <f>IF('Workings'!$C$67&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$C$67,-3),0),"Covered: R "&amp;FIXED(ROUND('Workings'!$C$68,-3),0)&amp;" left over")</f>
+        <f>IF('Workings'!$C$69&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$C$69,-3),0),"Covered: R "&amp;FIXED(ROUND('Workings'!$C$70,-3),0)&amp;" left over")</f>
       </c>
       <c r="D26" s="32">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),IF('Workings'!$D$67&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$D$67,-3),0),"Covered: R "&amp;FIXED(ROUND('Workings'!$D$68,-3),0)&amp;" left over"),"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),IF('Workings'!$D$69&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$D$69,-3),0),"Covered: R "&amp;FIXED(ROUND('Workings'!$D$70,-3),0)&amp;" left over"),"")</f>
       </c>
     </row>
     <row r="27" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="29">
-        <f>IF(OR(SUM('Inputs'!$R$22:$R$39)&gt;0,'Inputs'!$C$14="Spouse"),"Left for your spouse and heirs","Left for your heirs")&amp;IF('Workings'!$C$67&gt;0,CHAR(10)&amp;"if they pay any shortfall in","")</f>
+        <f>IF(OR(SUM('Inputs'!$R$22:$R$39)&gt;0,'Inputs'!$C$14="Spouse"),"Left for your spouse and heirs","Left for your heirs")&amp;IF('Workings'!$C$69&gt;0,CHAR(10)&amp;"if they pay any shortfall in","")</f>
       </c>
       <c r="C27" s="15">
-        <f>'Workings'!$C$69</f>
+        <f>'Workings'!$C$71</f>
       </c>
       <c r="D27" s="33">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$69,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$71,"")</f>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
@@ -6431,7 +6440,7 @@
     </row>
     <row r="29" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="16">
-        <f>IF('Workings'!$C$48&lt;0,"The people you leave policies or bequests to directly pay R "&amp;FIXED(-'Workings'!$C$48,0)&amp;" of the estate duty themselves; your executor recovers it from them and it is not in the cost above. If it cannot be recovered, your estate pays it.","")</f>
+        <f>IF('Workings'!$C$50&lt;0,"The people you leave policies or bequests to directly pay R "&amp;FIXED(-'Workings'!$C$50,0)&amp;" of the estate duty themselves; your executor recovers it from them and it is not in the cost above. If it cannot be recovered, your estate pays it.","")</f>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -6452,14 +6461,14 @@
     </row>
     <row r="33" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="35">
-        <f>"2.  "&amp;IF('Workings'!$C$67&gt;0,"Decide how your executor will find the cash: life cover paid to your estate (see the life cover need page), "&amp;IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),"the Legacy Protection Plan, ","")&amp;"a property sold, or your heirs paying it in.","Keep enough cash for your executor: today there is enough, with about R "&amp;FIXED(ROUND('Workings'!$C$68,-3),0)&amp;" to spare.")</f>
+        <f>"2.  "&amp;IF('Workings'!$C$69&gt;0,"Decide how your executor will find the cash: life cover paid to your estate (see the life cover need page), "&amp;IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),"the Legacy Protection Plan, ","")&amp;"a property sold, or your heirs paying it in.","Keep enough cash for your executor: today there is enough, with about R "&amp;FIXED(ROUND('Workings'!$C$70,-3),0)&amp;" to spare.")</f>
       </c>
       <c r="C33" s="35"/>
       <c r="D33" s="35"/>
     </row>
     <row r="34" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="35">
-        <f>"3.  Remember that your savings are your executor's cash. Every R 1 spent from them "&amp;IF('Workings'!$C$67&gt;0,"adds about "&amp;ROUND(100*(1-'Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*IF('Workings'!$C$38&gt;0,1-'Inputs'!$C$128/100,1),0)&amp;" cents to the shortfall.","takes about "&amp;ROUND(100*(1-'Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*IF('Workings'!$C$38&gt;0,1-'Inputs'!$C$128/100,1),0)&amp;" cents off what your executor has spare.")</f>
+        <f>"3.  Remember that your savings are your executor's cash. Every R 1 spent from them "&amp;IF('Workings'!$C$69&gt;0,"adds about "&amp;ROUND(100*(1-'Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*IF('Workings'!$C$40&gt;0,1-'Inputs'!$C$128/100,1),0)&amp;" cents to the shortfall.","takes about "&amp;ROUND(100*(1-'Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*IF('Workings'!$C$40&gt;0,1-'Inputs'!$C$128/100,1),0)&amp;" cents off what your executor has spare.")</f>
       </c>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
@@ -6490,7 +6499,7 @@
   </mergeCells>
   <conditionalFormatting sqref="B10:D12">
     <cfRule type="expression" dxfId="20" priority="1">
-      <formula>'Workings'!$C$67=0</formula>
+      <formula>'Workings'!$C$69=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:D26">
@@ -6515,7 +6524,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D36"/>
+  <dimension ref="B1:D37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -6676,10 +6685,10 @@
         <v>222</v>
       </c>
       <c r="C19" s="15">
-        <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$E$59:$E$70,"No")</f>
+        <f>'Workings'!$C$24</f>
       </c>
       <c r="D19" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$E$59:$E$70,"No"),"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$C$24,"")</f>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
@@ -6687,39 +6696,39 @@
         <v>223</v>
       </c>
       <c r="C20" s="15">
+        <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$E$59:$E$70,"No")</f>
+      </c>
+      <c r="D20" s="15">
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$E$59:$E$70,"No"),"")</f>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="15">
         <f>SUM('Inputs'!$D$87:$D$94)</f>
       </c>
-      <c r="D20" s="15">
+      <c r="D21" s="15">
         <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),SUM('Inputs'!$D$87:$D$94),"")</f>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-    </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="C22" s="15">
-        <f>C15+SUM(C17:C20)</f>
-      </c>
-      <c r="D22" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),C15+SUM(C17:C20),"")</f>
-      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
         <v>226</v>
       </c>
       <c r="C23" s="15">
-        <f>'Workings'!$C$24</f>
+        <f>C15+SUM(C17:C21)</f>
       </c>
       <c r="D23" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$C$24,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),C15+SUM(C17:C21),"")</f>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
@@ -6727,39 +6736,39 @@
         <v>227</v>
       </c>
       <c r="C24" s="15">
-        <f>'Workings'!$C$62</f>
+        <f>'Workings'!$C$26</f>
       </c>
       <c r="D24" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$C$62,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$C$26,"")</f>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
+      <c r="C25" s="15">
+        <f>'Workings'!$C$64</f>
+      </c>
+      <c r="D25" s="15">
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$C$64,"")</f>
+      </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="C26" s="15">
-        <f>'Workings'!$C$54</f>
-      </c>
-      <c r="D26" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$54,"")</f>
-      </c>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
         <v>230</v>
       </c>
       <c r="C27" s="15">
-        <f>'Workings'!$C$53</f>
+        <f>'Workings'!$C$56</f>
       </c>
       <c r="D27" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$53,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$56,"")</f>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
@@ -6778,73 +6787,84 @@
         <v>232</v>
       </c>
       <c r="C29" s="15">
-        <f>'Workings'!$C$56</f>
+        <f>'Workings'!$C$57</f>
       </c>
       <c r="D29" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$56,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$57,"")</f>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="C30" s="15">
-        <f>'Workings'!$C$57</f>
+        <f>'Workings'!$C$58</f>
       </c>
       <c r="D30" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$57,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$58,"")</f>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>233</v>
+        <v>176</v>
       </c>
       <c r="C31" s="15">
-        <f>'Workings'!$C$58</f>
+        <f>'Workings'!$C$59</f>
       </c>
       <c r="D31" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$58,"")</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$59,"")</f>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="31">
-        <f>'Workings'!$C$59</f>
-      </c>
-      <c r="D32" s="31">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$59,"")</f>
+      <c r="C32" s="15">
+        <f>'Workings'!$C$60</f>
+      </c>
+      <c r="D32" s="15">
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$60,"")</f>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C33" s="15">
-        <f>-'Workings'!$C$60</f>
-      </c>
-      <c r="D33" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),-'Workings'!$D$60,"")</f>
+      <c r="B33" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" s="31">
+        <f>'Workings'!$C$61</f>
+      </c>
+      <c r="D33" s="31">
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$61,"")</f>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="C34" s="15">
-        <f>'Workings'!$C$62</f>
+        <f>-'Workings'!$C$62</f>
       </c>
       <c r="D34" s="15">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$62,"")</f>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="36" t="s">
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),-'Workings'!$D$62,"")</f>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
+      <c r="C35" s="15">
+        <f>'Workings'!$C$64</f>
+      </c>
+      <c r="D35" s="15">
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Workings'!$D$64,"")</f>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
@@ -6853,9 +6873,9 @@
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B37:D37"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.25" footer="0.3"/>
@@ -6871,7 +6891,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D71"/>
+  <dimension ref="B1:D73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -6896,23 +6916,23 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>174</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
@@ -6928,7 +6948,7 @@
     </row>
     <row r="9" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C9" s="19">
         <f>SUM('Inputs'!$M$22:$M$39)</f>
@@ -6939,7 +6959,7 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C10" s="19">
         <f>-SUM('Inputs'!$N$22:$N$39)</f>
@@ -6950,7 +6970,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C11" s="19">
         <f>-MIN('Inputs'!$C$131,MAX(0,C9+C10))</f>
@@ -6961,7 +6981,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="30" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C12" s="43">
         <f>MAX(0,C9+C10+C11)</f>
@@ -6983,7 +7003,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C14" s="19">
         <f>(INDEX('Inputs'!$D$134:$D$140,MATCH(C8+C13,'Inputs'!$C$134:$C$140,1))+INDEX('Inputs'!$E$134:$E$140,MATCH(C8+C13,'Inputs'!$C$134:$C$140,1))/100*((C8+C13)-INDEX('Inputs'!$C$134:$C$140,MATCH(C8+C13,'Inputs'!$C$134:$C$140,1))))</f>
@@ -6994,7 +7014,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C15" s="19">
         <f>-(INDEX('Inputs'!$D$134:$D$140,MATCH(C8,'Inputs'!$C$134:$C$140,1))+INDEX('Inputs'!$E$134:$E$140,MATCH(C8,'Inputs'!$C$134:$C$140,1))/100*((C8)-INDEX('Inputs'!$C$134:$C$140,MATCH(C8,'Inputs'!$C$134:$C$140,1))))</f>
@@ -7005,7 +7025,7 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C16" s="43">
         <f>IF(C12&gt;0,ROUND(C14+C15,2),0)</f>
@@ -7016,18 +7036,18 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>174</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C19" s="19">
         <f>ROUND(SUM('Inputs'!$D$22:$D$39),2)</f>
@@ -7038,7 +7058,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C20" s="19">
         <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Estate")</f>
@@ -7049,7 +7069,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="30" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C21" s="43">
         <f>C19+C20</f>
@@ -7060,358 +7080,358 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C22" s="19">
-        <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"&lt;&gt;Estate",'Inputs'!$E$59:$E$70,"&lt;&gt;No")</f>
+        <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"&lt;&gt;Estate",'Inputs'!$C$59:$C$70,"&lt;&gt;Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")</f>
       </c>
       <c r="D22" s="19">
-        <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"&lt;&gt;Estate",'Inputs'!$E$59:$E$70,"&lt;&gt;No")</f>
+        <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"&lt;&gt;Estate",'Inputs'!$C$59:$C$70,"&lt;&gt;Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")</f>
       </c>
     </row>
     <row r="23" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7">
-        <f>"Death income benefits, counted for estate duty (the insurer's value, or worked out at "&amp;FIXED('Inputs'!$H$122,1)&amp;"% a year)"</f>
+        <f>"Death income for a named person, counted for estate duty (the insurer's value, or worked out at "&amp;FIXED('Inputs'!$H$122,1)&amp;"% a year)"</f>
       </c>
       <c r="C23" s="19">
-        <f>SUM('Inputs'!$M$76:$M$81)</f>
+        <f>SUM('Inputs'!$O$76:$O$81)</f>
       </c>
       <c r="D23" s="19">
-        <f>SUM('Inputs'!$M$76:$M$81)</f>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="C24" s="43">
-        <f>C21+C22+C23</f>
-      </c>
-      <c r="D24" s="43">
-        <f>D21+D22+D23</f>
+        <f>SUM('Inputs'!$O$76:$O$81)</f>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" s="19">
+        <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)</f>
+      </c>
+      <c r="D24" s="19">
+        <f>SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)</f>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="19">
-        <f>-SUM('Inputs'!$D$45:$D$54)</f>
+        <f>-IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),C24,0)</f>
       </c>
       <c r="D25" s="19">
-        <f>-SUM('Inputs'!$D$45:$D$54)</f>
+        <f>-IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),D24,0)</f>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="C26" s="19">
-        <f>-'Inputs'!$C$123</f>
-      </c>
-      <c r="D26" s="19">
-        <f>-'Inputs'!$C$123</f>
+      <c r="B26" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="43">
+        <f>C21+C22+C23+C24+C25</f>
+      </c>
+      <c r="D26" s="43">
+        <f>D21+D22+D23+D24+D25</f>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C27" s="19">
-        <f>-'Inputs'!$C$122</f>
+        <f>-SUM('Inputs'!$D$45:$D$54)</f>
       </c>
       <c r="D27" s="19">
-        <f>-'Inputs'!$C$122</f>
+        <f>-SUM('Inputs'!$D$45:$D$54)</f>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C28" s="19">
-        <f>-'Inputs'!$C$124</f>
+        <f>-'Inputs'!$C$123</f>
       </c>
       <c r="D28" s="19">
-        <f>-'Inputs'!$C$124</f>
+        <f>-'Inputs'!$C$123</f>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" s="7">
-        <f>"Less executor's fees: "&amp;IF(ROUND('Inputs'!$C$120,0)='Inputs'!$C$120,FIXED('Inputs'!$C$120,0),IF(ROUND('Inputs'!$C$120,1)='Inputs'!$C$120,FIXED('Inputs'!$C$120,1),FIXED('Inputs'!$C$120,2)))&amp;"%"&amp;" plus VAT"&amp;IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0)," / Capital Legacy "&amp;IF(ROUND('Inputs'!$C$112,0)='Inputs'!$C$112,FIXED('Inputs'!$C$112,0),IF(ROUND('Inputs'!$C$112,1)='Inputs'!$C$112,FIXED('Inputs'!$C$112,1),FIXED('Inputs'!$C$112,2)))&amp;"%"&amp;" plus VAT","")</f>
+      <c r="B29" s="7" t="s">
+        <v>259</v>
       </c>
       <c r="C29" s="19">
-        <f>-ROUND('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100)*C21,2)</f>
+        <f>-'Inputs'!$C$122</f>
       </c>
       <c r="D29" s="19">
-        <f>-ROUND(IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Inputs'!$C$112,'Inputs'!$C$120)/100*(1+'Inputs'!$C$121/100)*D21,2)</f>
+        <f>-'Inputs'!$C$122</f>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C30" s="19">
-        <f>-SUM('Inputs'!$P$22:$P$39)</f>
+        <f>-'Inputs'!$C$124</f>
       </c>
       <c r="D30" s="19">
-        <f>-IF(AND(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),ISNUMBER('Inputs'!$C$113)),'Inputs'!$C$113,SUM('Inputs'!$P$22:$P$39))</f>
+        <f>-'Inputs'!$C$124</f>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
-        <v>259</v>
+      <c r="B31" s="7">
+        <f>"Less executor's fees: "&amp;IF(ROUND('Inputs'!$C$120,0)='Inputs'!$C$120,FIXED('Inputs'!$C$120,0),IF(ROUND('Inputs'!$C$120,1)='Inputs'!$C$120,FIXED('Inputs'!$C$120,1),FIXED('Inputs'!$C$120,2)))&amp;"%"&amp;" plus VAT"&amp;IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0)," / Capital Legacy "&amp;IF(ROUND('Inputs'!$C$112,0)='Inputs'!$C$112,FIXED('Inputs'!$C$112,0),IF(ROUND('Inputs'!$C$112,1)='Inputs'!$C$112,FIXED('Inputs'!$C$112,1),FIXED('Inputs'!$C$112,2)))&amp;"%"&amp;" plus VAT","")</f>
       </c>
       <c r="C31" s="19">
-        <f>-SUM('Inputs'!$Q$22:$Q$39)</f>
+        <f>-ROUND('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100)*C21,2)</f>
       </c>
       <c r="D31" s="19">
-        <f>-SUM('Inputs'!$Q$22:$Q$39)</f>
+        <f>-ROUND(IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),'Inputs'!$C$112,'Inputs'!$C$120)/100*(1+'Inputs'!$C$121/100)*D21,2)</f>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C32" s="19">
-        <f>-C16</f>
+        <f>-SUM('Inputs'!$P$22:$P$39)</f>
       </c>
       <c r="D32" s="19">
-        <f>-D16</f>
+        <f>-IF(AND(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),ISNUMBER('Inputs'!$C$113)),'Inputs'!$C$113,SUM('Inputs'!$P$22:$P$39))</f>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C33" s="19">
-        <f>ROUND(C21+C25-(-C26-C27-C28-C29-C30-C31-C32)-SUM('Inputs'!$R$22:$R$39)-SUM('Inputs'!$S$22:$S$39),2)</f>
+        <f>-SUM('Inputs'!$Q$22:$Q$39)</f>
       </c>
       <c r="D33" s="19">
-        <f>ROUND(D21+D25-(-D26-D27-D28-D29-D30-D31-D32)-SUM('Inputs'!$R$22:$R$39)-SUM('Inputs'!$S$22:$S$39),2)</f>
+        <f>-SUM('Inputs'!$Q$22:$Q$39)</f>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C34" s="44">
-        <f>IF(C33&lt;0,IF(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39)&gt;0,MAX(0,1+C33/(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39))),1),1)</f>
-      </c>
-      <c r="D34" s="44">
-        <f>IF(D33&lt;0,IF(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39)&gt;0,MAX(0,1+D33/(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39))),1),1)</f>
+        <v>263</v>
+      </c>
+      <c r="C34" s="19">
+        <f>-C16</f>
+      </c>
+      <c r="D34" s="19">
+        <f>-D16</f>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C35" s="19">
-        <f>-IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*C34+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,C33),0),0)</f>
+        <f>ROUND(C21+C27-(-C28-C29-C30-C31-C32-C33-C34)-SUM('Inputs'!$R$22:$R$39)-SUM('Inputs'!$S$22:$S$39),2)</f>
       </c>
       <c r="D35" s="19">
-        <f>-IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*D34+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,D33),0),0)</f>
+        <f>ROUND(D21+D27-(-D28-D29-D30-D31-D32-D33-D34)-SUM('Inputs'!$R$22:$R$39)-SUM('Inputs'!$S$22:$S$39),2)</f>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="C36" s="43">
-        <f>ROUND(C24+C25+C26+C27+C28+C29+C30+C31+C32+C35,2)</f>
-      </c>
-      <c r="D36" s="43">
-        <f>ROUND(D24+D25+D26+D27+D28+D29+D30+D31+D32+D35,2)</f>
+      <c r="B36" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C36" s="44">
+        <f>IF(C35&lt;0,IF(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39)&gt;0,MAX(0,1+C35/(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39))),1),1)</f>
+      </c>
+      <c r="D36" s="44">
+        <f>IF(D35&lt;0,IF(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39)&gt;0,MAX(0,1+D35/(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39))),1),1)</f>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C37" s="19">
+        <f>-IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*C36+IF('Inputs'!$C$14="Spouse",MAX(0,C35),0),0)</f>
+      </c>
+      <c r="D37" s="19">
+        <f>-IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*D36+IF('Inputs'!$C$14="Spouse",MAX(0,D35),0),0)</f>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="C38" s="43">
+        <f>ROUND(C26+C27+C28+C29+C30+C31+C32+C33+C34+C37,2)</f>
+      </c>
+      <c r="D38" s="43">
+        <f>ROUND(D26+D27+D28+D29+D30+D31+D32+D33+D34+D37,2)</f>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C39" s="19">
         <f>-'Inputs'!$C$127</f>
       </c>
-      <c r="D37" s="19">
+      <c r="D39" s="19">
         <f>-'Inputs'!$C$127</f>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="C38" s="19">
-        <f>MAX(0,C36+C37)</f>
-      </c>
-      <c r="D38" s="19">
-        <f>MAX(0,D36+D37)</f>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="C39" s="43">
-        <f>ROUND(IF(C38&lt;='Inputs'!$C$129,C38*'Inputs'!$C$128/100,'Inputs'!$C$129*'Inputs'!$C$128/100+(C38-'Inputs'!$C$129)*'Inputs'!$C$130/100),2)</f>
-      </c>
-      <c r="D39" s="43">
-        <f>ROUND(IF(D38&lt;='Inputs'!$C$129,D38*'Inputs'!$C$128/100,'Inputs'!$C$129*'Inputs'!$C$128/100+(D38-'Inputs'!$C$129)*'Inputs'!$C$130/100),2)</f>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C40" s="45">
-        <f>IF(C36&gt;0,C39/C36,0)</f>
-      </c>
-      <c r="D40" s="45">
-        <f>IF(D36&gt;0,D39/D36,0)</f>
-      </c>
-    </row>
-    <row r="41" ht="27" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="7">
-        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(1,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(1,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(1,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
-      </c>
-      <c r="C42" s="19">
-        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(1,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(1,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(1,'Inputs'!$R$76:$R$81,0)),"")))</f>
-      </c>
-      <c r="D42" s="19">
-        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(1,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(1,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(1,'Inputs'!$R$76:$R$81,0)),"")))</f>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="7">
-        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(2,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(2,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(2,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
-      </c>
-      <c r="C43" s="19">
-        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(2,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(2,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(2,'Inputs'!$R$76:$R$81,0)),"")))</f>
-      </c>
-      <c r="D43" s="19">
-        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(2,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(2,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(2,'Inputs'!$R$76:$R$81,0)),"")))</f>
+        <v>269</v>
+      </c>
+      <c r="C40" s="19">
+        <f>MAX(0,C38+C39)</f>
+      </c>
+      <c r="D40" s="19">
+        <f>MAX(0,D38+D39)</f>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" s="43">
+        <f>ROUND(IF(C40&lt;='Inputs'!$C$129,C40*'Inputs'!$C$128/100,'Inputs'!$C$129*'Inputs'!$C$128/100+(C40-'Inputs'!$C$129)*'Inputs'!$C$130/100),2)</f>
+      </c>
+      <c r="D41" s="43">
+        <f>ROUND(IF(D40&lt;='Inputs'!$C$129,D40*'Inputs'!$C$128/100,'Inputs'!$C$129*'Inputs'!$C$128/100+(D40-'Inputs'!$C$129)*'Inputs'!$C$130/100),2)</f>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C42" s="45">
+        <f>IF(C38&gt;0,C41/C38,0)</f>
+      </c>
+      <c r="D42" s="45">
+        <f>IF(D38&gt;0,D41/D38,0)</f>
+      </c>
+    </row>
+    <row r="43" ht="27" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="7">
-        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(3,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(3,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(3,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(1,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(1,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(1,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(1,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(1,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
       </c>
       <c r="C44" s="19">
-        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(3,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(3,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(3,'Inputs'!$R$76:$R$81,0)),"")))</f>
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(1,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(1,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(1,'Inputs'!$R$76:$R$81,0)),"")))</f>
       </c>
       <c r="D44" s="19">
-        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(3,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(3,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(3,'Inputs'!$R$76:$R$81,0)),"")))</f>
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(1,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(1,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(1,'Inputs'!$R$76:$R$81,0)),"")))</f>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="7">
-        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(4,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(4,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(4,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(2,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(2,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(2,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(2,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(2,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
       </c>
       <c r="C45" s="19">
-        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(4,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(4,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(4,'Inputs'!$R$76:$R$81,0)),"")))</f>
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(2,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(2,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(2,'Inputs'!$R$76:$R$81,0)),"")))</f>
       </c>
       <c r="D45" s="19">
-        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(4,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(4,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(4,'Inputs'!$R$76:$R$81,0)),"")))</f>
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(2,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(2,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(2,'Inputs'!$R$76:$R$81,0)),"")))</f>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="7">
-        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(5,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(5,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(5,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(3,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(3,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(3,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(3,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(3,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
       </c>
       <c r="C46" s="19">
-        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(5,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(5,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(5,'Inputs'!$R$76:$R$81,0)),"")))</f>
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(3,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(3,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(3,'Inputs'!$R$76:$R$81,0)),"")))</f>
       </c>
       <c r="D46" s="19">
-        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(5,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(5,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(5,'Inputs'!$R$76:$R$81,0)),"")))</f>
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(3,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(3,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(3,'Inputs'!$R$76:$R$81,0)),"")))</f>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="7">
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(4,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(4,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(4,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(4,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(4,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
+      </c>
+      <c r="C47" s="19">
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(4,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(4,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(4,'Inputs'!$R$76:$R$81,0)),"")))</f>
+      </c>
+      <c r="D47" s="19">
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(4,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(4,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(4,'Inputs'!$R$76:$R$81,0)),"")))</f>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="7">
+        <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(5,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(5,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(5,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(5,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(5,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
+      </c>
+      <c r="C48" s="19">
+        <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(5,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(5,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(5,'Inputs'!$R$76:$R$81,0)),"")))</f>
+      </c>
+      <c r="D48" s="19">
+        <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(5,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(5,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(5,'Inputs'!$R$76:$R$81,0)),"")))</f>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="7">
         <f>IFERROR("   Bequest: "&amp;INDEX('Inputs'!$B$22:$B$39,MATCH(6,'Inputs'!$X$22:$X$39,0))&amp;IF(INDEX('Inputs'!$I$22:$I$39,MATCH(6,'Inputs'!$X$22:$X$39,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$22:$I$39,MATCH(6,'Inputs'!$X$22:$X$39,0))&amp;")",""),IFERROR("   Policy: "&amp;INDEX('Inputs'!$B$59:$B$70,MATCH(6,'Inputs'!$O$59:$O$70,0))&amp;IF(INDEX('Inputs'!$I$59:$I$70,MATCH(6,'Inputs'!$O$59:$O$70,0))&lt;&gt;""," ("&amp;INDEX('Inputs'!$I$59:$I$70,MATCH(6,'Inputs'!$O$59:$O$70,0))&amp;")",""),IFERROR("   Death income: "&amp;INDEX('Inputs'!$B$76:$B$81,MATCH(6,'Inputs'!$R$76:$R$81,0))&amp;IF(INDEX('Inputs'!$G$76:$G$81,MATCH(6,'Inputs'!$R$76:$R$81,0))&lt;&gt;""," (for "&amp;INDEX('Inputs'!$G$76:$G$81,MATCH(6,'Inputs'!$R$76:$R$81,0))&amp;")",""),"")))</f>
       </c>
-      <c r="C47" s="19">
+      <c r="C49" s="19">
         <f>IFERROR(INDEX('Inputs'!$U$22:$U$39,MATCH(6,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$M$59:$M$70,MATCH(6,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$P$76:$P$81,MATCH(6,'Inputs'!$R$76:$R$81,0)),"")))</f>
       </c>
-      <c r="D47" s="19">
+      <c r="D49" s="19">
         <f>IFERROR(INDEX('Inputs'!$V$22:$V$39,MATCH(6,'Inputs'!$X$22:$X$39,0)),IFERROR(INDEX('Inputs'!$N$59:$N$70,MATCH(6,'Inputs'!$O$59:$O$70,0)),IFERROR(INDEX('Inputs'!$Q$76:$Q$81,MATCH(6,'Inputs'!$R$76:$R$81,0)),"")))</f>
       </c>
     </row>
-    <row r="48" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="C48" s="19">
+    <row r="50" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C50" s="19">
         <f>-(SUM('Inputs'!$M$59:$M$70)+SUM('Inputs'!$U$22:$U$39)+SUM('Inputs'!$P$76:$P$81))</f>
       </c>
-      <c r="D48" s="19">
+      <c r="D50" s="19">
         <f>-(SUM('Inputs'!$N$59:$N$70)+SUM('Inputs'!$V$22:$V$39)+SUM('Inputs'!$Q$76:$Q$81))</f>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B49" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="C49" s="43">
-        <f>C39+C48</f>
-      </c>
-      <c r="D49" s="43">
-        <f>D39+D48</f>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B52" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="C52" s="13" t="s">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="C51" s="43">
+        <f>C41+C50</f>
+      </c>
+      <c r="D51" s="43">
+        <f>D41+D50</f>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="D52" s="13" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B53" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C53" s="19">
-        <f>-(C26+C27+C28)</f>
-      </c>
-      <c r="D53" s="19">
-        <f>-(D26+D27+D28)</f>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B54" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C54" s="19">
-        <f>-C29</f>
-      </c>
-      <c r="D54" s="19">
-        <f>-D29</f>
+      <c r="D54" s="13" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
-        <v>272</v>
+        <v>178</v>
       </c>
       <c r="C55" s="19">
-        <f>-C30</f>
+        <f>-(C28+C29+C30)</f>
       </c>
       <c r="D55" s="19">
-        <f>-D30</f>
+        <f>-(D28+D29+D30)</f>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="C56" s="19">
         <f>-C31</f>
@@ -7422,73 +7442,73 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="7" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="C57" s="19">
-        <f>C16</f>
+        <f>-C32</f>
       </c>
       <c r="D57" s="19">
-        <f>D16</f>
+        <f>-D32</f>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="7" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="C58" s="19">
-        <f>C49</f>
+        <f>-C33</f>
       </c>
       <c r="D58" s="19">
-        <f>D49</f>
+        <f>-D33</f>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B59" s="30" t="s">
+      <c r="B59" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C59" s="19">
+        <f>C16</f>
+      </c>
+      <c r="D59" s="19">
+        <f>D16</f>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B60" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="C59" s="43">
-        <f>ROUND(SUM(C53:C58),2)</f>
-      </c>
-      <c r="D59" s="43">
-        <f>ROUND(SUM(D53:D58),2)</f>
-      </c>
-    </row>
-    <row r="60" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B60" s="7">
-        <f>"Less paid by the Legacy plan: "&amp;IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),FIXED(N('Inputs'!$C$114),0)&amp;"% of the executor's fee and conveyancing, up to R "&amp;FIXED(N('Inputs'!$C$115),2),"no quote entered")</f>
-      </c>
       <c r="C60" s="19">
-        <f>0</f>
+        <f>C51</f>
       </c>
       <c r="D60" s="19">
-        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),-ROUND(MIN(N('Inputs'!$C$114)/100*(D54+D55),N('Inputs'!$C$115)),2),0)</f>
+        <f>D51</f>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="30" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="C61" s="43">
-        <f>ROUND(C59+C60,2)</f>
+        <f>ROUND(SUM(C55:C60),2)</f>
       </c>
       <c r="D61" s="43">
-        <f>ROUND(D59+D60,2)</f>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B62" s="7" t="s">
-        <v>182</v>
+        <f>ROUND(SUM(D55:D60),2)</f>
+      </c>
+    </row>
+    <row r="62" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B62" s="7">
+        <f>"Less paid by the Legacy plan: "&amp;IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),FIXED(N('Inputs'!$C$114),0)&amp;"% of the executor's fee and conveyancing, up to R "&amp;FIXED(N('Inputs'!$C$115),2),"no quote entered")</f>
       </c>
       <c r="C62" s="19">
-        <f>-C25</f>
+        <f>0</f>
       </c>
       <c r="D62" s="19">
-        <f>-D25</f>
+        <f>IF(AND(ISNUMBER('Inputs'!$C$112),'Inputs'!$C$112&gt;0),-ROUND(MIN(N('Inputs'!$C$114)/100*(D56+D57),N('Inputs'!$C$115)),2),0)</f>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="30" t="s">
-        <v>189</v>
+        <v>276</v>
       </c>
       <c r="C63" s="43">
         <f>ROUND(C61+C62,2)</f>
@@ -7499,83 +7519,105 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="7" t="s">
-        <v>274</v>
+        <v>182</v>
       </c>
       <c r="C64" s="19">
+        <f>-C27</f>
+      </c>
+      <c r="D64" s="19">
+        <f>-D27</f>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="C65" s="43">
+        <f>ROUND(C63+C64,2)</f>
+      </c>
+      <c r="D65" s="43">
+        <f>ROUND(D63+D64,2)</f>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C66" s="19">
         <f>ROUND(SUM('Inputs'!$O$22:$O$39),2)</f>
       </c>
-      <c r="D64" s="19">
+      <c r="D66" s="19">
         <f>ROUND(SUM('Inputs'!$O$22:$O$39),2)</f>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B65" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C65" s="19">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B67" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C67" s="19">
         <f>C20</f>
       </c>
-      <c r="D65" s="19">
+      <c r="D67" s="19">
         <f>D20</f>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B66" s="30" t="s">
+    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B68" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="C66" s="43">
-        <f>C64+C65</f>
-      </c>
-      <c r="D66" s="43">
-        <f>D64+D65</f>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B67" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="C67" s="43">
-        <f>ROUND(MAX(0,C63-C66),2)</f>
-      </c>
-      <c r="D67" s="43">
-        <f>ROUND(MAX(0,D63-D66),2)</f>
-      </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B68" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C68" s="19">
-        <f>ROUND(MAX(0,C66-C63),2)</f>
-      </c>
-      <c r="D68" s="19">
-        <f>ROUND(MAX(0,D66-D63),2)</f>
-      </c>
-    </row>
-    <row r="69" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C68" s="43">
+        <f>C66+C67</f>
+      </c>
+      <c r="D68" s="43">
+        <f>D66+D67</f>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C69" s="43">
-        <f>ROUND(C21-C63,2)</f>
+        <f>ROUND(MAX(0,C65-C68),2)</f>
       </c>
       <c r="D69" s="43">
-        <f>ROUND(D21-D63,2)</f>
-      </c>
-    </row>
-    <row r="71" ht="52" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B71" s="36">
+        <f>ROUND(MAX(0,D65-D68),2)</f>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B70" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C70" s="19">
+        <f>ROUND(MAX(0,C68-C65),2)</f>
+      </c>
+      <c r="D70" s="19">
+        <f>ROUND(MAX(0,D68-D65),2)</f>
+      </c>
+    </row>
+    <row r="71" ht="27" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="C71" s="43">
+        <f>ROUND(C21-C65,2)</f>
+      </c>
+      <c r="D71" s="43">
+        <f>ROUND(D21-D65,2)</f>
+      </c>
+    </row>
+    <row r="73" ht="52" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B73" s="36">
         <f>"Our standard assumptions: executor "&amp;IF(ROUND('Inputs'!$C$120,0)='Inputs'!$C$120,FIXED('Inputs'!$C$120,0),IF(ROUND('Inputs'!$C$120,1)='Inputs'!$C$120,FIXED('Inputs'!$C$120,1),FIXED('Inputs'!$C$120,2)))&amp;"%"&amp;" plus VAT unless Capital Legacy acts; Master's fees R "&amp;FIXED('Inputs'!$C$122,0)&amp;"; funeral R "&amp;FIXED('Inputs'!$C$123,0)&amp;"; sundries R "&amp;FIXED('Inputs'!$C$124,0)&amp;"; property transfer costs "&amp;IF(ROUND('Inputs'!$C$125,0)='Inputs'!$C$125,FIXED('Inputs'!$C$125,0),IF(ROUND('Inputs'!$C$125,1)='Inputs'!$C$125,FIXED('Inputs'!$C$125,1),FIXED('Inputs'!$C$125,2)))&amp;"%"&amp;" of value; agent's commission "&amp;IF(ROUND('Inputs'!$C$126,0)='Inputs'!$C$126,FIXED('Inputs'!$C$126,0),IF(ROUND('Inputs'!$C$126,1)='Inputs'!$C$126,FIXED('Inputs'!$C$126,1),FIXED('Inputs'!$C$126,2)))&amp;"%"&amp;" plus VAT on a property sold; estate duty "&amp;IF(ROUND('Inputs'!$C$128,0)='Inputs'!$C$128,FIXED('Inputs'!$C$128,0),IF(ROUND('Inputs'!$C$128,1)='Inputs'!$C$128,FIXED('Inputs'!$C$128,1),FIXED('Inputs'!$C$128,2)))&amp;"%"&amp;" above R "&amp;FIXED('Inputs'!$C$127,0)&amp;"; 2027 tax tables. Capital gains tax on death (s.9HA): everything treated as sold at its value; assets left to a spouse roll over (no tax now). The Capital Legacy fees stay deductible for estate duty, although the plan pays them."</f>
       </c>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
   <mergeCells count="3">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B73:D73"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.6" header="0.25" footer="0.3"/>
@@ -7612,27 +7654,27 @@
         <f>N('Inputs'!$D$100)</f>
       </c>
       <c r="I3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C4">
         <f>IF($C$3&gt;=75,'Inputs'!$H$131,IF($C$3&gt;=65,'Inputs'!$H$130,'Inputs'!$H$124))</f>
@@ -7658,7 +7700,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C5">
         <f>N('Inputs'!$I$100)</f>
@@ -7684,7 +7726,7 @@
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C6">
         <f>IF($C$2="",0,N('Inputs'!$F$100))</f>
@@ -7710,7 +7752,7 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C7">
         <f>N('Inputs'!$E$100)</f>
@@ -7736,7 +7778,7 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C8">
         <f>IF('Inputs'!$G$100="",'Inputs'!$H$129/100,'Inputs'!$G$100/100)</f>
@@ -7762,7 +7804,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C9">
         <f>IF('Inputs'!$H$100="Yes",1,0)</f>
@@ -7788,7 +7830,7 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C10">
         <f>IF($C$2="",0,N('Inputs'!$J$100))</f>
@@ -7814,7 +7856,7 @@
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C11">
         <f>ROUND(Q4,2)</f>
@@ -7840,7 +7882,7 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C12">
         <f>ROUND(SUM($Q$4:$Q$53),2)</f>
@@ -7866,7 +7908,7 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C13">
         <f>IF($C$9&lt;&gt;1,0,ROUND(IF($C$14=0,SUM($J$4:$J$53),(1-(1+$C$14)^-1)/(1-(1+$C$14)^(-1/12))/12*SUMPRODUCT($J$4:$J$53,(1+$C$14)^(-$I$4:$I$53)))-IF(($C$14+'Inputs'!$H$123/100)=0,SUM($J$4:$J$53),(1-(1+($C$14+'Inputs'!$H$123/100))^-1)/(1-(1+($C$14+'Inputs'!$H$123/100))^(-1/12))/12*SUMPRODUCT($J$4:$J$53,(1+($C$14+'Inputs'!$H$123/100))^(-$I$4:$I$53))),2))</f>
@@ -7892,7 +7934,7 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C14">
         <f>IF($C$9=1,'Needs calc'!$C$43,0)</f>
@@ -7918,7 +7960,7 @@
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C15">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$2)*($C$2&lt;&gt;"")*('Inputs'!$F$76:$F$81&gt;0)*'Inputs'!$D$76:$D$81)</f>
@@ -7944,7 +7986,7 @@
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C16">
         <f>IF($C$6&gt;0,$C$7-J4/12,0)</f>
@@ -7970,7 +8012,7 @@
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C17">
         <f>SUMPRODUCT(MAX(('Inputs'!$G$76:$G$81=$C$2)*($C$2&lt;&gt;"")*'Inputs'!$F$76:$F$81))</f>
@@ -7996,7 +8038,7 @@
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C18">
         <f>SUM($J$4:$J$53)</f>
@@ -8022,7 +8064,7 @@
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C19">
         <f>IF('Needs calc'!$C$45&gt;0,IF(N('Inputs'!$E$100)&gt;0,IF('Needs years'!$C$15&lt;=0,IF('Needs years'!$C$10&lt;=0,'Inputs'!$B$100&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$46,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$100,-2),0)&amp;" you want. ",IF('Needs calc'!$C$40&gt;='Needs years'!$C$10,'Inputs'!$B$100&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$46,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$100,-2),0)&amp;" you want, after the R "&amp;FIXED(ROUND('Needs years'!$C$10,-3),0)&amp;" once-off. ",'Inputs'!$B$100&amp;" would have "&amp;IF('Needs calc'!$C$40&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$40,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$10,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$46,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$100,-2),0)&amp;". ")),IF('Needs years'!$C$18&lt;=0,IF('Needs years'!$C$10&gt;0,'Inputs'!$B$100&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$100,-2),0)&amp;" a month you want"&amp;", but "&amp;'Inputs'!$B$100&amp;" would have "&amp;IF('Needs calc'!$C$40&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$40,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$10,-3),0)&amp;" once-off you want for them. ",'Inputs'!$B$100&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$100,-2),0)&amp;" a month you want"&amp;", but the estate duty on it, about R "&amp;FIXED(ROUND('Needs years'!$C$21,-3),0)&amp;", leaves "&amp;'Inputs'!$B$100&amp;" short. "),IF('Needs years'!$J$4&lt;=0,'Inputs'!$B$100&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$100,-2),0)&amp;" a month you want"&amp;" for "&amp;IF('Needs years'!$C$20=1,"the first year","the first "&amp;'Needs years'!$C$20&amp;" years")&amp;"; after that "&amp;'Inputs'!$B$100&amp;" would be short"&amp;IF(AND('Needs years'!$C$10&gt;0,'Needs calc'!$C$40&lt;'Needs years'!$C$10),", and would have "&amp;IF('Needs calc'!$C$40&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$40,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$10,-3),0)&amp;" once-off","")&amp;". ",IF('Needs years'!$C$10&lt;=0,'Inputs'!$B$100&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$46,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$100,-2),0)&amp;" you want, part of it from the death income, and less once it stops. ",IF('Needs calc'!$C$40&gt;='Needs years'!$C$10,'Inputs'!$B$100&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$46,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$100,-2),0)&amp;" you want, part of it from the death income, and less once it stops, after the R "&amp;FIXED(ROUND('Needs years'!$C$10,-3),0)&amp;" once-off. ",'Inputs'!$B$100&amp;" would have "&amp;IF('Needs calc'!$C$40&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$40,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$10,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$46,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$100,-2),0)&amp;", part of it from the death income, and less once it stops. "))))),'Inputs'!$B$100&amp;" would have "&amp;IF('Needs calc'!$C$40&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$40,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$10,-3),0)&amp;" you want to leave them. "),"")</f>
@@ -8048,7 +8090,7 @@
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C20">
         <f>IFERROR(MATCH(1,$L$4:$L$53,0)-1,$C$6)</f>
@@ -8074,7 +8116,7 @@
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C21">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$2)*($C$2&lt;&gt;"")*'Inputs'!$P$76:$P$81)</f>
@@ -8754,27 +8796,27 @@
         <f>N('Inputs'!$D$101)</f>
       </c>
       <c r="I59" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J59" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K59" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L59" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P59" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q59" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C60">
         <f>IF($C$59&gt;=75,'Inputs'!$H$131,IF($C$59&gt;=65,'Inputs'!$H$130,'Inputs'!$H$124))</f>
@@ -8800,7 +8842,7 @@
     </row>
     <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C61">
         <f>N('Inputs'!$I$101)</f>
@@ -8826,7 +8868,7 @@
     </row>
     <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C62">
         <f>IF($C$58="",0,N('Inputs'!$F$101))</f>
@@ -8852,7 +8894,7 @@
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C63">
         <f>N('Inputs'!$E$101)</f>
@@ -8878,7 +8920,7 @@
     </row>
     <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C64">
         <f>IF('Inputs'!$G$101="",'Inputs'!$H$129/100,'Inputs'!$G$101/100)</f>
@@ -8904,7 +8946,7 @@
     </row>
     <row r="65" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C65">
         <f>IF('Inputs'!$H$101="Yes",1,0)</f>
@@ -8930,7 +8972,7 @@
     </row>
     <row r="66" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C66">
         <f>IF($C$58="",0,N('Inputs'!$J$101))</f>
@@ -8956,7 +8998,7 @@
     </row>
     <row r="67" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C67">
         <f>ROUND(Q60,2)</f>
@@ -8982,7 +9024,7 @@
     </row>
     <row r="68" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C68">
         <f>ROUND(SUM($Q$60:$Q$109),2)</f>
@@ -9008,7 +9050,7 @@
     </row>
     <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C69">
         <f>IF($C$65&lt;&gt;1,0,ROUND(IF($C$70=0,SUM($J$60:$J$109),(1-(1+$C$70)^-1)/(1-(1+$C$70)^(-1/12))/12*SUMPRODUCT($J$60:$J$109,(1+$C$70)^(-$I$60:$I$109)))-IF(($C$70+'Inputs'!$H$123/100)=0,SUM($J$60:$J$109),(1-(1+($C$70+'Inputs'!$H$123/100))^-1)/(1-(1+($C$70+'Inputs'!$H$123/100))^(-1/12))/12*SUMPRODUCT($J$60:$J$109,(1+($C$70+'Inputs'!$H$123/100))^(-$I$60:$I$109))),2))</f>
@@ -9034,7 +9076,7 @@
     </row>
     <row r="70" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C70">
         <f>IF($C$65=1,'Needs calc'!$C$50,0)</f>
@@ -9060,7 +9102,7 @@
     </row>
     <row r="71" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C71">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$58)*($C$58&lt;&gt;"")*('Inputs'!$F$76:$F$81&gt;0)*'Inputs'!$D$76:$D$81)</f>
@@ -9086,7 +9128,7 @@
     </row>
     <row r="72" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C72">
         <f>IF($C$62&gt;0,$C$63-J60/12,0)</f>
@@ -9112,7 +9154,7 @@
     </row>
     <row r="73" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C73">
         <f>SUMPRODUCT(MAX(('Inputs'!$G$76:$G$81=$C$58)*($C$58&lt;&gt;"")*'Inputs'!$F$76:$F$81))</f>
@@ -9138,7 +9180,7 @@
     </row>
     <row r="74" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C74">
         <f>SUM($J$60:$J$109)</f>
@@ -9164,7 +9206,7 @@
     </row>
     <row r="75" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C75">
         <f>IF('Needs calc'!$C$52&gt;0,IF(N('Inputs'!$E$101)&gt;0,IF('Needs years'!$C$71&lt;=0,IF('Needs years'!$C$66&lt;=0,'Inputs'!$B$101&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$53,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$101,-2),0)&amp;" you want. ",IF('Needs calc'!$C$47&gt;='Needs years'!$C$66,'Inputs'!$B$101&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$53,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$101,-2),0)&amp;" you want, after the R "&amp;FIXED(ROUND('Needs years'!$C$66,-3),0)&amp;" once-off. ",'Inputs'!$B$101&amp;" would have "&amp;IF('Needs calc'!$C$47&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$47,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$66,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$53,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$101,-2),0)&amp;". ")),IF('Needs years'!$C$74&lt;=0,IF('Needs years'!$C$66&gt;0,'Inputs'!$B$101&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$101,-2),0)&amp;" a month you want"&amp;", but "&amp;'Inputs'!$B$101&amp;" would have "&amp;IF('Needs calc'!$C$47&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$47,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$66,-3),0)&amp;" once-off you want for them. ",'Inputs'!$B$101&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$101,-2),0)&amp;" a month you want"&amp;", but the estate duty on it, about R "&amp;FIXED(ROUND('Needs years'!$C$77,-3),0)&amp;", leaves "&amp;'Inputs'!$B$101&amp;" short. "),IF('Needs years'!$J$60&lt;=0,'Inputs'!$B$101&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$101,-2),0)&amp;" a month you want"&amp;" for "&amp;IF('Needs years'!$C$76=1,"the first year","the first "&amp;'Needs years'!$C$76&amp;" years")&amp;"; after that "&amp;'Inputs'!$B$101&amp;" would be short"&amp;IF(AND('Needs years'!$C$66&gt;0,'Needs calc'!$C$47&lt;'Needs years'!$C$66),", and would have "&amp;IF('Needs calc'!$C$47&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$47,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$66,-3),0)&amp;" once-off","")&amp;". ",IF('Needs years'!$C$66&lt;=0,'Inputs'!$B$101&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$53,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$101,-2),0)&amp;" you want, part of it from the death income, and less once it stops. ",IF('Needs calc'!$C$47&gt;='Needs years'!$C$66,'Inputs'!$B$101&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$53,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$101,-2),0)&amp;" you want, part of it from the death income, and less once it stops, after the R "&amp;FIXED(ROUND('Needs years'!$C$66,-3),0)&amp;" once-off. ",'Inputs'!$B$101&amp;" would have "&amp;IF('Needs calc'!$C$47&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$47,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$66,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$53,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$101,-2),0)&amp;", part of it from the death income, and less once it stops. "))))),'Inputs'!$B$101&amp;" would have "&amp;IF('Needs calc'!$C$47&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$47,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$66,-3),0)&amp;" you want to leave them. "),"")</f>
@@ -9190,7 +9232,7 @@
     </row>
     <row r="76" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C76">
         <f>IFERROR(MATCH(1,$L$60:$L$109,0)-1,$C$62)</f>
@@ -9216,7 +9258,7 @@
     </row>
     <row r="77" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C77">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$58)*($C$58&lt;&gt;"")*'Inputs'!$P$76:$P$81)</f>
@@ -9896,27 +9938,27 @@
         <f>N('Inputs'!$D$102)</f>
       </c>
       <c r="I115" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J115" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K115" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L115" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P115" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q115" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="116" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C116">
         <f>IF($C$115&gt;=75,'Inputs'!$H$131,IF($C$115&gt;=65,'Inputs'!$H$130,'Inputs'!$H$124))</f>
@@ -9942,7 +9984,7 @@
     </row>
     <row r="117" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C117">
         <f>N('Inputs'!$I$102)</f>
@@ -9968,7 +10010,7 @@
     </row>
     <row r="118" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C118">
         <f>IF($C$114="",0,N('Inputs'!$F$102))</f>
@@ -9994,7 +10036,7 @@
     </row>
     <row r="119" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C119">
         <f>N('Inputs'!$E$102)</f>
@@ -10020,7 +10062,7 @@
     </row>
     <row r="120" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C120">
         <f>IF('Inputs'!$G$102="",'Inputs'!$H$129/100,'Inputs'!$G$102/100)</f>
@@ -10046,7 +10088,7 @@
     </row>
     <row r="121" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C121">
         <f>IF('Inputs'!$H$102="Yes",1,0)</f>
@@ -10072,7 +10114,7 @@
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C122">
         <f>IF($C$114="",0,N('Inputs'!$J$102))</f>
@@ -10098,7 +10140,7 @@
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C123">
         <f>ROUND(Q116,2)</f>
@@ -10124,7 +10166,7 @@
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C124">
         <f>ROUND(SUM($Q$116:$Q$165),2)</f>
@@ -10150,7 +10192,7 @@
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C125">
         <f>IF($C$121&lt;&gt;1,0,ROUND(IF($C$126=0,SUM($J$116:$J$165),(1-(1+$C$126)^-1)/(1-(1+$C$126)^(-1/12))/12*SUMPRODUCT($J$116:$J$165,(1+$C$126)^(-$I$116:$I$165)))-IF(($C$126+'Inputs'!$H$123/100)=0,SUM($J$116:$J$165),(1-(1+($C$126+'Inputs'!$H$123/100))^-1)/(1-(1+($C$126+'Inputs'!$H$123/100))^(-1/12))/12*SUMPRODUCT($J$116:$J$165,(1+($C$126+'Inputs'!$H$123/100))^(-$I$116:$I$165))),2))</f>
@@ -10176,7 +10218,7 @@
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C126">
         <f>IF($C$121=1,'Needs calc'!$C$57,0)</f>
@@ -10202,7 +10244,7 @@
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C127">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$114)*($C$114&lt;&gt;"")*('Inputs'!$F$76:$F$81&gt;0)*'Inputs'!$D$76:$D$81)</f>
@@ -10228,7 +10270,7 @@
     </row>
     <row r="128" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C128">
         <f>IF($C$118&gt;0,$C$119-J116/12,0)</f>
@@ -10254,7 +10296,7 @@
     </row>
     <row r="129" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C129">
         <f>SUMPRODUCT(MAX(('Inputs'!$G$76:$G$81=$C$114)*($C$114&lt;&gt;"")*'Inputs'!$F$76:$F$81))</f>
@@ -10280,7 +10322,7 @@
     </row>
     <row r="130" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C130">
         <f>SUM($J$116:$J$165)</f>
@@ -10306,7 +10348,7 @@
     </row>
     <row r="131" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C131">
         <f>IF('Needs calc'!$C$59&gt;0,IF(N('Inputs'!$E$102)&gt;0,IF('Needs years'!$C$127&lt;=0,IF('Needs years'!$C$122&lt;=0,'Inputs'!$B$102&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$60,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$102,-2),0)&amp;" you want. ",IF('Needs calc'!$C$54&gt;='Needs years'!$C$122,'Inputs'!$B$102&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$60,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$102,-2),0)&amp;" you want, after the R "&amp;FIXED(ROUND('Needs years'!$C$122,-3),0)&amp;" once-off. ",'Inputs'!$B$102&amp;" would have "&amp;IF('Needs calc'!$C$54&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$54,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$122,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$60,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$102,-2),0)&amp;". ")),IF('Needs years'!$C$130&lt;=0,IF('Needs years'!$C$122&gt;0,'Inputs'!$B$102&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$102,-2),0)&amp;" a month you want"&amp;", but "&amp;'Inputs'!$B$102&amp;" would have "&amp;IF('Needs calc'!$C$54&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$54,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$122,-3),0)&amp;" once-off you want for them. ",'Inputs'!$B$102&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$102,-2),0)&amp;" a month you want"&amp;", but the estate duty on it, about R "&amp;FIXED(ROUND('Needs years'!$C$133,-3),0)&amp;", leaves "&amp;'Inputs'!$B$102&amp;" short. "),IF('Needs years'!$J$116&lt;=0,'Inputs'!$B$102&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$102,-2),0)&amp;" a month you want"&amp;" for "&amp;IF('Needs years'!$C$132=1,"the first year","the first "&amp;'Needs years'!$C$132&amp;" years")&amp;"; after that "&amp;'Inputs'!$B$102&amp;" would be short"&amp;IF(AND('Needs years'!$C$122&gt;0,'Needs calc'!$C$54&lt;'Needs years'!$C$122),", and would have "&amp;IF('Needs calc'!$C$54&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$54,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$122,-3),0)&amp;" once-off","")&amp;". ",IF('Needs years'!$C$122&lt;=0,'Inputs'!$B$102&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$60,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$102,-2),0)&amp;" you want, part of it from the death income, and less once it stops. ",IF('Needs calc'!$C$54&gt;='Needs years'!$C$122,'Inputs'!$B$102&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$60,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$102,-2),0)&amp;" you want, part of it from the death income, and less once it stops, after the R "&amp;FIXED(ROUND('Needs years'!$C$122,-3),0)&amp;" once-off. ",'Inputs'!$B$102&amp;" would have "&amp;IF('Needs calc'!$C$54&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$54,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$122,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$60,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$102,-2),0)&amp;", part of it from the death income, and less once it stops. "))))),'Inputs'!$B$102&amp;" would have "&amp;IF('Needs calc'!$C$54&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$54,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$122,-3),0)&amp;" you want to leave them. "),"")</f>
@@ -10332,7 +10374,7 @@
     </row>
     <row r="132" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C132">
         <f>IFERROR(MATCH(1,$L$116:$L$165,0)-1,$C$118)</f>
@@ -10358,7 +10400,7 @@
     </row>
     <row r="133" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C133">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$114)*($C$114&lt;&gt;"")*'Inputs'!$P$76:$P$81)</f>
@@ -11038,27 +11080,27 @@
         <f>N('Inputs'!$D$103)</f>
       </c>
       <c r="I171" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J171" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K171" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L171" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P171" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q171" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="172" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C172">
         <f>IF($C$171&gt;=75,'Inputs'!$H$131,IF($C$171&gt;=65,'Inputs'!$H$130,'Inputs'!$H$124))</f>
@@ -11084,7 +11126,7 @@
     </row>
     <row r="173" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C173">
         <f>N('Inputs'!$I$103)</f>
@@ -11110,7 +11152,7 @@
     </row>
     <row r="174" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C174">
         <f>IF($C$170="",0,N('Inputs'!$F$103))</f>
@@ -11136,7 +11178,7 @@
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C175">
         <f>N('Inputs'!$E$103)</f>
@@ -11162,7 +11204,7 @@
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C176">
         <f>IF('Inputs'!$G$103="",'Inputs'!$H$129/100,'Inputs'!$G$103/100)</f>
@@ -11188,7 +11230,7 @@
     </row>
     <row r="177" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C177">
         <f>IF('Inputs'!$H$103="Yes",1,0)</f>
@@ -11214,7 +11256,7 @@
     </row>
     <row r="178" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C178">
         <f>IF($C$170="",0,N('Inputs'!$J$103))</f>
@@ -11240,7 +11282,7 @@
     </row>
     <row r="179" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C179">
         <f>ROUND(Q172,2)</f>
@@ -11266,7 +11308,7 @@
     </row>
     <row r="180" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C180">
         <f>ROUND(SUM($Q$172:$Q$221),2)</f>
@@ -11292,7 +11334,7 @@
     </row>
     <row r="181" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C181">
         <f>IF($C$177&lt;&gt;1,0,ROUND(IF($C$182=0,SUM($J$172:$J$221),(1-(1+$C$182)^-1)/(1-(1+$C$182)^(-1/12))/12*SUMPRODUCT($J$172:$J$221,(1+$C$182)^(-$I$172:$I$221)))-IF(($C$182+'Inputs'!$H$123/100)=0,SUM($J$172:$J$221),(1-(1+($C$182+'Inputs'!$H$123/100))^-1)/(1-(1+($C$182+'Inputs'!$H$123/100))^(-1/12))/12*SUMPRODUCT($J$172:$J$221,(1+($C$182+'Inputs'!$H$123/100))^(-$I$172:$I$221))),2))</f>
@@ -11318,7 +11360,7 @@
     </row>
     <row r="182" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C182">
         <f>IF($C$177=1,'Needs calc'!$C$64,0)</f>
@@ -11344,7 +11386,7 @@
     </row>
     <row r="183" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C183">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$170)*($C$170&lt;&gt;"")*('Inputs'!$F$76:$F$81&gt;0)*'Inputs'!$D$76:$D$81)</f>
@@ -11370,7 +11412,7 @@
     </row>
     <row r="184" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C184">
         <f>IF($C$174&gt;0,$C$175-J172/12,0)</f>
@@ -11396,7 +11438,7 @@
     </row>
     <row r="185" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C185">
         <f>SUMPRODUCT(MAX(('Inputs'!$G$76:$G$81=$C$170)*($C$170&lt;&gt;"")*'Inputs'!$F$76:$F$81))</f>
@@ -11422,7 +11464,7 @@
     </row>
     <row r="186" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C186">
         <f>SUM($J$172:$J$221)</f>
@@ -11448,7 +11490,7 @@
     </row>
     <row r="187" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C187">
         <f>IF('Needs calc'!$C$66&gt;0,IF(N('Inputs'!$E$103)&gt;0,IF('Needs years'!$C$183&lt;=0,IF('Needs years'!$C$178&lt;=0,'Inputs'!$B$103&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$67,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$103,-2),0)&amp;" you want. ",IF('Needs calc'!$C$61&gt;='Needs years'!$C$178,'Inputs'!$B$103&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$67,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$103,-2),0)&amp;" you want, after the R "&amp;FIXED(ROUND('Needs years'!$C$178,-3),0)&amp;" once-off. ",'Inputs'!$B$103&amp;" would have "&amp;IF('Needs calc'!$C$61&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$61,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$178,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$67,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$103,-2),0)&amp;". ")),IF('Needs years'!$C$186&lt;=0,IF('Needs years'!$C$178&gt;0,'Inputs'!$B$103&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$103,-2),0)&amp;" a month you want"&amp;", but "&amp;'Inputs'!$B$103&amp;" would have "&amp;IF('Needs calc'!$C$61&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$61,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$178,-3),0)&amp;" once-off you want for them. ",'Inputs'!$B$103&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$103,-2),0)&amp;" a month you want"&amp;", but the estate duty on it, about R "&amp;FIXED(ROUND('Needs years'!$C$189,-3),0)&amp;", leaves "&amp;'Inputs'!$B$103&amp;" short. "),IF('Needs years'!$J$172&lt;=0,'Inputs'!$B$103&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$103,-2),0)&amp;" a month you want"&amp;" for "&amp;IF('Needs years'!$C$188=1,"the first year","the first "&amp;'Needs years'!$C$188&amp;" years")&amp;"; after that "&amp;'Inputs'!$B$103&amp;" would be short"&amp;IF(AND('Needs years'!$C$178&gt;0,'Needs calc'!$C$61&lt;'Needs years'!$C$178),", and would have "&amp;IF('Needs calc'!$C$61&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$61,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$178,-3),0)&amp;" once-off","")&amp;". ",IF('Needs years'!$C$178&lt;=0,'Inputs'!$B$103&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$67,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$103,-2),0)&amp;" you want, part of it from the death income, and less once it stops. ",IF('Needs calc'!$C$61&gt;='Needs years'!$C$178,'Inputs'!$B$103&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$67,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$103,-2),0)&amp;" you want, part of it from the death income, and less once it stops, after the R "&amp;FIXED(ROUND('Needs years'!$C$178,-3),0)&amp;" once-off. ",'Inputs'!$B$103&amp;" would have "&amp;IF('Needs calc'!$C$61&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$61,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$178,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$67,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$103,-2),0)&amp;", part of it from the death income, and less once it stops. "))))),'Inputs'!$B$103&amp;" would have "&amp;IF('Needs calc'!$C$61&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$61,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$178,-3),0)&amp;" you want to leave them. "),"")</f>
@@ -11474,7 +11516,7 @@
     </row>
     <row r="188" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C188">
         <f>IFERROR(MATCH(1,$L$172:$L$221,0)-1,$C$174)</f>
@@ -11500,7 +11542,7 @@
     </row>
     <row r="189" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C189">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$170)*($C$170&lt;&gt;"")*'Inputs'!$P$76:$P$81)</f>
@@ -12180,27 +12222,27 @@
         <f>N('Inputs'!$D$104)</f>
       </c>
       <c r="I227" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J227" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K227" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L227" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P227" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q227" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="228" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C228">
         <f>IF($C$227&gt;=75,'Inputs'!$H$131,IF($C$227&gt;=65,'Inputs'!$H$130,'Inputs'!$H$124))</f>
@@ -12226,7 +12268,7 @@
     </row>
     <row r="229" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C229">
         <f>N('Inputs'!$I$104)</f>
@@ -12252,7 +12294,7 @@
     </row>
     <row r="230" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C230">
         <f>IF($C$226="",0,N('Inputs'!$F$104))</f>
@@ -12278,7 +12320,7 @@
     </row>
     <row r="231" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C231">
         <f>N('Inputs'!$E$104)</f>
@@ -12304,7 +12346,7 @@
     </row>
     <row r="232" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C232">
         <f>IF('Inputs'!$G$104="",'Inputs'!$H$129/100,'Inputs'!$G$104/100)</f>
@@ -12330,7 +12372,7 @@
     </row>
     <row r="233" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C233">
         <f>IF('Inputs'!$H$104="Yes",1,0)</f>
@@ -12356,7 +12398,7 @@
     </row>
     <row r="234" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C234">
         <f>IF($C$226="",0,N('Inputs'!$J$104))</f>
@@ -12382,7 +12424,7 @@
     </row>
     <row r="235" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C235">
         <f>ROUND(Q228,2)</f>
@@ -12408,7 +12450,7 @@
     </row>
     <row r="236" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C236">
         <f>ROUND(SUM($Q$228:$Q$277),2)</f>
@@ -12434,7 +12476,7 @@
     </row>
     <row r="237" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C237">
         <f>IF($C$233&lt;&gt;1,0,ROUND(IF($C$238=0,SUM($J$228:$J$277),(1-(1+$C$238)^-1)/(1-(1+$C$238)^(-1/12))/12*SUMPRODUCT($J$228:$J$277,(1+$C$238)^(-$I$228:$I$277)))-IF(($C$238+'Inputs'!$H$123/100)=0,SUM($J$228:$J$277),(1-(1+($C$238+'Inputs'!$H$123/100))^-1)/(1-(1+($C$238+'Inputs'!$H$123/100))^(-1/12))/12*SUMPRODUCT($J$228:$J$277,(1+($C$238+'Inputs'!$H$123/100))^(-$I$228:$I$277))),2))</f>
@@ -12460,7 +12502,7 @@
     </row>
     <row r="238" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C238">
         <f>IF($C$233=1,'Needs calc'!$C$71,0)</f>
@@ -12486,7 +12528,7 @@
     </row>
     <row r="239" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C239">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$226)*($C$226&lt;&gt;"")*('Inputs'!$F$76:$F$81&gt;0)*'Inputs'!$D$76:$D$81)</f>
@@ -12512,7 +12554,7 @@
     </row>
     <row r="240" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C240">
         <f>IF($C$230&gt;0,$C$231-J228/12,0)</f>
@@ -12538,7 +12580,7 @@
     </row>
     <row r="241" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C241">
         <f>SUMPRODUCT(MAX(('Inputs'!$G$76:$G$81=$C$226)*($C$226&lt;&gt;"")*'Inputs'!$F$76:$F$81))</f>
@@ -12564,7 +12606,7 @@
     </row>
     <row r="242" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C242">
         <f>SUM($J$228:$J$277)</f>
@@ -12590,7 +12632,7 @@
     </row>
     <row r="243" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C243">
         <f>IF('Needs calc'!$C$73&gt;0,IF(N('Inputs'!$E$104)&gt;0,IF('Needs years'!$C$239&lt;=0,IF('Needs years'!$C$234&lt;=0,'Inputs'!$B$104&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$74,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$104,-2),0)&amp;" you want. ",IF('Needs calc'!$C$68&gt;='Needs years'!$C$234,'Inputs'!$B$104&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$74,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$104,-2),0)&amp;" you want, after the R "&amp;FIXED(ROUND('Needs years'!$C$234,-3),0)&amp;" once-off. ",'Inputs'!$B$104&amp;" would have "&amp;IF('Needs calc'!$C$68&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$68,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$234,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$74,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$104,-2),0)&amp;". ")),IF('Needs years'!$C$242&lt;=0,IF('Needs years'!$C$234&gt;0,'Inputs'!$B$104&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$104,-2),0)&amp;" a month you want"&amp;", but "&amp;'Inputs'!$B$104&amp;" would have "&amp;IF('Needs calc'!$C$68&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$68,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$234,-3),0)&amp;" once-off you want for them. ",'Inputs'!$B$104&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$104,-2),0)&amp;" a month you want"&amp;", but the estate duty on it, about R "&amp;FIXED(ROUND('Needs years'!$C$245,-3),0)&amp;", leaves "&amp;'Inputs'!$B$104&amp;" short. "),IF('Needs years'!$J$228&lt;=0,'Inputs'!$B$104&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$104,-2),0)&amp;" a month you want"&amp;" for "&amp;IF('Needs years'!$C$244=1,"the first year","the first "&amp;'Needs years'!$C$244&amp;" years")&amp;"; after that "&amp;'Inputs'!$B$104&amp;" would be short"&amp;IF(AND('Needs years'!$C$234&gt;0,'Needs calc'!$C$68&lt;'Needs years'!$C$234),", and would have "&amp;IF('Needs calc'!$C$68&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$68,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$234,-3),0)&amp;" once-off","")&amp;". ",IF('Needs years'!$C$234&lt;=0,'Inputs'!$B$104&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$74,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$104,-2),0)&amp;" you want, part of it from the death income, and less once it stops. ",IF('Needs calc'!$C$68&gt;='Needs years'!$C$234,'Inputs'!$B$104&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$74,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$104,-2),0)&amp;" you want, part of it from the death income, and less once it stops, after the R "&amp;FIXED(ROUND('Needs years'!$C$234,-3),0)&amp;" once-off. ",'Inputs'!$B$104&amp;" would have "&amp;IF('Needs calc'!$C$68&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$68,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$234,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$74,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$104,-2),0)&amp;", part of it from the death income, and less once it stops. "))))),'Inputs'!$B$104&amp;" would have "&amp;IF('Needs calc'!$C$68&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$68,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$234,-3),0)&amp;" you want to leave them. "),"")</f>
@@ -12616,7 +12658,7 @@
     </row>
     <row r="244" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C244">
         <f>IFERROR(MATCH(1,$L$228:$L$277,0)-1,$C$230)</f>
@@ -12642,7 +12684,7 @@
     </row>
     <row r="245" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C245">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$226)*($C$226&lt;&gt;"")*'Inputs'!$P$76:$P$81)</f>
@@ -13322,27 +13364,27 @@
         <f>N('Inputs'!$D$105)</f>
       </c>
       <c r="I283" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J283" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K283" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L283" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P283" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q283" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="284" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C284">
         <f>IF($C$283&gt;=75,'Inputs'!$H$131,IF($C$283&gt;=65,'Inputs'!$H$130,'Inputs'!$H$124))</f>
@@ -13368,7 +13410,7 @@
     </row>
     <row r="285" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C285">
         <f>N('Inputs'!$I$105)</f>
@@ -13394,7 +13436,7 @@
     </row>
     <row r="286" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C286">
         <f>IF($C$282="",0,N('Inputs'!$F$105))</f>
@@ -13420,7 +13462,7 @@
     </row>
     <row r="287" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B287" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C287">
         <f>N('Inputs'!$E$105)</f>
@@ -13446,7 +13488,7 @@
     </row>
     <row r="288" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C288">
         <f>IF('Inputs'!$G$105="",'Inputs'!$H$129/100,'Inputs'!$G$105/100)</f>
@@ -13472,7 +13514,7 @@
     </row>
     <row r="289" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C289">
         <f>IF('Inputs'!$H$105="Yes",1,0)</f>
@@ -13498,7 +13540,7 @@
     </row>
     <row r="290" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C290">
         <f>IF($C$282="",0,N('Inputs'!$J$105))</f>
@@ -13524,7 +13566,7 @@
     </row>
     <row r="291" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C291">
         <f>ROUND(Q284,2)</f>
@@ -13550,7 +13592,7 @@
     </row>
     <row r="292" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C292">
         <f>ROUND(SUM($Q$284:$Q$333),2)</f>
@@ -13576,7 +13618,7 @@
     </row>
     <row r="293" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B293" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C293">
         <f>IF($C$289&lt;&gt;1,0,ROUND(IF($C$294=0,SUM($J$284:$J$333),(1-(1+$C$294)^-1)/(1-(1+$C$294)^(-1/12))/12*SUMPRODUCT($J$284:$J$333,(1+$C$294)^(-$I$284:$I$333)))-IF(($C$294+'Inputs'!$H$123/100)=0,SUM($J$284:$J$333),(1-(1+($C$294+'Inputs'!$H$123/100))^-1)/(1-(1+($C$294+'Inputs'!$H$123/100))^(-1/12))/12*SUMPRODUCT($J$284:$J$333,(1+($C$294+'Inputs'!$H$123/100))^(-$I$284:$I$333))),2))</f>
@@ -13602,7 +13644,7 @@
     </row>
     <row r="294" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C294">
         <f>IF($C$289=1,'Needs calc'!$C$78,0)</f>
@@ -13628,7 +13670,7 @@
     </row>
     <row r="295" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C295">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$282)*($C$282&lt;&gt;"")*('Inputs'!$F$76:$F$81&gt;0)*'Inputs'!$D$76:$D$81)</f>
@@ -13654,7 +13696,7 @@
     </row>
     <row r="296" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C296">
         <f>IF($C$286&gt;0,$C$287-J284/12,0)</f>
@@ -13680,7 +13722,7 @@
     </row>
     <row r="297" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C297">
         <f>SUMPRODUCT(MAX(('Inputs'!$G$76:$G$81=$C$282)*($C$282&lt;&gt;"")*'Inputs'!$F$76:$F$81))</f>
@@ -13706,7 +13748,7 @@
     </row>
     <row r="298" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C298">
         <f>SUM($J$284:$J$333)</f>
@@ -13732,7 +13774,7 @@
     </row>
     <row r="299" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C299">
         <f>IF('Needs calc'!$C$80&gt;0,IF(N('Inputs'!$E$105)&gt;0,IF('Needs years'!$C$295&lt;=0,IF('Needs years'!$C$290&lt;=0,'Inputs'!$B$105&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$81,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$105,-2),0)&amp;" you want. ",IF('Needs calc'!$C$75&gt;='Needs years'!$C$290,'Inputs'!$B$105&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$81,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$105,-2),0)&amp;" you want, after the R "&amp;FIXED(ROUND('Needs years'!$C$290,-3),0)&amp;" once-off. ",'Inputs'!$B$105&amp;" would have "&amp;IF('Needs calc'!$C$75&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$75,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$290,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$81,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$105,-2),0)&amp;". ")),IF('Needs years'!$C$298&lt;=0,IF('Needs years'!$C$290&gt;0,'Inputs'!$B$105&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$105,-2),0)&amp;" a month you want"&amp;", but "&amp;'Inputs'!$B$105&amp;" would have "&amp;IF('Needs calc'!$C$75&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$75,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$290,-3),0)&amp;" once-off you want for them. ",'Inputs'!$B$105&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$105,-2),0)&amp;" a month you want"&amp;", but the estate duty on it, about R "&amp;FIXED(ROUND('Needs years'!$C$301,-3),0)&amp;", leaves "&amp;'Inputs'!$B$105&amp;" short. "),IF('Needs years'!$J$284&lt;=0,'Inputs'!$B$105&amp;"'s death income covers the R "&amp;FIXED(ROUND('Inputs'!$E$105,-2),0)&amp;" a month you want"&amp;" for "&amp;IF('Needs years'!$C$300=1,"the first year","the first "&amp;'Needs years'!$C$300&amp;" years")&amp;"; after that "&amp;'Inputs'!$B$105&amp;" would be short"&amp;IF(AND('Needs years'!$C$290&gt;0,'Needs calc'!$C$75&lt;'Needs years'!$C$290),", and would have "&amp;IF('Needs calc'!$C$75&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$75,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$290,-3),0)&amp;" once-off","")&amp;". ",IF('Needs years'!$C$290&lt;=0,'Inputs'!$B$105&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$81,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$105,-2),0)&amp;" you want, part of it from the death income, and less once it stops. ",IF('Needs calc'!$C$75&gt;='Needs years'!$C$290,'Inputs'!$B$105&amp;" would have about R "&amp;FIXED(ROUND('Needs calc'!$C$81,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$105,-2),0)&amp;" you want, part of it from the death income, and less once it stops, after the R "&amp;FIXED(ROUND('Needs years'!$C$290,-3),0)&amp;" once-off. ",'Inputs'!$B$105&amp;" would have "&amp;IF('Needs calc'!$C$75&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$75,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$290,-3),0)&amp;" once-off you want for them, and about R "&amp;FIXED(ROUND('Needs calc'!$C$81,-2),0)&amp;" a month of the R "&amp;FIXED(ROUND('Inputs'!$E$105,-2),0)&amp;", part of it from the death income, and less once it stops. "))))),'Inputs'!$B$105&amp;" would have "&amp;IF('Needs calc'!$C$75&lt;=0,"nothing","about R "&amp;FIXED(ROUND('Needs calc'!$C$75,-3),0))&amp;" of the R "&amp;FIXED(ROUND('Needs years'!$C$290,-3),0)&amp;" you want to leave them. "),"")</f>
@@ -13758,7 +13800,7 @@
     </row>
     <row r="300" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C300">
         <f>IFERROR(MATCH(1,$L$284:$L$333,0)-1,$C$286)</f>
@@ -13784,7 +13826,7 @@
     </row>
     <row r="301" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B301" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C301">
         <f>SUMPRODUCT(('Inputs'!$G$76:$G$81=$C$282)*($C$282&lt;&gt;"")*'Inputs'!$P$76:$P$81)</f>
@@ -14466,15 +14508,15 @@
   <sheetData>
     <row r="2" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C3">
         <f>0</f>
@@ -14530,7 +14572,7 @@
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C4">
         <f>0</f>
@@ -14586,7 +14628,7 @@
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C5">
         <f>0</f>
@@ -14642,7 +14684,7 @@
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C6">
         <f>0</f>
@@ -14698,7 +14740,7 @@
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C7">
         <f>0</f>
@@ -14754,7 +14796,7 @@
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C8">
         <f>0</f>
@@ -14810,7 +14852,7 @@
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C9">
         <f>0</f>
@@ -14866,7 +14908,7 @@
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C10">
         <f>0</f>
@@ -14922,7 +14964,7 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C11">
         <f>(1-'Inputs'!$T$100)*C4+(1-'Inputs'!$T$101)*C5+(1-'Inputs'!$T$102)*C6+(1-'Inputs'!$T$103)*C7+(1-'Inputs'!$T$104)*C8+(1-'Inputs'!$T$105)*C9</f>
@@ -14978,119 +15020,119 @@
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C12">
-        <f>IF(C10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+C10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(C10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+C10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="E12">
-        <f>IF(E10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+E10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(E10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+E10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="F12">
-        <f>IF(F10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+F10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(F10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+F10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="G12">
-        <f>IF(G10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+G10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(G10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+G10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="H12">
-        <f>IF(H10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+H10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(H10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+H10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="I12">
-        <f>IF(I10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+I10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(I10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+I10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="J12">
-        <f>IF(J10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+J10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(J10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+J10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="K12">
-        <f>IF(K10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+K10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(K10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+K10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="L12">
-        <f>IF(L10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+L10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(L10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+L10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="M12">
-        <f>IF(M10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+M10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(M10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+M10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="N12">
-        <f>IF(N10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+N10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(N10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+N10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="O12">
-        <f>IF(O10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+O10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(O10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+O10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="P12">
-        <f>IF(P10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+P10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(P10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+P10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="Q12">
-        <f>IF(Q10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+Q10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(Q10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+Q10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="R12">
-        <f>IF(R10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+R10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(R10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+R10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="S12">
-        <f>IF(S10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+S10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(S10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+S10),2)+'Workings'!$C$31,0)</f>
       </c>
       <c r="T12">
-        <f>IF(T10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+T10),2)+'Workings'!$C$29,0)</f>
+        <f>IF(T10&gt;0,ROUND(('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100))*('Workings'!$C$21+T10),2)+'Workings'!$C$31,0)</f>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C13">
-        <f>ROUND('Workings'!$C$33+C10-C12,2)</f>
+        <f>ROUND('Workings'!$C$35+C10-C12,2)</f>
       </c>
       <c r="E13">
-        <f>ROUND('Workings'!$C$33+E10-E12,2)</f>
+        <f>ROUND('Workings'!$C$35+E10-E12,2)</f>
       </c>
       <c r="F13">
-        <f>ROUND('Workings'!$C$33+F10-F12,2)</f>
+        <f>ROUND('Workings'!$C$35+F10-F12,2)</f>
       </c>
       <c r="G13">
-        <f>ROUND('Workings'!$C$33+G10-G12,2)</f>
+        <f>ROUND('Workings'!$C$35+G10-G12,2)</f>
       </c>
       <c r="H13">
-        <f>ROUND('Workings'!$C$33+H10-H12,2)</f>
+        <f>ROUND('Workings'!$C$35+H10-H12,2)</f>
       </c>
       <c r="I13">
-        <f>ROUND('Workings'!$C$33+I10-I12,2)</f>
+        <f>ROUND('Workings'!$C$35+I10-I12,2)</f>
       </c>
       <c r="J13">
-        <f>ROUND('Workings'!$C$33+J10-J12,2)</f>
+        <f>ROUND('Workings'!$C$35+J10-J12,2)</f>
       </c>
       <c r="K13">
-        <f>ROUND('Workings'!$C$33+K10-K12,2)</f>
+        <f>ROUND('Workings'!$C$35+K10-K12,2)</f>
       </c>
       <c r="L13">
-        <f>ROUND('Workings'!$C$33+L10-L12,2)</f>
+        <f>ROUND('Workings'!$C$35+L10-L12,2)</f>
       </c>
       <c r="M13">
-        <f>ROUND('Workings'!$C$33+M10-M12,2)</f>
+        <f>ROUND('Workings'!$C$35+M10-M12,2)</f>
       </c>
       <c r="N13">
-        <f>ROUND('Workings'!$C$33+N10-N12,2)</f>
+        <f>ROUND('Workings'!$C$35+N10-N12,2)</f>
       </c>
       <c r="O13">
-        <f>ROUND('Workings'!$C$33+O10-O12,2)</f>
+        <f>ROUND('Workings'!$C$35+O10-O12,2)</f>
       </c>
       <c r="P13">
-        <f>ROUND('Workings'!$C$33+P10-P12,2)</f>
+        <f>ROUND('Workings'!$C$35+P10-P12,2)</f>
       </c>
       <c r="Q13">
-        <f>ROUND('Workings'!$C$33+Q10-Q12,2)</f>
+        <f>ROUND('Workings'!$C$35+Q10-Q12,2)</f>
       </c>
       <c r="R13">
-        <f>ROUND('Workings'!$C$33+R10-R12,2)</f>
+        <f>ROUND('Workings'!$C$35+R10-R12,2)</f>
       </c>
       <c r="S13">
-        <f>ROUND('Workings'!$C$33+S10-S12,2)</f>
+        <f>ROUND('Workings'!$C$35+S10-S12,2)</f>
       </c>
       <c r="T13">
-        <f>ROUND('Workings'!$C$33+T10-T12,2)</f>
+        <f>ROUND('Workings'!$C$35+T10-T12,2)</f>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C14">
         <f>IF(C13&lt;0,IF(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39)&gt;0,MAX(0,1+C13/(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39))),1),1)</f>
@@ -15146,119 +15188,119 @@
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*C14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,C13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*C14+IF('Inputs'!$C$14="Spouse",MAX(0,C13),0),0)</f>
       </c>
       <c r="E15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*E14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,E13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*E14+IF('Inputs'!$C$14="Spouse",MAX(0,E13),0),0)</f>
       </c>
       <c r="F15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*F14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,F13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*F14+IF('Inputs'!$C$14="Spouse",MAX(0,F13),0),0)</f>
       </c>
       <c r="G15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*G14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,G13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*G14+IF('Inputs'!$C$14="Spouse",MAX(0,G13),0),0)</f>
       </c>
       <c r="H15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*H14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,H13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*H14+IF('Inputs'!$C$14="Spouse",MAX(0,H13),0),0)</f>
       </c>
       <c r="I15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*I14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,I13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*I14+IF('Inputs'!$C$14="Spouse",MAX(0,I13),0),0)</f>
       </c>
       <c r="J15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*J14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,J13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*J14+IF('Inputs'!$C$14="Spouse",MAX(0,J13),0),0)</f>
       </c>
       <c r="K15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*K14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,K13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*K14+IF('Inputs'!$C$14="Spouse",MAX(0,K13),0),0)</f>
       </c>
       <c r="L15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*L14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,L13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*L14+IF('Inputs'!$C$14="Spouse",MAX(0,L13),0),0)</f>
       </c>
       <c r="M15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*M14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,M13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*M14+IF('Inputs'!$C$14="Spouse",MAX(0,M13),0),0)</f>
       </c>
       <c r="N15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*N14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,N13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*N14+IF('Inputs'!$C$14="Spouse",MAX(0,N13),0),0)</f>
       </c>
       <c r="O15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*O14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,O13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*O14+IF('Inputs'!$C$14="Spouse",MAX(0,O13),0),0)</f>
       </c>
       <c r="P15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*P14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,P13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*P14+IF('Inputs'!$C$14="Spouse",MAX(0,P13),0),0)</f>
       </c>
       <c r="Q15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*Q14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,Q13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*Q14+IF('Inputs'!$C$14="Spouse",MAX(0,Q13),0),0)</f>
       </c>
       <c r="R15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*R14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,R13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*R14+IF('Inputs'!$C$14="Spouse",MAX(0,R13),0),0)</f>
       </c>
       <c r="S15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*S14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,S13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*S14+IF('Inputs'!$C$14="Spouse",MAX(0,S13),0),0)</f>
       </c>
       <c r="T15">
-        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*T14+SUMIFS('Inputs'!$D$59:$D$70,'Inputs'!$C$59:$C$70,"Spouse",'Inputs'!$E$59:$E$70,"&lt;&gt;No")+SUM('Inputs'!$S$76:$S$81)+IF('Inputs'!$C$14="Spouse",MAX(0,T13),0),0)</f>
+        <f>IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),SUM('Inputs'!$R$22:$R$39)*T14+IF('Inputs'!$C$14="Spouse",MAX(0,T13),0),0)</f>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C16">
-        <f>ROUND('Workings'!$C$36+C11+C10-C12-(C15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+C11+C10-C12-(C15+'Workings'!$C$37),2)</f>
       </c>
       <c r="E16">
-        <f>ROUND('Workings'!$C$36+E11+E10-E12-(E15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+E11+E10-E12-(E15+'Workings'!$C$37),2)</f>
       </c>
       <c r="F16">
-        <f>ROUND('Workings'!$C$36+F11+F10-F12-(F15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+F11+F10-F12-(F15+'Workings'!$C$37),2)</f>
       </c>
       <c r="G16">
-        <f>ROUND('Workings'!$C$36+G11+G10-G12-(G15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+G11+G10-G12-(G15+'Workings'!$C$37),2)</f>
       </c>
       <c r="H16">
-        <f>ROUND('Workings'!$C$36+H11+H10-H12-(H15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+H11+H10-H12-(H15+'Workings'!$C$37),2)</f>
       </c>
       <c r="I16">
-        <f>ROUND('Workings'!$C$36+I11+I10-I12-(I15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+I11+I10-I12-(I15+'Workings'!$C$37),2)</f>
       </c>
       <c r="J16">
-        <f>ROUND('Workings'!$C$36+J11+J10-J12-(J15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+J11+J10-J12-(J15+'Workings'!$C$37),2)</f>
       </c>
       <c r="K16">
-        <f>ROUND('Workings'!$C$36+K11+K10-K12-(K15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+K11+K10-K12-(K15+'Workings'!$C$37),2)</f>
       </c>
       <c r="L16">
-        <f>ROUND('Workings'!$C$36+L11+L10-L12-(L15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+L11+L10-L12-(L15+'Workings'!$C$37),2)</f>
       </c>
       <c r="M16">
-        <f>ROUND('Workings'!$C$36+M11+M10-M12-(M15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+M11+M10-M12-(M15+'Workings'!$C$37),2)</f>
       </c>
       <c r="N16">
-        <f>ROUND('Workings'!$C$36+N11+N10-N12-(N15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+N11+N10-N12-(N15+'Workings'!$C$37),2)</f>
       </c>
       <c r="O16">
-        <f>ROUND('Workings'!$C$36+O11+O10-O12-(O15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+O11+O10-O12-(O15+'Workings'!$C$37),2)</f>
       </c>
       <c r="P16">
-        <f>ROUND('Workings'!$C$36+P11+P10-P12-(P15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+P11+P10-P12-(P15+'Workings'!$C$37),2)</f>
       </c>
       <c r="Q16">
-        <f>ROUND('Workings'!$C$36+Q11+Q10-Q12-(Q15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+Q11+Q10-Q12-(Q15+'Workings'!$C$37),2)</f>
       </c>
       <c r="R16">
-        <f>ROUND('Workings'!$C$36+R11+R10-R12-(R15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+R11+R10-R12-(R15+'Workings'!$C$37),2)</f>
       </c>
       <c r="S16">
-        <f>ROUND('Workings'!$C$36+S11+S10-S12-(S15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+S11+S10-S12-(S15+'Workings'!$C$37),2)</f>
       </c>
       <c r="T16">
-        <f>ROUND('Workings'!$C$36+T11+T10-T12-(T15+'Workings'!$C$35),2)</f>
+        <f>ROUND('Workings'!$C$38+T11+T10-T12-(T15+'Workings'!$C$37),2)</f>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C17">
         <f>ROUND(IF(MAX(0,C16-'Inputs'!$C$127)&lt;='Inputs'!$C$129,MAX(0,C16-'Inputs'!$C$127)*'Inputs'!$C$128/100,'Inputs'!$C$129*'Inputs'!$C$128/100+(MAX(0,C16-'Inputs'!$C$127)-'Inputs'!$C$129)*'Inputs'!$C$130/100),2)</f>
@@ -15314,7 +15356,7 @@
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C18">
         <f>IF(C16&gt;0,C17/C16,0)</f>
@@ -15370,7 +15412,7 @@
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C19">
         <f>SUMPRODUCT(ROUND(C18*'Inputs'!$L$59:$L$70,2))</f>
@@ -15426,7 +15468,7 @@
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C20">
         <f>SUMPRODUCT(ROUND(C18*'Inputs'!$S$22:$S$39,2))</f>
@@ -15482,7 +15524,7 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C21">
         <f>(1-'Inputs'!$T$100)*ROUND(C18*C4,2)+(1-'Inputs'!$T$101)*ROUND(C18*C5,2)+(1-'Inputs'!$T$102)*ROUND(C18*C6,2)+(1-'Inputs'!$T$103)*ROUND(C18*C7,2)+(1-'Inputs'!$T$104)*ROUND(C18*C8,2)+(1-'Inputs'!$T$105)*ROUND(C18*C9,2)</f>
@@ -15538,7 +15580,7 @@
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C22">
         <f>SUMPRODUCT(ROUND(C18*'Inputs'!$O$76:$O$81,2))</f>
@@ -15594,7 +15636,7 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C23">
         <f>ROUND(C17-C19-C20-C21-C22,2)</f>
@@ -15650,119 +15692,119 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+C23+C12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+C23+C12,2)</f>
       </c>
       <c r="E24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+E23+E12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+E23+E12,2)</f>
       </c>
       <c r="F24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+F23+F12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+F23+F12,2)</f>
       </c>
       <c r="G24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+G23+G12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+G23+G12,2)</f>
       </c>
       <c r="H24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+H23+H12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+H23+H12,2)</f>
       </c>
       <c r="I24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+I23+I12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+I23+I12,2)</f>
       </c>
       <c r="J24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+J23+J12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+J23+J12,2)</f>
       </c>
       <c r="K24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+K23+K12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+K23+K12,2)</f>
       </c>
       <c r="L24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+L23+L12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+L23+L12,2)</f>
       </c>
       <c r="M24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+M23+M12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+M23+M12,2)</f>
       </c>
       <c r="N24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+N23+N12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+N23+N12,2)</f>
       </c>
       <c r="O24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+O23+O12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+O23+O12,2)</f>
       </c>
       <c r="P24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+P23+P12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+P23+P12,2)</f>
       </c>
       <c r="Q24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+Q23+Q12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+Q23+Q12,2)</f>
       </c>
       <c r="R24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+R23+R12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+R23+R12,2)</f>
       </c>
       <c r="S24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+S23+S12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+S23+S12,2)</f>
       </c>
       <c r="T24">
-        <f>ROUND('Workings'!$C$63-'Workings'!$C$49+T23+T12,2)</f>
+        <f>ROUND('Workings'!$C$65-'Workings'!$C$51+T23+T12,2)</f>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C25">
-        <f>ROUND('Workings'!$C$66+C10,2)</f>
+        <f>ROUND('Workings'!$C$68+C10,2)</f>
       </c>
       <c r="E25">
-        <f>ROUND('Workings'!$C$66+E10,2)</f>
+        <f>ROUND('Workings'!$C$68+E10,2)</f>
       </c>
       <c r="F25">
-        <f>ROUND('Workings'!$C$66+F10,2)</f>
+        <f>ROUND('Workings'!$C$68+F10,2)</f>
       </c>
       <c r="G25">
-        <f>ROUND('Workings'!$C$66+G10,2)</f>
+        <f>ROUND('Workings'!$C$68+G10,2)</f>
       </c>
       <c r="H25">
-        <f>ROUND('Workings'!$C$66+H10,2)</f>
+        <f>ROUND('Workings'!$C$68+H10,2)</f>
       </c>
       <c r="I25">
-        <f>ROUND('Workings'!$C$66+I10,2)</f>
+        <f>ROUND('Workings'!$C$68+I10,2)</f>
       </c>
       <c r="J25">
-        <f>ROUND('Workings'!$C$66+J10,2)</f>
+        <f>ROUND('Workings'!$C$68+J10,2)</f>
       </c>
       <c r="K25">
-        <f>ROUND('Workings'!$C$66+K10,2)</f>
+        <f>ROUND('Workings'!$C$68+K10,2)</f>
       </c>
       <c r="L25">
-        <f>ROUND('Workings'!$C$66+L10,2)</f>
+        <f>ROUND('Workings'!$C$68+L10,2)</f>
       </c>
       <c r="M25">
-        <f>ROUND('Workings'!$C$66+M10,2)</f>
+        <f>ROUND('Workings'!$C$68+M10,2)</f>
       </c>
       <c r="N25">
-        <f>ROUND('Workings'!$C$66+N10,2)</f>
+        <f>ROUND('Workings'!$C$68+N10,2)</f>
       </c>
       <c r="O25">
-        <f>ROUND('Workings'!$C$66+O10,2)</f>
+        <f>ROUND('Workings'!$C$68+O10,2)</f>
       </c>
       <c r="P25">
-        <f>ROUND('Workings'!$C$66+P10,2)</f>
+        <f>ROUND('Workings'!$C$68+P10,2)</f>
       </c>
       <c r="Q25">
-        <f>ROUND('Workings'!$C$66+Q10,2)</f>
+        <f>ROUND('Workings'!$C$68+Q10,2)</f>
       </c>
       <c r="R25">
-        <f>ROUND('Workings'!$C$66+R10,2)</f>
+        <f>ROUND('Workings'!$C$68+R10,2)</f>
       </c>
       <c r="S25">
-        <f>ROUND('Workings'!$C$66+S10,2)</f>
+        <f>ROUND('Workings'!$C$68+S10,2)</f>
       </c>
       <c r="T25">
-        <f>ROUND('Workings'!$C$66+T10,2)</f>
+        <f>ROUND('Workings'!$C$68+T10,2)</f>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C26">
         <f>ROUND(MAX(0,C25-C24),2)</f>
@@ -15818,7 +15860,7 @@
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C27">
         <f>ROUND(C24-C25,2)</f>
@@ -15874,7 +15916,7 @@
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C28">
         <f>ROUND(C26+SUM('Inputs'!$Y$22:$Y$39),2)</f>
@@ -15930,7 +15972,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C29">
         <f>SUM('Inputs'!$L$100:$L$105)</f>
@@ -15986,7 +16028,7 @@
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C30">
         <f>SUM('Inputs'!$Q$100:$Q$105)</f>
@@ -16042,7 +16084,7 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C31">
         <f>IF('Inputs'!$C$14="Spouse","S",IF('Inputs'!$C$106="Not to the dependants","N","K"))</f>
@@ -16098,7 +16140,7 @@
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C32">
         <f>IF(C29=0,0,ROUNDDOWN(C28/C29,2))</f>
@@ -16154,7 +16196,7 @@
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C33">
         <f>ROUND(C28-C32*(C29-1),2)</f>
@@ -16210,7 +16252,7 @@
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C34">
         <f>IF(C30=0,0,SUMPRODUCT('Inputs'!$Q$59:$Q$70,ROUNDDOWN(('Inputs'!$D$59:$D$70-'Inputs'!$R$59:$R$70*ROUND(C18*'Inputs'!$D$59:$D$70,2))/C30,2)))</f>
@@ -16266,7 +16308,7 @@
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C35">
         <f>IF(C30=0,0,SUMPRODUCT('Inputs'!$Q$59:$Q$70,('Inputs'!$D$59:$D$70-'Inputs'!$R$59:$R$70*ROUND(C18*'Inputs'!$D$59:$D$70,2))-ROUNDDOWN(('Inputs'!$D$59:$D$70-'Inputs'!$R$59:$R$70*ROUND(C18*'Inputs'!$D$59:$D$70,2))/C30,2)*(C30-1)))</f>
@@ -16322,7 +16364,7 @@
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C36">
         <f>IF(C30=0,0,SUMPRODUCT(('Inputs'!$F$87:$F$94="The children's trust")*ROUNDDOWN('Inputs'!$J$87:$J$94/C30,2)))</f>
@@ -16378,7 +16420,7 @@
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C37">
         <f>IF(C30=0,0,SUMPRODUCT(('Inputs'!$F$87:$F$94="The children's trust")*('Inputs'!$J$87:$J$94-ROUNDDOWN('Inputs'!$J$87:$J$94/C30,2)*(C30-1))))</f>
@@ -16434,7 +16476,7 @@
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C38">
         <f>SUMPRODUCT('Inputs'!$R$59:$R$70*('Inputs'!$F$59:$F$70=""),'Inputs'!$D$59:$D$70)</f>
@@ -16490,7 +16532,7 @@
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C39">
         <f>SUMPRODUCT('Inputs'!$R$59:$R$70*('Inputs'!$F$59:$F$70=""),ROUND(C18*'Inputs'!$D$59:$D$70,2))</f>
@@ -16546,7 +16588,7 @@
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C40">
         <f>IF('Inputs'!$B$100="",0,ROUND(IF(C31="S",'Inputs'!$O$100*C28,IF(C31="K",'Inputs'!$L$100*IF('Inputs'!$N$100=1,C33,C32),0))+'Inputs'!$O$100*ROUND(SUM('Inputs'!$Z$22:$Z$39)*C14,2)+'Inputs'!$Q$100*IF('Inputs'!$S$100=1,C35+C37,C34+C36)+SUMPRODUCT(('Inputs'!$F$59:$F$70='Inputs'!$B$100)*('Inputs'!$C$59:$C$70&lt;&gt;"Estate")*('Inputs'!$C$59:$C$70&lt;&gt;""),('Inputs'!$D$59:$D$70-'Inputs'!$R$59:$R$70*ROUND(C18*'Inputs'!$D$59:$D$70,2)))+SUMPRODUCT(('Inputs'!$F$87:$F$94='Inputs'!$B$100)*'Inputs'!$J$87:$J$94)+C4-(1-'Inputs'!$T$100)*ROUND(C18*C4,2)-SUMPRODUCT(('Inputs'!$G$76:$G$81='Inputs'!$B$100)*ROUND(C18*'Inputs'!$O$76:$O$81,2)),2))</f>
@@ -16602,7 +16644,7 @@
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C41">
         <f>'Needs years'!$C$5+MAX(0,C40-'Needs years'!$C$10)*('Inputs'!$H$122/100*('Inputs'!$H$125/100+'Inputs'!$H$120/100*'Inputs'!$H$127/100))</f>
@@ -16658,7 +16700,7 @@
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C42">
         <f>IF(C41&lt;='Needs years'!$C$4,0,INDEX('Inputs'!$E$134:$E$140,MATCH(C41,'Inputs'!$C$134:$C$140,1)-IF(COUNTIF('Inputs'!$C$134:$C$140,C41)&gt;0,1,0))/100)</f>
@@ -16714,7 +16756,7 @@
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C43">
         <f>('Inputs'!$H$122/100*(1-('Inputs'!$H$125/100*C42+'Inputs'!$H$126/100*'Inputs'!$H$128/100+'Inputs'!$H$127/100*'Inputs'!$H$120/100*C42))-IF('Needs years'!$C$9=1,'Inputs'!$H$123/100,0))</f>
@@ -16770,7 +16812,7 @@
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C44">
         <f>IF('Inputs'!$B$100="",0,ROUND('Needs years'!$C$10+ROUND(IF(C43=0,SUM('Needs years'!$J$4:$J$53),(1-(1+C43)^-1)/(1-(1+C43)^(-1/12))/12*SUMPRODUCT('Needs years'!$J$4:$J$53,(1+C43)^(-'Needs years'!$I$4:$I$53))),2),2))</f>
@@ -16826,7 +16868,7 @@
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C45">
         <f>IF('Inputs'!$B$100="",0,ROUND(C44-C40,2))</f>
@@ -16882,7 +16924,7 @@
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C46">
         <f>IF('Inputs'!$B$100="",0,'Needs years'!$C$16+IF((C44-'Needs years'!$C$10)&gt;0,MAX(0,C40-'Needs years'!$C$10)/(C44-'Needs years'!$C$10)*'Needs years'!$J$4/12,0))</f>
@@ -16938,7 +16980,7 @@
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C47">
         <f>IF('Inputs'!$B$101="",0,ROUND(IF(C31="S",'Inputs'!$O$101*C28,IF(C31="K",'Inputs'!$L$101*IF('Inputs'!$N$101=1,C33,C32),0))+'Inputs'!$O$101*ROUND(SUM('Inputs'!$Z$22:$Z$39)*C14,2)+'Inputs'!$Q$101*IF('Inputs'!$S$101=1,C35+C37,C34+C36)+SUMPRODUCT(('Inputs'!$F$59:$F$70='Inputs'!$B$101)*('Inputs'!$C$59:$C$70&lt;&gt;"Estate")*('Inputs'!$C$59:$C$70&lt;&gt;""),('Inputs'!$D$59:$D$70-'Inputs'!$R$59:$R$70*ROUND(C18*'Inputs'!$D$59:$D$70,2)))+SUMPRODUCT(('Inputs'!$F$87:$F$94='Inputs'!$B$101)*'Inputs'!$J$87:$J$94)+C5-(1-'Inputs'!$T$101)*ROUND(C18*C5,2)-SUMPRODUCT(('Inputs'!$G$76:$G$81='Inputs'!$B$101)*ROUND(C18*'Inputs'!$O$76:$O$81,2)),2))</f>
@@ -16994,7 +17036,7 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C48">
         <f>'Needs years'!$C$61+MAX(0,C47-'Needs years'!$C$66)*('Inputs'!$H$122/100*('Inputs'!$H$125/100+'Inputs'!$H$120/100*'Inputs'!$H$127/100))</f>
@@ -17050,7 +17092,7 @@
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C49">
         <f>IF(C48&lt;='Needs years'!$C$60,0,INDEX('Inputs'!$E$134:$E$140,MATCH(C48,'Inputs'!$C$134:$C$140,1)-IF(COUNTIF('Inputs'!$C$134:$C$140,C48)&gt;0,1,0))/100)</f>
@@ -17106,7 +17148,7 @@
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C50">
         <f>('Inputs'!$H$122/100*(1-('Inputs'!$H$125/100*C49+'Inputs'!$H$126/100*'Inputs'!$H$128/100+'Inputs'!$H$127/100*'Inputs'!$H$120/100*C49))-IF('Needs years'!$C$65=1,'Inputs'!$H$123/100,0))</f>
@@ -17162,7 +17204,7 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C51">
         <f>IF('Inputs'!$B$101="",0,ROUND('Needs years'!$C$66+ROUND(IF(C50=0,SUM('Needs years'!$J$60:$J$109),(1-(1+C50)^-1)/(1-(1+C50)^(-1/12))/12*SUMPRODUCT('Needs years'!$J$60:$J$109,(1+C50)^(-'Needs years'!$I$60:$I$109))),2),2))</f>
@@ -17218,7 +17260,7 @@
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C52">
         <f>IF('Inputs'!$B$101="",0,ROUND(C51-C47,2))</f>
@@ -17274,7 +17316,7 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C53">
         <f>IF('Inputs'!$B$101="",0,'Needs years'!$C$72+IF((C51-'Needs years'!$C$66)&gt;0,MAX(0,C47-'Needs years'!$C$66)/(C51-'Needs years'!$C$66)*'Needs years'!$J$60/12,0))</f>
@@ -17330,7 +17372,7 @@
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C54">
         <f>IF('Inputs'!$B$102="",0,ROUND(IF(C31="S",'Inputs'!$O$102*C28,IF(C31="K",'Inputs'!$L$102*IF('Inputs'!$N$102=1,C33,C32),0))+'Inputs'!$O$102*ROUND(SUM('Inputs'!$Z$22:$Z$39)*C14,2)+'Inputs'!$Q$102*IF('Inputs'!$S$102=1,C35+C37,C34+C36)+SUMPRODUCT(('Inputs'!$F$59:$F$70='Inputs'!$B$102)*('Inputs'!$C$59:$C$70&lt;&gt;"Estate")*('Inputs'!$C$59:$C$70&lt;&gt;""),('Inputs'!$D$59:$D$70-'Inputs'!$R$59:$R$70*ROUND(C18*'Inputs'!$D$59:$D$70,2)))+SUMPRODUCT(('Inputs'!$F$87:$F$94='Inputs'!$B$102)*'Inputs'!$J$87:$J$94)+C6-(1-'Inputs'!$T$102)*ROUND(C18*C6,2)-SUMPRODUCT(('Inputs'!$G$76:$G$81='Inputs'!$B$102)*ROUND(C18*'Inputs'!$O$76:$O$81,2)),2))</f>
@@ -17386,7 +17428,7 @@
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C55">
         <f>'Needs years'!$C$117+MAX(0,C54-'Needs years'!$C$122)*('Inputs'!$H$122/100*('Inputs'!$H$125/100+'Inputs'!$H$120/100*'Inputs'!$H$127/100))</f>
@@ -17442,7 +17484,7 @@
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C56">
         <f>IF(C55&lt;='Needs years'!$C$116,0,INDEX('Inputs'!$E$134:$E$140,MATCH(C55,'Inputs'!$C$134:$C$140,1)-IF(COUNTIF('Inputs'!$C$134:$C$140,C55)&gt;0,1,0))/100)</f>
@@ -17498,7 +17540,7 @@
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C57">
         <f>('Inputs'!$H$122/100*(1-('Inputs'!$H$125/100*C56+'Inputs'!$H$126/100*'Inputs'!$H$128/100+'Inputs'!$H$127/100*'Inputs'!$H$120/100*C56))-IF('Needs years'!$C$121=1,'Inputs'!$H$123/100,0))</f>
@@ -17554,7 +17596,7 @@
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C58">
         <f>IF('Inputs'!$B$102="",0,ROUND('Needs years'!$C$122+ROUND(IF(C57=0,SUM('Needs years'!$J$116:$J$165),(1-(1+C57)^-1)/(1-(1+C57)^(-1/12))/12*SUMPRODUCT('Needs years'!$J$116:$J$165,(1+C57)^(-'Needs years'!$I$116:$I$165))),2),2))</f>
@@ -17610,7 +17652,7 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C59">
         <f>IF('Inputs'!$B$102="",0,ROUND(C58-C54,2))</f>
@@ -17666,7 +17708,7 @@
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C60">
         <f>IF('Inputs'!$B$102="",0,'Needs years'!$C$128+IF((C58-'Needs years'!$C$122)&gt;0,MAX(0,C54-'Needs years'!$C$122)/(C58-'Needs years'!$C$122)*'Needs years'!$J$116/12,0))</f>
@@ -17722,7 +17764,7 @@
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C61">
         <f>IF('Inputs'!$B$103="",0,ROUND(IF(C31="S",'Inputs'!$O$103*C28,IF(C31="K",'Inputs'!$L$103*IF('Inputs'!$N$103=1,C33,C32),0))+'Inputs'!$O$103*ROUND(SUM('Inputs'!$Z$22:$Z$39)*C14,2)+'Inputs'!$Q$103*IF('Inputs'!$S$103=1,C35+C37,C34+C36)+SUMPRODUCT(('Inputs'!$F$59:$F$70='Inputs'!$B$103)*('Inputs'!$C$59:$C$70&lt;&gt;"Estate")*('Inputs'!$C$59:$C$70&lt;&gt;""),('Inputs'!$D$59:$D$70-'Inputs'!$R$59:$R$70*ROUND(C18*'Inputs'!$D$59:$D$70,2)))+SUMPRODUCT(('Inputs'!$F$87:$F$94='Inputs'!$B$103)*'Inputs'!$J$87:$J$94)+C7-(1-'Inputs'!$T$103)*ROUND(C18*C7,2)-SUMPRODUCT(('Inputs'!$G$76:$G$81='Inputs'!$B$103)*ROUND(C18*'Inputs'!$O$76:$O$81,2)),2))</f>
@@ -17778,7 +17820,7 @@
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C62">
         <f>'Needs years'!$C$173+MAX(0,C61-'Needs years'!$C$178)*('Inputs'!$H$122/100*('Inputs'!$H$125/100+'Inputs'!$H$120/100*'Inputs'!$H$127/100))</f>
@@ -17834,7 +17876,7 @@
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C63">
         <f>IF(C62&lt;='Needs years'!$C$172,0,INDEX('Inputs'!$E$134:$E$140,MATCH(C62,'Inputs'!$C$134:$C$140,1)-IF(COUNTIF('Inputs'!$C$134:$C$140,C62)&gt;0,1,0))/100)</f>
@@ -17890,7 +17932,7 @@
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C64">
         <f>('Inputs'!$H$122/100*(1-('Inputs'!$H$125/100*C63+'Inputs'!$H$126/100*'Inputs'!$H$128/100+'Inputs'!$H$127/100*'Inputs'!$H$120/100*C63))-IF('Needs years'!$C$177=1,'Inputs'!$H$123/100,0))</f>
@@ -17946,7 +17988,7 @@
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C65">
         <f>IF('Inputs'!$B$103="",0,ROUND('Needs years'!$C$178+ROUND(IF(C64=0,SUM('Needs years'!$J$172:$J$221),(1-(1+C64)^-1)/(1-(1+C64)^(-1/12))/12*SUMPRODUCT('Needs years'!$J$172:$J$221,(1+C64)^(-'Needs years'!$I$172:$I$221))),2),2))</f>
@@ -18002,7 +18044,7 @@
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C66">
         <f>IF('Inputs'!$B$103="",0,ROUND(C65-C61,2))</f>
@@ -18058,7 +18100,7 @@
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C67">
         <f>IF('Inputs'!$B$103="",0,'Needs years'!$C$184+IF((C65-'Needs years'!$C$178)&gt;0,MAX(0,C61-'Needs years'!$C$178)/(C65-'Needs years'!$C$178)*'Needs years'!$J$172/12,0))</f>
@@ -18114,7 +18156,7 @@
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C68">
         <f>IF('Inputs'!$B$104="",0,ROUND(IF(C31="S",'Inputs'!$O$104*C28,IF(C31="K",'Inputs'!$L$104*IF('Inputs'!$N$104=1,C33,C32),0))+'Inputs'!$O$104*ROUND(SUM('Inputs'!$Z$22:$Z$39)*C14,2)+'Inputs'!$Q$104*IF('Inputs'!$S$104=1,C35+C37,C34+C36)+SUMPRODUCT(('Inputs'!$F$59:$F$70='Inputs'!$B$104)*('Inputs'!$C$59:$C$70&lt;&gt;"Estate")*('Inputs'!$C$59:$C$70&lt;&gt;""),('Inputs'!$D$59:$D$70-'Inputs'!$R$59:$R$70*ROUND(C18*'Inputs'!$D$59:$D$70,2)))+SUMPRODUCT(('Inputs'!$F$87:$F$94='Inputs'!$B$104)*'Inputs'!$J$87:$J$94)+C8-(1-'Inputs'!$T$104)*ROUND(C18*C8,2)-SUMPRODUCT(('Inputs'!$G$76:$G$81='Inputs'!$B$104)*ROUND(C18*'Inputs'!$O$76:$O$81,2)),2))</f>
@@ -18170,7 +18212,7 @@
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C69">
         <f>'Needs years'!$C$229+MAX(0,C68-'Needs years'!$C$234)*('Inputs'!$H$122/100*('Inputs'!$H$125/100+'Inputs'!$H$120/100*'Inputs'!$H$127/100))</f>
@@ -18226,7 +18268,7 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C70">
         <f>IF(C69&lt;='Needs years'!$C$228,0,INDEX('Inputs'!$E$134:$E$140,MATCH(C69,'Inputs'!$C$134:$C$140,1)-IF(COUNTIF('Inputs'!$C$134:$C$140,C69)&gt;0,1,0))/100)</f>
@@ -18282,7 +18324,7 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C71">
         <f>('Inputs'!$H$122/100*(1-('Inputs'!$H$125/100*C70+'Inputs'!$H$126/100*'Inputs'!$H$128/100+'Inputs'!$H$127/100*'Inputs'!$H$120/100*C70))-IF('Needs years'!$C$233=1,'Inputs'!$H$123/100,0))</f>
@@ -18338,7 +18380,7 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C72">
         <f>IF('Inputs'!$B$104="",0,ROUND('Needs years'!$C$234+ROUND(IF(C71=0,SUM('Needs years'!$J$228:$J$277),(1-(1+C71)^-1)/(1-(1+C71)^(-1/12))/12*SUMPRODUCT('Needs years'!$J$228:$J$277,(1+C71)^(-'Needs years'!$I$228:$I$277))),2),2))</f>
@@ -18394,7 +18436,7 @@
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C73">
         <f>IF('Inputs'!$B$104="",0,ROUND(C72-C68,2))</f>
@@ -18450,7 +18492,7 @@
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C74">
         <f>IF('Inputs'!$B$104="",0,'Needs years'!$C$240+IF((C72-'Needs years'!$C$234)&gt;0,MAX(0,C68-'Needs years'!$C$234)/(C72-'Needs years'!$C$234)*'Needs years'!$J$228/12,0))</f>
@@ -18506,7 +18548,7 @@
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C75">
         <f>IF('Inputs'!$B$105="",0,ROUND(IF(C31="S",'Inputs'!$O$105*C28,IF(C31="K",'Inputs'!$L$105*IF('Inputs'!$N$105=1,C33,C32),0))+'Inputs'!$O$105*ROUND(SUM('Inputs'!$Z$22:$Z$39)*C14,2)+'Inputs'!$Q$105*IF('Inputs'!$S$105=1,C35+C37,C34+C36)+SUMPRODUCT(('Inputs'!$F$59:$F$70='Inputs'!$B$105)*('Inputs'!$C$59:$C$70&lt;&gt;"Estate")*('Inputs'!$C$59:$C$70&lt;&gt;""),('Inputs'!$D$59:$D$70-'Inputs'!$R$59:$R$70*ROUND(C18*'Inputs'!$D$59:$D$70,2)))+SUMPRODUCT(('Inputs'!$F$87:$F$94='Inputs'!$B$105)*'Inputs'!$J$87:$J$94)+C9-(1-'Inputs'!$T$105)*ROUND(C18*C9,2)-SUMPRODUCT(('Inputs'!$G$76:$G$81='Inputs'!$B$105)*ROUND(C18*'Inputs'!$O$76:$O$81,2)),2))</f>
@@ -18562,7 +18604,7 @@
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C76">
         <f>'Needs years'!$C$285+MAX(0,C75-'Needs years'!$C$290)*('Inputs'!$H$122/100*('Inputs'!$H$125/100+'Inputs'!$H$120/100*'Inputs'!$H$127/100))</f>
@@ -18618,7 +18660,7 @@
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C77">
         <f>IF(C76&lt;='Needs years'!$C$284,0,INDEX('Inputs'!$E$134:$E$140,MATCH(C76,'Inputs'!$C$134:$C$140,1)-IF(COUNTIF('Inputs'!$C$134:$C$140,C76)&gt;0,1,0))/100)</f>
@@ -18674,7 +18716,7 @@
     </row>
     <row r="78" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C78">
         <f>('Inputs'!$H$122/100*(1-('Inputs'!$H$125/100*C77+'Inputs'!$H$126/100*'Inputs'!$H$128/100+'Inputs'!$H$127/100*'Inputs'!$H$120/100*C77))-IF('Needs years'!$C$289=1,'Inputs'!$H$123/100,0))</f>
@@ -18730,7 +18772,7 @@
     </row>
     <row r="79" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C79">
         <f>IF('Inputs'!$B$105="",0,ROUND('Needs years'!$C$290+ROUND(IF(C78=0,SUM('Needs years'!$J$284:$J$333),(1-(1+C78)^-1)/(1-(1+C78)^(-1/12))/12*SUMPRODUCT('Needs years'!$J$284:$J$333,(1+C78)^(-'Needs years'!$I$284:$I$333))),2),2))</f>
@@ -18786,7 +18828,7 @@
     </row>
     <row r="80" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C80">
         <f>IF('Inputs'!$B$105="",0,ROUND(C79-C75,2))</f>
@@ -18842,7 +18884,7 @@
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C81">
         <f>IF('Inputs'!$B$105="",0,'Needs years'!$C$296+IF((C79-'Needs years'!$C$290)&gt;0,MAX(0,C75-'Needs years'!$C$290)/(C79-'Needs years'!$C$290)*'Needs years'!$J$284/12,0))</f>
@@ -18898,7 +18940,7 @@
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C82">
         <f>IF(C3=1,IF(AND(C4=0,C45&lt;=0),0,MAX(0,C4+C45/(1-(1-'Inputs'!$T$100)*C18))),0)</f>
@@ -18954,7 +18996,7 @@
     </row>
     <row r="83" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C83">
         <f>IF(C3=1,IF(AND(C5=0,C52&lt;=0),0,MAX(0,C5+C52/(1-(1-'Inputs'!$T$101)*C18))),0)</f>
@@ -19010,7 +19052,7 @@
     </row>
     <row r="84" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C84">
         <f>IF(C3=1,IF(AND(C6=0,C59&lt;=0),0,MAX(0,C6+C59/(1-(1-'Inputs'!$T$102)*C18))),0)</f>
@@ -19066,7 +19108,7 @@
     </row>
     <row r="85" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C85">
         <f>IF(C3=1,IF(AND(C7=0,C66&lt;=0),0,MAX(0,C7+C66/(1-(1-'Inputs'!$T$103)*C18))),0)</f>
@@ -19122,7 +19164,7 @@
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C86">
         <f>IF(C3=1,IF(AND(C8=0,C73&lt;=0),0,MAX(0,C8+C73/(1-(1-'Inputs'!$T$104)*C18))),0)</f>
@@ -19178,7 +19220,7 @@
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C87">
         <f>IF(C3=1,IF(AND(C9=0,C80&lt;=0),0,MAX(0,C9+C80/(1-(1-'Inputs'!$T$105)*C18))),0)</f>
@@ -19234,7 +19276,7 @@
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C88">
         <f>IF(C3=1,IF(AND(C10=0,C27&lt;=0),0,MAX(0,C10+C27/((1-('Inputs'!$C$120/100*(1+'Inputs'!$C$121/100)))*(1-IF('Inputs'!$C$14="Spouse",0,C18))))),0)</f>
@@ -19335,17 +19377,17 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -19380,7 +19422,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C8" s="19">
         <f>IF('Inputs'!$B$100="","",N('Inputs'!$E$100))</f>
@@ -19449,7 +19491,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C11" s="19">
         <f>IF('Inputs'!$B$100="","",'Needs years'!$C$10)</f>
@@ -19472,7 +19514,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C12" s="19">
         <f>IF('Inputs'!$B$100="","",'Needs years'!$C$15)</f>
@@ -19495,7 +19537,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C13" s="19">
         <f>IF('Inputs'!$B$100="","",SUMPRODUCT(('Inputs'!$G$76:$G$81='Inputs'!$B$100)*'Inputs'!$P$76:$P$81))</f>
@@ -19518,7 +19560,7 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="30" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C14" s="43">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$40)</f>
@@ -19541,7 +19583,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C15" s="38">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$42)</f>
@@ -19564,7 +19606,7 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C16" s="47">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$43)</f>
@@ -19587,7 +19629,7 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="30" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C17" s="43">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$44)</f>
@@ -19610,7 +19652,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C18" s="43">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$45)</f>
@@ -19633,7 +19675,7 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C19" s="19">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$46)</f>
@@ -19656,7 +19698,7 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -19691,7 +19733,7 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C23" s="43">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$T$4)</f>
@@ -19714,7 +19756,7 @@
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C24" s="19">
         <f>IF('Inputs'!$B$100="","",IF('Needs calc'!$T$4=0,"",IF('Inputs'!$T$100=1,"spouse, no duty",IF('Inputs'!$Q$100=1,"the trust","them"))))</f>
@@ -19737,7 +19779,7 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C25" s="19">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$T$40)</f>
@@ -19760,7 +19802,7 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C26" s="38">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$T$42)</f>
@@ -19783,7 +19825,7 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C27" s="19">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$T$44)</f>
@@ -19806,7 +19848,7 @@
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C28" s="19">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$T$45)</f>
@@ -19829,15 +19871,15 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C30" s="19">
-        <f>'Workings'!$C$67</f>
+        <f>'Workings'!$C$69</f>
       </c>
     </row>
     <row r="31" ht="27" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C31" s="19">
         <f>'Needs calc'!$T$10</f>
@@ -19845,7 +19887,7 @@
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C32" s="19">
         <f>'Needs calc'!$T$27</f>
@@ -19853,15 +19895,15 @@
     </row>
     <row r="33" ht="27" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C33" s="19">
-        <f>IF(AND(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),'Workings'!$C$67&gt;0),'Workings'!$C$67,0)</f>
+        <f>IF(AND(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union"),'Workings'!$C$69&gt;0),'Workings'!$C$69,0)</f>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C34" s="19">
         <f>'Needs calc'!$T$17</f>
@@ -19869,7 +19911,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C35" s="45">
         <f>'Needs calc'!$T$18</f>
@@ -19877,7 +19919,7 @@
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C36" s="19">
         <f>'Needs calc'!$T$26</f>
@@ -19885,7 +19927,7 @@
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="30" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C37" s="43">
         <f>('Needs calc'!$T$10+('Needs calc'!$T$4+'Needs calc'!$T$5+'Needs calc'!$T$6+'Needs calc'!$T$7+'Needs calc'!$T$8+'Needs calc'!$T$9))</f>
@@ -19893,7 +19935,7 @@
     </row>
     <row r="39" ht="18" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
@@ -19928,7 +19970,7 @@
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C41" s="19">
         <f>IF('Inputs'!$B$100="","",'Needs years'!$C$11)</f>
@@ -19951,7 +19993,7 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C42" s="19">
         <f>IF('Inputs'!$B$100="","",'Needs years'!$C$12)</f>
@@ -19974,7 +20016,7 @@
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C43" s="19">
         <f>IF('Inputs'!$B$100="","",'Needs years'!$C$13)</f>
@@ -20084,7 +20126,7 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="25">
-        <f>IF('Workings'!$C$67&gt;0,"Your estate itself would be short of cash by about R "&amp;FIXED(ROUND('Workings'!$C$67,-3),0)&amp;" to pay its debts and costs.","Your estate itself has enough cash to pay its debts and costs, with about R "&amp;FIXED(ROUND('Workings'!$C$68,-3),0)&amp;" left over for your heirs.")</f>
+        <f>IF('Workings'!$C$69&gt;0,"Your estate itself would be short of cash by about R "&amp;FIXED(ROUND('Workings'!$C$69,-3),0)&amp;" to pay its debts and costs.","Your estate itself has enough cash to pay its debts and costs, with about R "&amp;FIXED(ROUND('Workings'!$C$70,-3),0)&amp;" left over for your heirs.")</f>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
@@ -20134,7 +20176,7 @@
         <v>189</v>
       </c>
       <c r="C15" s="15">
-        <f>'Workings'!$C$63</f>
+        <f>'Workings'!$C$65</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
@@ -20145,7 +20187,7 @@
         <v>190</v>
       </c>
       <c r="C16" s="15">
-        <f>'Workings'!$C$66</f>
+        <f>'Workings'!$C$68</f>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
@@ -20156,7 +20198,7 @@
         <v>191</v>
       </c>
       <c r="C17" s="37">
-        <f>IF('Workings'!$C$67&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$C$67,-3),0)&amp;". Cover paid to your estate to close it: R "&amp;FIXED(ROUND('Needs calc'!$T$10,-3),0)&amp;IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union")," (or R "&amp;FIXED(ROUND('Workings'!$C$67,-3),0)&amp;" nominated to your spouse, who pays it in)","")&amp;".","Covered: R "&amp;FIXED(ROUND('Workings'!$C$68,-3),0)&amp;" left for your heirs")</f>
+        <f>IF('Workings'!$C$69&gt;0,"Short R "&amp;FIXED(ROUND('Workings'!$C$69,-3),0)&amp;". Cover paid to your estate to close it: R "&amp;FIXED(ROUND('Needs calc'!$T$10,-3),0)&amp;IF(OR(LEFT('Inputs'!$C$13,7)="Married",'Inputs'!$C$13="Life partner",'Inputs'!$C$13="Civil Union")," (or R "&amp;FIXED(ROUND('Workings'!$C$69,-3),0)&amp;" nominated to your spouse, who pays it in)","")&amp;".","Covered: R "&amp;FIXED(ROUND('Workings'!$C$70,-3),0)&amp;" left for your heirs")</f>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>

--- a/Duwalcoe_Quick_FNA_Template.xlsx
+++ b/Duwalcoe_Quick_FNA_Template.xlsx
@@ -1726,7 +1726,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
     <dxf>
       <font>
         <b/>
@@ -1947,6 +1947,18 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6006,6 +6018,11 @@
       <formula>B100&lt;&gt;AA100</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
+    <cfRule type="expression" dxfId="27" priority="21">
+      <formula>AND(C11&lt;&gt;"",NOT(ISNUMBER(C11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="53">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C100:C105">
       <formula1>'Lists'!$F$2:$F$4</formula1>
@@ -6016,10 +6033,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C107">
       <formula1>'Lists'!$H$2:$H$3</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2026-10-13." sqref="C11:C12">
-      <formula1>32874</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C11:C12"/>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Percentage" error="Please type the percentage as a plain number, e.g. 2.92 for 2.92%. Do not add the % sign." sqref="C112">
       <formula1>0</formula1>
       <formula2>100</formula2>

--- a/Duwalcoe_Quick_FNA_Template.xlsx
+++ b/Duwalcoe_Quick_FNA_Template.xlsx
@@ -95,7 +95,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inputs'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Summary'!$A1:$D36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Life cover need'!$A1:$F42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Life cover need'!$A1:$F49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Life cover need'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Figures for quoting'!$A1:$D37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Figures for quoting'!$1:$2</definedName>
@@ -201,7 +201,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.8</t>
+    <t>2.9</t>
   </si>
   <si>
     <t>Shares and unit trusts</t>
@@ -1705,7 +1705,7 @@
     <numFmt numFmtId="166" formatCode="&quot;R &quot;#,##0;&quot;(R &quot;#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1822,6 +1822,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF0E413A"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color rgb="FF333333"/>
       <sz val="9.5"/>
       <name val="Arial"/>
@@ -1911,7 +1917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
@@ -2034,7 +2040,10 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -2836,7 +2845,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:F42"/>
+  <dimension ref="B1:F49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2939,7 +2948,7 @@
     </row>
     <row r="15" ht="27" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="37">
-        <f>IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")=0,"No one who depends on you is recorded","Income for "&amp;('Inputs'!$X$100&amp;'Inputs'!$X$101&amp;'Inputs'!$X$102&amp;'Inputs'!$X$103&amp;'Inputs'!$X$104&amp;'Inputs'!$X$105)&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," (each for their own years)","")&amp;IF(('Needs years'!$C$10+'Needs years'!$C$66+'Needs years'!$C$122+'Needs years'!$C$178+'Needs years'!$C$234+'Needs years'!$C$290)&gt;0,", and the once-off needs",""))</f>
+        <f>IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")=0,"No one who depends on you is recorded","Income for "&amp;('Inputs'!$X$100&amp;'Inputs'!$X$101&amp;'Inputs'!$X$102&amp;'Inputs'!$X$103&amp;'Inputs'!$X$104&amp;'Inputs'!$X$105)&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," (each for their own years)","")&amp;IF(('Needs years'!$C$10+'Needs years'!$C$66+'Needs years'!$C$122+'Needs years'!$C$178+'Needs years'!$C$234+'Needs years'!$C$290)&gt;0,", and the once-off needs","")&amp;IF((SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))&gt;0,", after the income already coming in",""))</f>
       </c>
       <c r="C15" s="37"/>
       <c r="D15" s="37"/>
@@ -3158,72 +3167,126 @@
         <f>IF('Inputs'!$B$103="","",IF('Inputs'!$U$103=1,"with "&amp;'Needs years'!$C$1,IF('Needs calc'!$T$7&gt;0,'Needs calc'!$T$7,"None needed")))</f>
       </c>
     </row>
-    <row r="33" ht="40" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="41">
-        <f>TRIM(IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;4,"The others who depend on you are on the workings page. ","")&amp;IF(SUM('Inputs'!$U$100:$U$105)&gt;0,"The children's needs are added to "&amp;'Needs years'!$C$1&amp;"'s, who provides for them. ","")&amp;IF('Needs calc'!$C$38&gt;0,"Life cover of R "&amp;FIXED(ROUND('Needs calc'!$C$38,-3),0)&amp;" is paid directly to "&amp;IF(SUMPRODUCT('Inputs'!$R$59:$R$70*('Inputs'!$F$59:$F$70="")*('Inputs'!$D$59:$D$70&gt;0))=1,"someone who is","people who are")&amp;" not recorded as depending on you"&amp;IF('Needs calc'!$C$39&gt;0,"; they pay R "&amp;FIXED(ROUND('Needs calc'!$C$39,-3),0)&amp;" of the estate duty on it today","")&amp;", and it is not counted above. ","")&amp;IF(SUMPRODUCT(('Inputs'!$D$76:$D$81&gt;0)*1)&gt;0,"Death income from your policies is set against the need of the person it is for while it pays"&amp;IF(SUM('Inputs'!$P$76:$P$81)&gt;0,"; the people it is paid to or for pay R "&amp;FIXED(ROUND(SUM('Inputs'!$P$76:$P$81),-3),0)&amp;" of the estate duty on it today, taken off what reaches them","")&amp;".","")&amp;IF(SUMPRODUCT(('Inputs'!$D$114:$D$121&gt;0)*1)&gt;0," Income they will still receive is set against their need in each year it pays. It is not a policy, so it carries no estate duty.",""))</f>
+        <f>IF((SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))=0,"","Income already coming in, which the figures above have taken off")</f>
       </c>
       <c r="C33" s="41"/>
       <c r="D33" s="41"/>
       <c r="E33" s="41"/>
       <c r="F33" s="41"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="41">
+    <row r="34" ht="13" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="42">
+        <f>IF(IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(1,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(1,'Inputs'!$N$114:$N$121,0)),""))="","","   •   "&amp;IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(1,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(1,'Inputs'!$N$114:$N$121,0)),""))&amp;IF(AND(1=5,(SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))&gt;5),"   (and "&amp;FIXED((SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))-5,0)&amp;" more on the workings page)",""))</f>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+    </row>
+    <row r="35" ht="13" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="42">
+        <f>IF(IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(2,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(2,'Inputs'!$N$114:$N$121,0)),""))="","","   •   "&amp;IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(2,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(2,'Inputs'!$N$114:$N$121,0)),""))&amp;IF(AND(2=5,(SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))&gt;5),"   (and "&amp;FIXED((SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))-5,0)&amp;" more on the workings page)",""))</f>
+      </c>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+    </row>
+    <row r="36" ht="13" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="42">
+        <f>IF(IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(3,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(3,'Inputs'!$N$114:$N$121,0)),""))="","","   •   "&amp;IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(3,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(3,'Inputs'!$N$114:$N$121,0)),""))&amp;IF(AND(3=5,(SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))&gt;5),"   (and "&amp;FIXED((SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))-5,0)&amp;" more on the workings page)",""))</f>
+      </c>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+    </row>
+    <row r="37" ht="13" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="42">
+        <f>IF(IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(4,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(4,'Inputs'!$N$114:$N$121,0)),""))="","","   •   "&amp;IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(4,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(4,'Inputs'!$N$114:$N$121,0)),""))&amp;IF(AND(4=5,(SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))&gt;5),"   (and "&amp;FIXED((SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))-5,0)&amp;" more on the workings page)",""))</f>
+      </c>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+    </row>
+    <row r="38" ht="13" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="42">
+        <f>IF(IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(5,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(5,'Inputs'!$N$114:$N$121,0)),""))="","","   •   "&amp;IFERROR(INDEX('Inputs'!$W$76:$W$81,MATCH(5,'Inputs'!$V$76:$V$81,0)),IFERROR(INDEX('Inputs'!$P$114:$P$121,MATCH(5,'Inputs'!$N$114:$N$121,0)),""))&amp;IF(AND(5=5,(SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))&gt;5),"   (and "&amp;FIXED((SUM('Inputs'!$U$76:$U$81)+SUM('Inputs'!$M$114:$M$121))-5,0)&amp;" more on the workings page)",""))</f>
+      </c>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+    </row>
+    <row r="40" ht="40" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="42">
+        <f>TRIM(IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;4,"The others who depend on you are on the workings page. ","")&amp;IF(SUM('Inputs'!$U$100:$U$105)&gt;0,"The children's needs are added to "&amp;'Needs years'!$C$1&amp;"'s, who provides for them. ","")&amp;IF('Needs calc'!$C$38&gt;0,"Life cover of R "&amp;FIXED(ROUND('Needs calc'!$C$38,-3),0)&amp;" is paid directly to "&amp;IF(SUMPRODUCT('Inputs'!$R$59:$R$70*('Inputs'!$F$59:$F$70="")*('Inputs'!$D$59:$D$70&gt;0))=1,"someone who is","people who are")&amp;" not recorded as depending on you"&amp;IF('Needs calc'!$C$39&gt;0,"; they pay R "&amp;FIXED(ROUND('Needs calc'!$C$39,-3),0)&amp;" of the estate duty on it today","")&amp;", and it is not counted above. ","")&amp;IF(SUMPRODUCT(('Inputs'!$D$76:$D$81&gt;0)*1)&gt;0,"Death income from your policies is set against the need of the person it is for while it pays"&amp;IF(SUM('Inputs'!$P$76:$P$81)&gt;0,"; the people it is paid to or for pay R "&amp;FIXED(ROUND(SUM('Inputs'!$P$76:$P$81),-3),0)&amp;" of the estate duty on it today, taken off what reaches them","")&amp;".","")&amp;IF(SUMPRODUCT(('Inputs'!$D$114:$D$121&gt;0)*1)&gt;0," Income they will still receive is set against their need in each year it pays. It is not a policy, so it carries no estate duty.",""))</f>
+      </c>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="42">
         <f>IF(SUMPRODUCT(('Inputs'!$H$100:$H$105="Yes")*('Inputs'!$B$100:$B$105&lt;&gt;""))&gt;0,"Money held in the children's trust is charged trustee fees of "&amp;IF(ROUND('Inputs'!$H$137,0)='Inputs'!$H$137,FIXED('Inputs'!$H$137,0),IF(ROUND('Inputs'!$H$137,1)='Inputs'!$H$137,FIXED('Inputs'!$H$137,1),FIXED('Inputs'!$H$137,2)))&amp;"%"&amp;" a year; the capital needed above includes them.","")</f>
       </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="5" t="s">
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" ht="27" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="35">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" ht="27" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="35">
         <f>"1.  "&amp;IF(('Needs calc'!$T$10+('Needs calc'!$T$4+'Needs calc'!$T$5+'Needs calc'!$T$6+'Needs calc'!$T$7+'Needs calc'!$T$8+'Needs calc'!$T$9))&gt;0,"New life cover of R "&amp;FIXED(ROUND(('Needs calc'!$T$10+('Needs calc'!$T$4+'Needs calc'!$T$5+'Needs calc'!$T$6+'Needs calc'!$T$7+'Needs calc'!$T$8+'Needs calc'!$T$9)),-3),0)&amp;": "&amp;IF('Needs calc'!$T$10&gt;0,"R "&amp;FIXED(ROUND('Needs calc'!$T$10,-3),0)&amp;" paid into your estate"&amp;IF(('Needs calc'!$T$4+'Needs calc'!$T$5+'Needs calc'!$T$6+'Needs calc'!$T$7+'Needs calc'!$T$8+'Needs calc'!$T$9)&gt;0,", R "&amp;FIXED(ROUND(('Needs calc'!$T$4+'Needs calc'!$T$5+'Needs calc'!$T$6+'Needs calc'!$T$7+'Needs calc'!$T$8+'Needs calc'!$T$9),-3),0)&amp;" nominated to the people who depend on you",""),IF(AND(('Needs calc'!$T$4+'Needs calc'!$T$5+'Needs calc'!$T$6+'Needs calc'!$T$7+'Needs calc'!$T$8+'Needs calc'!$T$9)&gt;0,ABS(('Inputs'!$O$100*'Needs calc'!$T$4+'Inputs'!$O$101*'Needs calc'!$T$5+'Inputs'!$O$102*'Needs calc'!$T$6+'Inputs'!$O$103*'Needs calc'!$T$7+'Inputs'!$O$104*'Needs calc'!$T$8+'Inputs'!$O$105*'Needs calc'!$T$9)-('Needs calc'!$T$4+'Needs calc'!$T$5+'Needs calc'!$T$6+'Needs calc'!$T$7+'Needs calc'!$T$8+'Needs calc'!$T$9))&lt;0.01),"nominated to "&amp;'Needs years'!$F$1&amp;IF(SUMPRODUCT(('Inputs'!$T$100:$T$105=1)*1)&gt;0,", so no estate duty",""),"nominated to the people who depend on you as shown below"))&amp;".","Keep your nominations and will instructions as they are: they provide for everyone today.")</f>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-    </row>
-    <row r="39" ht="27" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="35" t="s">
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="35"/>
+    </row>
+    <row r="46" ht="27" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-    </row>
-    <row r="40" ht="27" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="35">
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+    </row>
+    <row r="47" ht="27" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="35">
         <f>"3.  "&amp;IF(SUMPRODUCT(('Inputs'!$H$100:$H$105="Yes")*('Inputs'!$B$100:$B$105&lt;&gt;""))&gt;0,"Make sure your will sets up the trust that receives the children's money, and names the trustees.","Sign a will that says who inherits, so the law does not decide it for you.")</f>
       </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-    </row>
-    <row r="42" ht="44" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="36">
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+    </row>
+    <row r="49" ht="44" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="36">
         <f>"Basis: indicative, on the needs you gave us and your policies and will instructions as they stand. Capital for a person is invested at "&amp;FIXED('Inputs'!$H$136,0)&amp;"% a year before tax as a unit trust, less their tax"&amp;IF(SUMPRODUCT(('Inputs'!$H$100:$H$105="Yes")*('Inputs'!$B$100:$B$105&lt;&gt;""))&gt;0," and trustee fees of "&amp;IF(ROUND('Inputs'!$H$137,0)='Inputs'!$H$137,FIXED('Inputs'!$H$137,0),IF(ROUND('Inputs'!$H$137,1)='Inputs'!$H$137,FIXED('Inputs'!$H$137,1),FIXED('Inputs'!$H$137,2)))&amp;"%"&amp;" a year while it is in the trust","")&amp;". Once-off needs are in today's money. Retirement money is paid out in cash, after the lump sum tax on death benefits. Each need rises as you asked. Not legal or tax advice."</f>
       </c>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
-  <mergeCells count="26">
+  <mergeCells count="32">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
@@ -3245,11 +3308,17 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B49:F49"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:F12">
     <cfRule type="expression" dxfId="26" priority="1">
@@ -5459,7 +5528,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="76" ht="27" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="76" ht="27" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B76" s="8"/>
       <c r="C76" s="10"/>
       <c r="D76" s="11"/>
@@ -5498,8 +5567,17 @@
       <c r="T76">
         <f>IF(AND(B76="",N(D76)=0),0,IF(OR(C76="",N(D76)&lt;=0,N(F76)&lt;=0,N(F76)&lt;&gt;INT(N(F76)),AND(C76="Estate",G76=""),AND(G76&lt;&gt;"",COUNTIF($B$100:$B$105,G76)=0)),1,0))</f>
       </c>
-    </row>
-    <row r="77" ht="27" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U76">
+        <f>IF(AND(N(D76)&gt;0,N(F76)&gt;0,G76&lt;&gt;"",COUNTIF($B$100:$B$105,G76)&gt;0),1,0)</f>
+      </c>
+      <c r="V76">
+        <f>IF(U76=1,SUM(U$76:U76),0)</f>
+      </c>
+      <c r="W76">
+        <f>"Your "&amp;B76&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;G76,"")&amp;": R "&amp;FIXED(ROUND(N(D76),0),0)&amp;" a month "&amp;IF(MOD(N(F76),12)=0,"for the first "&amp;FIXED(N(F76)/12,0)&amp;" year"&amp;IF(N(F76)=12,"","s"),"for the first "&amp;FIXED(N(F76),0)&amp;" months")</f>
+      </c>
+    </row>
+    <row r="77" ht="27" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B77" s="8"/>
       <c r="C77" s="10"/>
       <c r="D77" s="11"/>
@@ -5538,8 +5616,17 @@
       <c r="T77">
         <f>IF(AND(B77="",N(D77)=0),0,IF(OR(C77="",N(D77)&lt;=0,N(F77)&lt;=0,N(F77)&lt;&gt;INT(N(F77)),AND(C77="Estate",G77=""),AND(G77&lt;&gt;"",COUNTIF($B$100:$B$105,G77)=0)),1,0))</f>
       </c>
-    </row>
-    <row r="78" ht="27" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U77">
+        <f>IF(AND(N(D77)&gt;0,N(F77)&gt;0,G77&lt;&gt;"",COUNTIF($B$100:$B$105,G77)&gt;0),1,0)</f>
+      </c>
+      <c r="V77">
+        <f>IF(U77=1,SUM(U$76:U77),0)</f>
+      </c>
+      <c r="W77">
+        <f>"Your "&amp;B77&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;G77,"")&amp;": R "&amp;FIXED(ROUND(N(D77),0),0)&amp;" a month "&amp;IF(MOD(N(F77),12)=0,"for the first "&amp;FIXED(N(F77)/12,0)&amp;" year"&amp;IF(N(F77)=12,"","s"),"for the first "&amp;FIXED(N(F77),0)&amp;" months")</f>
+      </c>
+    </row>
+    <row r="78" ht="27" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B78" s="8"/>
       <c r="C78" s="10"/>
       <c r="D78" s="11"/>
@@ -5578,8 +5665,17 @@
       <c r="T78">
         <f>IF(AND(B78="",N(D78)=0),0,IF(OR(C78="",N(D78)&lt;=0,N(F78)&lt;=0,N(F78)&lt;&gt;INT(N(F78)),AND(C78="Estate",G78=""),AND(G78&lt;&gt;"",COUNTIF($B$100:$B$105,G78)=0)),1,0))</f>
       </c>
-    </row>
-    <row r="79" ht="27" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U78">
+        <f>IF(AND(N(D78)&gt;0,N(F78)&gt;0,G78&lt;&gt;"",COUNTIF($B$100:$B$105,G78)&gt;0),1,0)</f>
+      </c>
+      <c r="V78">
+        <f>IF(U78=1,SUM(U$76:U78),0)</f>
+      </c>
+      <c r="W78">
+        <f>"Your "&amp;B78&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;G78,"")&amp;": R "&amp;FIXED(ROUND(N(D78),0),0)&amp;" a month "&amp;IF(MOD(N(F78),12)=0,"for the first "&amp;FIXED(N(F78)/12,0)&amp;" year"&amp;IF(N(F78)=12,"","s"),"for the first "&amp;FIXED(N(F78),0)&amp;" months")</f>
+      </c>
+    </row>
+    <row r="79" ht="27" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B79" s="8"/>
       <c r="C79" s="10"/>
       <c r="D79" s="11"/>
@@ -5618,8 +5714,17 @@
       <c r="T79">
         <f>IF(AND(B79="",N(D79)=0),0,IF(OR(C79="",N(D79)&lt;=0,N(F79)&lt;=0,N(F79)&lt;&gt;INT(N(F79)),AND(C79="Estate",G79=""),AND(G79&lt;&gt;"",COUNTIF($B$100:$B$105,G79)=0)),1,0))</f>
       </c>
-    </row>
-    <row r="80" ht="27" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U79">
+        <f>IF(AND(N(D79)&gt;0,N(F79)&gt;0,G79&lt;&gt;"",COUNTIF($B$100:$B$105,G79)&gt;0),1,0)</f>
+      </c>
+      <c r="V79">
+        <f>IF(U79=1,SUM(U$76:U79),0)</f>
+      </c>
+      <c r="W79">
+        <f>"Your "&amp;B79&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;G79,"")&amp;": R "&amp;FIXED(ROUND(N(D79),0),0)&amp;" a month "&amp;IF(MOD(N(F79),12)=0,"for the first "&amp;FIXED(N(F79)/12,0)&amp;" year"&amp;IF(N(F79)=12,"","s"),"for the first "&amp;FIXED(N(F79),0)&amp;" months")</f>
+      </c>
+    </row>
+    <row r="80" ht="27" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B80" s="8"/>
       <c r="C80" s="10"/>
       <c r="D80" s="11"/>
@@ -5658,8 +5763,17 @@
       <c r="T80">
         <f>IF(AND(B80="",N(D80)=0),0,IF(OR(C80="",N(D80)&lt;=0,N(F80)&lt;=0,N(F80)&lt;&gt;INT(N(F80)),AND(C80="Estate",G80=""),AND(G80&lt;&gt;"",COUNTIF($B$100:$B$105,G80)=0)),1,0))</f>
       </c>
-    </row>
-    <row r="81" ht="27" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U80">
+        <f>IF(AND(N(D80)&gt;0,N(F80)&gt;0,G80&lt;&gt;"",COUNTIF($B$100:$B$105,G80)&gt;0),1,0)</f>
+      </c>
+      <c r="V80">
+        <f>IF(U80=1,SUM(U$76:U80),0)</f>
+      </c>
+      <c r="W80">
+        <f>"Your "&amp;B80&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;G80,"")&amp;": R "&amp;FIXED(ROUND(N(D80),0),0)&amp;" a month "&amp;IF(MOD(N(F80),12)=0,"for the first "&amp;FIXED(N(F80)/12,0)&amp;" year"&amp;IF(N(F80)=12,"","s"),"for the first "&amp;FIXED(N(F80),0)&amp;" months")</f>
+      </c>
+    </row>
+    <row r="81" ht="27" customHeight="1" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B81" s="8"/>
       <c r="C81" s="10"/>
       <c r="D81" s="11"/>
@@ -5697,6 +5811,15 @@
       </c>
       <c r="T81">
         <f>IF(AND(B81="",N(D81)=0),0,IF(OR(C81="",N(D81)&lt;=0,N(F81)&lt;=0,N(F81)&lt;&gt;INT(N(F81)),AND(C81="Estate",G81=""),AND(G81&lt;&gt;"",COUNTIF($B$100:$B$105,G81)=0)),1,0))</f>
+      </c>
+      <c r="U81">
+        <f>IF(AND(N(D81)&gt;0,N(F81)&gt;0,G81&lt;&gt;"",COUNTIF($B$100:$B$105,G81)&gt;0),1,0)</f>
+      </c>
+      <c r="V81">
+        <f>IF(U81=1,SUM(U$76:U81),0)</f>
+      </c>
+      <c r="W81">
+        <f>"Your "&amp;B81&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;G81,"")&amp;": R "&amp;FIXED(ROUND(N(D81),0),0)&amp;" a month "&amp;IF(MOD(N(F81),12)=0,"for the first "&amp;FIXED(N(F81)/12,0)&amp;" year"&amp;IF(N(F81)=12,"","s"),"for the first "&amp;FIXED(N(F81),0)&amp;" months")</f>
       </c>
     </row>
     <row r="82" ht="39" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
@@ -6371,7 +6494,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="114" ht="27" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="114" ht="27" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
       <c r="D114" s="11"/>
@@ -6382,8 +6505,17 @@
       <c r="L114">
         <f>IF(AND(B114="",N(D114)=0),0,IF(OR(N(D114)&lt;=0,C114="",COUNTIF($B$100:$B$105,C114)=0,N(F114)&lt;&gt;INT(N(F114)),N(G114)&lt;&gt;INT(N(G114))),1,0))</f>
       </c>
-    </row>
-    <row r="115" ht="27" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M114">
+        <f>IF(AND(N(D114)&gt;0,C114&lt;&gt;"",COUNTIF($B$100:$B$105,C114)&gt;0),1,0)</f>
+      </c>
+      <c r="N114">
+        <f>IF(M114=1,SUM('Inputs'!$U$76:$U$81)+SUM(M$114:M114),0)</f>
+      </c>
+      <c r="P114">
+        <f>B114&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;C114,"")&amp;": R "&amp;FIXED(ROUND(N(D114),0),0)&amp;" a month "&amp;TRIM(IF(N(F114)=0,"",IF(MOD(N(F114),12)=0,"from year "&amp;FIXED(N(F114)/12,0),"from month "&amp;FIXED(N(F114),0)))&amp;" "&amp;IF(N(G114)=0,IF(N(F114)=0,"for as long as this need lasts","onwards"),IF(MOD(N(G114),12)=0,"for "&amp;FIXED(N(G114)/12,0)&amp;" year"&amp;IF(N(G114)=12,"","s"),"for "&amp;FIXED(N(G114),0)&amp;" months")))</f>
+      </c>
+    </row>
+    <row r="115" ht="27" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
       <c r="D115" s="11"/>
@@ -6394,8 +6526,17 @@
       <c r="L115">
         <f>IF(AND(B115="",N(D115)=0),0,IF(OR(N(D115)&lt;=0,C115="",COUNTIF($B$100:$B$105,C115)=0,N(F115)&lt;&gt;INT(N(F115)),N(G115)&lt;&gt;INT(N(G115))),1,0))</f>
       </c>
-    </row>
-    <row r="116" ht="27" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M115">
+        <f>IF(AND(N(D115)&gt;0,C115&lt;&gt;"",COUNTIF($B$100:$B$105,C115)&gt;0),1,0)</f>
+      </c>
+      <c r="N115">
+        <f>IF(M115=1,SUM('Inputs'!$U$76:$U$81)+SUM(M$114:M115),0)</f>
+      </c>
+      <c r="P115">
+        <f>B115&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;C115,"")&amp;": R "&amp;FIXED(ROUND(N(D115),0),0)&amp;" a month "&amp;TRIM(IF(N(F115)=0,"",IF(MOD(N(F115),12)=0,"from year "&amp;FIXED(N(F115)/12,0),"from month "&amp;FIXED(N(F115),0)))&amp;" "&amp;IF(N(G115)=0,IF(N(F115)=0,"for as long as this need lasts","onwards"),IF(MOD(N(G115),12)=0,"for "&amp;FIXED(N(G115)/12,0)&amp;" year"&amp;IF(N(G115)=12,"","s"),"for "&amp;FIXED(N(G115),0)&amp;" months")))</f>
+      </c>
+    </row>
+    <row r="116" ht="27" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
       <c r="D116" s="11"/>
@@ -6406,8 +6547,17 @@
       <c r="L116">
         <f>IF(AND(B116="",N(D116)=0),0,IF(OR(N(D116)&lt;=0,C116="",COUNTIF($B$100:$B$105,C116)=0,N(F116)&lt;&gt;INT(N(F116)),N(G116)&lt;&gt;INT(N(G116))),1,0))</f>
       </c>
-    </row>
-    <row r="117" ht="27" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M116">
+        <f>IF(AND(N(D116)&gt;0,C116&lt;&gt;"",COUNTIF($B$100:$B$105,C116)&gt;0),1,0)</f>
+      </c>
+      <c r="N116">
+        <f>IF(M116=1,SUM('Inputs'!$U$76:$U$81)+SUM(M$114:M116),0)</f>
+      </c>
+      <c r="P116">
+        <f>B116&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;C116,"")&amp;": R "&amp;FIXED(ROUND(N(D116),0),0)&amp;" a month "&amp;TRIM(IF(N(F116)=0,"",IF(MOD(N(F116),12)=0,"from year "&amp;FIXED(N(F116)/12,0),"from month "&amp;FIXED(N(F116),0)))&amp;" "&amp;IF(N(G116)=0,IF(N(F116)=0,"for as long as this need lasts","onwards"),IF(MOD(N(G116),12)=0,"for "&amp;FIXED(N(G116)/12,0)&amp;" year"&amp;IF(N(G116)=12,"","s"),"for "&amp;FIXED(N(G116),0)&amp;" months")))</f>
+      </c>
+    </row>
+    <row r="117" ht="27" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
       <c r="D117" s="11"/>
@@ -6418,8 +6568,17 @@
       <c r="L117">
         <f>IF(AND(B117="",N(D117)=0),0,IF(OR(N(D117)&lt;=0,C117="",COUNTIF($B$100:$B$105,C117)=0,N(F117)&lt;&gt;INT(N(F117)),N(G117)&lt;&gt;INT(N(G117))),1,0))</f>
       </c>
-    </row>
-    <row r="118" ht="27" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M117">
+        <f>IF(AND(N(D117)&gt;0,C117&lt;&gt;"",COUNTIF($B$100:$B$105,C117)&gt;0),1,0)</f>
+      </c>
+      <c r="N117">
+        <f>IF(M117=1,SUM('Inputs'!$U$76:$U$81)+SUM(M$114:M117),0)</f>
+      </c>
+      <c r="P117">
+        <f>B117&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;C117,"")&amp;": R "&amp;FIXED(ROUND(N(D117),0),0)&amp;" a month "&amp;TRIM(IF(N(F117)=0,"",IF(MOD(N(F117),12)=0,"from year "&amp;FIXED(N(F117)/12,0),"from month "&amp;FIXED(N(F117),0)))&amp;" "&amp;IF(N(G117)=0,IF(N(F117)=0,"for as long as this need lasts","onwards"),IF(MOD(N(G117),12)=0,"for "&amp;FIXED(N(G117)/12,0)&amp;" year"&amp;IF(N(G117)=12,"","s"),"for "&amp;FIXED(N(G117),0)&amp;" months")))</f>
+      </c>
+    </row>
+    <row r="118" ht="27" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
       <c r="D118" s="11"/>
@@ -6430,8 +6589,17 @@
       <c r="L118">
         <f>IF(AND(B118="",N(D118)=0),0,IF(OR(N(D118)&lt;=0,C118="",COUNTIF($B$100:$B$105,C118)=0,N(F118)&lt;&gt;INT(N(F118)),N(G118)&lt;&gt;INT(N(G118))),1,0))</f>
       </c>
-    </row>
-    <row r="119" ht="27" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M118">
+        <f>IF(AND(N(D118)&gt;0,C118&lt;&gt;"",COUNTIF($B$100:$B$105,C118)&gt;0),1,0)</f>
+      </c>
+      <c r="N118">
+        <f>IF(M118=1,SUM('Inputs'!$U$76:$U$81)+SUM(M$114:M118),0)</f>
+      </c>
+      <c r="P118">
+        <f>B118&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;C118,"")&amp;": R "&amp;FIXED(ROUND(N(D118),0),0)&amp;" a month "&amp;TRIM(IF(N(F118)=0,"",IF(MOD(N(F118),12)=0,"from year "&amp;FIXED(N(F118)/12,0),"from month "&amp;FIXED(N(F118),0)))&amp;" "&amp;IF(N(G118)=0,IF(N(F118)=0,"for as long as this need lasts","onwards"),IF(MOD(N(G118),12)=0,"for "&amp;FIXED(N(G118)/12,0)&amp;" year"&amp;IF(N(G118)=12,"","s"),"for "&amp;FIXED(N(G118),0)&amp;" months")))</f>
+      </c>
+    </row>
+    <row r="119" ht="27" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
       <c r="D119" s="11"/>
@@ -6442,8 +6610,17 @@
       <c r="L119">
         <f>IF(AND(B119="",N(D119)=0),0,IF(OR(N(D119)&lt;=0,C119="",COUNTIF($B$100:$B$105,C119)=0,N(F119)&lt;&gt;INT(N(F119)),N(G119)&lt;&gt;INT(N(G119))),1,0))</f>
       </c>
-    </row>
-    <row r="120" ht="27" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M119">
+        <f>IF(AND(N(D119)&gt;0,C119&lt;&gt;"",COUNTIF($B$100:$B$105,C119)&gt;0),1,0)</f>
+      </c>
+      <c r="N119">
+        <f>IF(M119=1,SUM('Inputs'!$U$76:$U$81)+SUM(M$114:M119),0)</f>
+      </c>
+      <c r="P119">
+        <f>B119&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;C119,"")&amp;": R "&amp;FIXED(ROUND(N(D119),0),0)&amp;" a month "&amp;TRIM(IF(N(F119)=0,"",IF(MOD(N(F119),12)=0,"from year "&amp;FIXED(N(F119)/12,0),"from month "&amp;FIXED(N(F119),0)))&amp;" "&amp;IF(N(G119)=0,IF(N(F119)=0,"for as long as this need lasts","onwards"),IF(MOD(N(G119),12)=0,"for "&amp;FIXED(N(G119)/12,0)&amp;" year"&amp;IF(N(G119)=12,"","s"),"for "&amp;FIXED(N(G119),0)&amp;" months")))</f>
+      </c>
+    </row>
+    <row r="120" ht="27" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
       <c r="D120" s="11"/>
@@ -6454,8 +6631,17 @@
       <c r="L120">
         <f>IF(AND(B120="",N(D120)=0),0,IF(OR(N(D120)&lt;=0,C120="",COUNTIF($B$100:$B$105,C120)=0,N(F120)&lt;&gt;INT(N(F120)),N(G120)&lt;&gt;INT(N(G120))),1,0))</f>
       </c>
-    </row>
-    <row r="121" ht="27" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M120">
+        <f>IF(AND(N(D120)&gt;0,C120&lt;&gt;"",COUNTIF($B$100:$B$105,C120)&gt;0),1,0)</f>
+      </c>
+      <c r="N120">
+        <f>IF(M120=1,SUM('Inputs'!$U$76:$U$81)+SUM(M$114:M120),0)</f>
+      </c>
+      <c r="P120">
+        <f>B120&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;C120,"")&amp;": R "&amp;FIXED(ROUND(N(D120),0),0)&amp;" a month "&amp;TRIM(IF(N(F120)=0,"",IF(MOD(N(F120),12)=0,"from year "&amp;FIXED(N(F120)/12,0),"from month "&amp;FIXED(N(F120),0)))&amp;" "&amp;IF(N(G120)=0,IF(N(F120)=0,"for as long as this need lasts","onwards"),IF(MOD(N(G120),12)=0,"for "&amp;FIXED(N(G120)/12,0)&amp;" year"&amp;IF(N(G120)=12,"","s"),"for "&amp;FIXED(N(G120),0)&amp;" months")))</f>
+      </c>
+    </row>
+    <row r="121" ht="27" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
       <c r="D121" s="11"/>
@@ -6465,6 +6651,15 @@
       <c r="I121" s="14"/>
       <c r="L121">
         <f>IF(AND(B121="",N(D121)=0),0,IF(OR(N(D121)&lt;=0,C121="",COUNTIF($B$100:$B$105,C121)=0,N(F121)&lt;&gt;INT(N(F121)),N(G121)&lt;&gt;INT(N(G121))),1,0))</f>
+      </c>
+      <c r="M121">
+        <f>IF(AND(N(D121)&gt;0,C121&lt;&gt;"",COUNTIF($B$100:$B$105,C121)&gt;0),1,0)</f>
+      </c>
+      <c r="N121">
+        <f>IF(M121=1,SUM('Inputs'!$U$76:$U$81)+SUM(M$114:M121),0)</f>
+      </c>
+      <c r="P121">
+        <f>B121&amp;IF(COUNTIF('Inputs'!$B$100:$B$105,"?*")&gt;1," for "&amp;C121,"")&amp;": R "&amp;FIXED(ROUND(N(D121),0),0)&amp;" a month "&amp;TRIM(IF(N(F121)=0,"",IF(MOD(N(F121),12)=0,"from year "&amp;FIXED(N(F121)/12,0),"from month "&amp;FIXED(N(F121),0)))&amp;" "&amp;IF(N(G121)=0,IF(N(F121)=0,"for as long as this need lasts","onwards"),IF(MOD(N(G121),12)=0,"for "&amp;FIXED(N(G121)/12,0)&amp;" year"&amp;IF(N(G121)=12,"","s"),"for "&amp;FIXED(N(G121),0)&amp;" months")))</f>
       </c>
     </row>
     <row r="122" ht="52" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
@@ -8050,11 +8245,11 @@
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
@@ -8134,11 +8329,11 @@
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
@@ -8196,11 +8391,11 @@
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
@@ -8236,11 +8431,11 @@
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
@@ -8465,10 +8660,10 @@
       <c r="B12" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="44">
         <f>MAX(0,C9+C10+C11)</f>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="44">
         <f>MAX(0,D9+D10+D11)</f>
       </c>
     </row>
@@ -8509,10 +8704,10 @@
       <c r="B16" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="44">
         <f>IF(C12&gt;0,ROUND(C14+C15,2),0)</f>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="44">
         <f>IF(D12&gt;0,ROUND(D14+D15,2),0)</f>
       </c>
     </row>
@@ -8553,10 +8748,10 @@
       <c r="B21" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="44">
         <f>C19+C20</f>
       </c>
-      <c r="D21" s="43">
+      <c r="D21" s="44">
         <f>D19+D20</f>
       </c>
     </row>
@@ -8608,10 +8803,10 @@
       <c r="B26" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="44">
         <f>C21+C22+C23+C24+C25</f>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="44">
         <f>D21+D22+D23+D24+D25</f>
       </c>
     </row>
@@ -8718,10 +8913,10 @@
       <c r="B36" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="45">
         <f>IF(C35&lt;0,IF(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39)&gt;0,MAX(0,1+C35/(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39))),1),1)</f>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="45">
         <f>IF(D35&lt;0,IF(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39)&gt;0,MAX(0,1+D35/(SUM('Inputs'!$R$22:$R$39)+SUM('Inputs'!$S$22:$S$39))),1),1)</f>
       </c>
     </row>
@@ -8740,10 +8935,10 @@
       <c r="B38" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="C38" s="43">
+      <c r="C38" s="44">
         <f>ROUND(C26+C27+C28+C29+C30+C31+C32+C33+C34+C37,2)</f>
       </c>
-      <c r="D38" s="43">
+      <c r="D38" s="44">
         <f>ROUND(D26+D27+D28+D29+D30+D31+D32+D33+D34+D37,2)</f>
       </c>
     </row>
@@ -8773,10 +8968,10 @@
       <c r="B41" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="C41" s="43">
+      <c r="C41" s="44">
         <f>ROUND(IF(C40&lt;='Inputs'!$C$143,C40*'Inputs'!$C$142/100,'Inputs'!$C$143*'Inputs'!$C$142/100+(C40-'Inputs'!$C$143)*'Inputs'!$C$144/100),2)</f>
       </c>
-      <c r="D41" s="43">
+      <c r="D41" s="44">
         <f>ROUND(IF(D40&lt;='Inputs'!$C$143,D40*'Inputs'!$C$142/100,'Inputs'!$C$143*'Inputs'!$C$142/100+(D40-'Inputs'!$C$143)*'Inputs'!$C$144/100),2)</f>
       </c>
     </row>
@@ -8784,10 +8979,10 @@
       <c r="B42" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="C42" s="45">
+      <c r="C42" s="46">
         <f>IF(C38&gt;0,C41/C38,0)</f>
       </c>
-      <c r="D42" s="45">
+      <c r="D42" s="46">
         <f>IF(D38&gt;0,D41/D38,0)</f>
       </c>
     </row>
@@ -8877,10 +9072,10 @@
       <c r="B51" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="43">
+      <c r="C51" s="44">
         <f>C41+C50</f>
       </c>
-      <c r="D51" s="43">
+      <c r="D51" s="44">
         <f>D41+D50</f>
       </c>
     </row>
@@ -8970,10 +9165,10 @@
       <c r="B61" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="C61" s="43">
+      <c r="C61" s="44">
         <f>ROUND(SUM(C55:C60),2)</f>
       </c>
-      <c r="D61" s="43">
+      <c r="D61" s="44">
         <f>ROUND(SUM(D55:D60),2)</f>
       </c>
     </row>
@@ -8992,10 +9187,10 @@
       <c r="B63" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="C63" s="43">
+      <c r="C63" s="44">
         <f>ROUND(C61+C62,2)</f>
       </c>
-      <c r="D63" s="43">
+      <c r="D63" s="44">
         <f>ROUND(D61+D62,2)</f>
       </c>
     </row>
@@ -9014,10 +9209,10 @@
       <c r="B65" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="C65" s="43">
+      <c r="C65" s="44">
         <f>ROUND(C63+C64,2)</f>
       </c>
-      <c r="D65" s="43">
+      <c r="D65" s="44">
         <f>ROUND(D63+D64,2)</f>
       </c>
     </row>
@@ -9102,10 +9297,10 @@
       <c r="B73" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="C73" s="43">
+      <c r="C73" s="44">
         <f>C66+C67+C72</f>
       </c>
-      <c r="D73" s="43">
+      <c r="D73" s="44">
         <f>D66+D67+D72</f>
       </c>
     </row>
@@ -9113,10 +9308,10 @@
       <c r="B74" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="C74" s="43">
+      <c r="C74" s="44">
         <f>ROUND(MAX(0,C65-C73),2)</f>
       </c>
-      <c r="D74" s="43">
+      <c r="D74" s="44">
         <f>ROUND(MAX(0,D65-D73),2)</f>
       </c>
     </row>
@@ -9135,10 +9330,10 @@
       <c r="B76" s="30" t="s">
         <v>292</v>
       </c>
-      <c r="C76" s="43">
+      <c r="C76" s="44">
         <f>ROUND(C21-C65,2)</f>
       </c>
-      <c r="D76" s="43">
+      <c r="D76" s="44">
         <f>ROUND(D21-D65,2)</f>
       </c>
     </row>
@@ -27476,22 +27671,22 @@
       <c r="B9" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="47">
         <f>IF('Inputs'!$B$100="","",IF('Needs years'!$C$6=0,"",'Needs years'!$C$6))</f>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="47">
         <f>IF('Inputs'!$B$101="","",IF('Needs years'!$C$62=0,"",'Needs years'!$C$62))</f>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="47">
         <f>IF('Inputs'!$B$102="","",IF('Needs years'!$C$118=0,"",'Needs years'!$C$118))</f>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="47">
         <f>IF('Inputs'!$B$103="","",IF('Needs years'!$C$174=0,"",'Needs years'!$C$174))</f>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="47">
         <f>IF('Inputs'!$B$104="","",IF('Needs years'!$C$230=0,"",'Needs years'!$C$230))</f>
       </c>
-      <c r="H9" s="46">
+      <c r="H9" s="47">
         <f>IF('Inputs'!$B$105="","",IF('Needs years'!$C$286=0,"",'Needs years'!$C$286))</f>
       </c>
     </row>
@@ -27499,22 +27694,22 @@
       <c r="B10" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="48">
         <f>IF('Inputs'!$B$100="","",IF('Needs years'!$C$6=0,"",'Needs years'!$C$8))</f>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="48">
         <f>IF('Inputs'!$B$101="","",IF('Needs years'!$C$62=0,"",'Needs years'!$C$64))</f>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="48">
         <f>IF('Inputs'!$B$102="","",IF('Needs years'!$C$118=0,"",'Needs years'!$C$120))</f>
       </c>
-      <c r="F10" s="47">
+      <c r="F10" s="48">
         <f>IF('Inputs'!$B$103="","",IF('Needs years'!$C$174=0,"",'Needs years'!$C$176))</f>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="48">
         <f>IF('Inputs'!$B$104="","",IF('Needs years'!$C$230=0,"",'Needs years'!$C$232))</f>
       </c>
-      <c r="H10" s="47">
+      <c r="H10" s="48">
         <f>IF('Inputs'!$B$105="","",IF('Needs years'!$C$286=0,"",'Needs years'!$C$288))</f>
       </c>
     </row>
@@ -27660,22 +27855,22 @@
       <c r="B17" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="44">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$40)</f>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="44">
         <f>IF('Inputs'!$B$101="","",'Needs calc'!$C$52)</f>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="44">
         <f>IF('Inputs'!$B$102="","",'Needs calc'!$C$64)</f>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="44">
         <f>IF('Inputs'!$B$103="","",'Needs calc'!$C$76)</f>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="44">
         <f>IF('Inputs'!$B$104="","",'Needs calc'!$C$88)</f>
       </c>
-      <c r="H17" s="43">
+      <c r="H17" s="44">
         <f>IF('Inputs'!$B$105="","",'Needs calc'!$C$100)</f>
       </c>
     </row>
@@ -27683,22 +27878,22 @@
       <c r="B18" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C18" s="48">
+      <c r="C18" s="49">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$42)</f>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="49">
         <f>IF('Inputs'!$B$101="","",'Needs calc'!$C$54)</f>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="49">
         <f>IF('Inputs'!$B$102="","",'Needs calc'!$C$66)</f>
       </c>
-      <c r="F18" s="48">
+      <c r="F18" s="49">
         <f>IF('Inputs'!$B$103="","",'Needs calc'!$C$78)</f>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="49">
         <f>IF('Inputs'!$B$104="","",'Needs calc'!$C$90)</f>
       </c>
-      <c r="H18" s="48">
+      <c r="H18" s="49">
         <f>IF('Inputs'!$B$105="","",'Needs calc'!$C$102)</f>
       </c>
     </row>
@@ -27706,22 +27901,22 @@
       <c r="B19" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="C19" s="47">
+      <c r="C19" s="48">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$43)</f>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="48">
         <f>IF('Inputs'!$B$101="","",'Needs calc'!$C$55)</f>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="48">
         <f>IF('Inputs'!$B$102="","",'Needs calc'!$C$67)</f>
       </c>
-      <c r="F19" s="47">
+      <c r="F19" s="48">
         <f>IF('Inputs'!$B$103="","",'Needs calc'!$C$79)</f>
       </c>
-      <c r="G19" s="47">
+      <c r="G19" s="48">
         <f>IF('Inputs'!$B$104="","",'Needs calc'!$C$91)</f>
       </c>
-      <c r="H19" s="47">
+      <c r="H19" s="48">
         <f>IF('Inputs'!$B$105="","",'Needs calc'!$C$103)</f>
       </c>
     </row>
@@ -27752,22 +27947,22 @@
       <c r="B21" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="44">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$44)</f>
       </c>
-      <c r="D21" s="43">
+      <c r="D21" s="44">
         <f>IF('Inputs'!$B$101="","",'Needs calc'!$C$56)</f>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="44">
         <f>IF('Inputs'!$B$102="","",'Needs calc'!$C$68)</f>
       </c>
-      <c r="F21" s="43">
+      <c r="F21" s="44">
         <f>IF('Inputs'!$B$103="","",'Needs calc'!$C$80)</f>
       </c>
-      <c r="G21" s="43">
+      <c r="G21" s="44">
         <f>IF('Inputs'!$B$104="","",'Needs calc'!$C$92)</f>
       </c>
-      <c r="H21" s="43">
+      <c r="H21" s="44">
         <f>IF('Inputs'!$B$105="","",'Needs calc'!$C$104)</f>
       </c>
     </row>
@@ -27775,22 +27970,22 @@
       <c r="B22" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="44">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$C$45)</f>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="44">
         <f>IF('Inputs'!$B$101="","",'Needs calc'!$C$57)</f>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="44">
         <f>IF('Inputs'!$B$102="","",'Needs calc'!$C$69)</f>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="44">
         <f>IF('Inputs'!$B$103="","",'Needs calc'!$C$81)</f>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="44">
         <f>IF('Inputs'!$B$104="","",'Needs calc'!$C$93)</f>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="44">
         <f>IF('Inputs'!$B$105="","",'Needs calc'!$C$105)</f>
       </c>
     </row>
@@ -27856,22 +28051,22 @@
       <c r="B27" s="30" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="44">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$T$4)</f>
       </c>
-      <c r="D27" s="43">
+      <c r="D27" s="44">
         <f>IF('Inputs'!$B$101="","",'Needs calc'!$T$5)</f>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="44">
         <f>IF('Inputs'!$B$102="","",'Needs calc'!$T$6)</f>
       </c>
-      <c r="F27" s="43">
+      <c r="F27" s="44">
         <f>IF('Inputs'!$B$103="","",'Needs calc'!$T$7)</f>
       </c>
-      <c r="G27" s="43">
+      <c r="G27" s="44">
         <f>IF('Inputs'!$B$104="","",'Needs calc'!$T$8)</f>
       </c>
-      <c r="H27" s="43">
+      <c r="H27" s="44">
         <f>IF('Inputs'!$B$105="","",'Needs calc'!$T$9)</f>
       </c>
     </row>
@@ -27925,22 +28120,22 @@
       <c r="B30" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C30" s="48">
+      <c r="C30" s="49">
         <f>IF('Inputs'!$B$100="","",'Needs calc'!$T$42)</f>
       </c>
-      <c r="D30" s="48">
+      <c r="D30" s="49">
         <f>IF('Inputs'!$B$101="","",'Needs calc'!$T$54)</f>
       </c>
-      <c r="E30" s="48">
+      <c r="E30" s="49">
         <f>IF('Inputs'!$B$102="","",'Needs calc'!$T$66)</f>
       </c>
-      <c r="F30" s="48">
+      <c r="F30" s="49">
         <f>IF('Inputs'!$B$103="","",'Needs calc'!$T$78)</f>
       </c>
-      <c r="G30" s="48">
+      <c r="G30" s="49">
         <f>IF('Inputs'!$B$104="","",'Needs calc'!$T$90)</f>
       </c>
-      <c r="H30" s="48">
+      <c r="H30" s="49">
         <f>IF('Inputs'!$B$105="","",'Needs calc'!$T$102)</f>
       </c>
     </row>
@@ -28042,7 +28237,7 @@
       <c r="B40" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="C40" s="45">
+      <c r="C40" s="46">
         <f>'Needs calc'!$T$18</f>
       </c>
     </row>
@@ -28058,7 +28253,7 @@
       <c r="B42" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="C42" s="43">
+      <c r="C42" s="44">
         <f>('Needs calc'!$T$10+('Needs calc'!$T$4+'Needs calc'!$T$5+'Needs calc'!$T$6+'Needs calc'!$T$7+'Needs calc'!$T$8+'Needs calc'!$T$9))</f>
       </c>
     </row>
